--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="153">
   <si>
     <t>Date</t>
   </si>
@@ -127,6 +127,9 @@
     <t>08:30</t>
   </si>
   <si>
+    <t>09:00</t>
+  </si>
+  <si>
     <t>10:00</t>
   </si>
   <si>
@@ -178,6 +181,9 @@
     <t>Thailand Thai League T1</t>
   </si>
   <si>
+    <t>Tunisia Ligue 1</t>
+  </si>
+  <si>
     <t>Montenegro Montenegrin First League</t>
   </si>
   <si>
@@ -214,12 +220,12 @@
     <t>England Championship</t>
   </si>
   <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
     <t>Brazil Serie A</t>
   </si>
   <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
     <t>Algeria Ligue 1</t>
   </si>
   <si>
@@ -235,33 +241,36 @@
     <t>Nakhon Ratchasima</t>
   </si>
   <si>
+    <t>Métlaoui</t>
+  </si>
+  <si>
+    <t>Dečić</t>
+  </si>
+  <si>
+    <t>Ethiopian Medhin</t>
+  </si>
+  <si>
+    <t>FK Jezero Plav</t>
+  </si>
+  <si>
+    <t>Sutjeska</t>
+  </si>
+  <si>
+    <t>Mladost DG</t>
+  </si>
+  <si>
     <t>Arsenal Tivat</t>
   </si>
   <si>
-    <t>Dečić</t>
-  </si>
-  <si>
-    <t>Mladost DG</t>
-  </si>
-  <si>
-    <t>Ethiopian Medhin</t>
-  </si>
-  <si>
-    <t>Sutjeska</t>
-  </si>
-  <si>
-    <t>FK Jezero Plav</t>
-  </si>
-  <si>
     <t>Persebaya Surabaya</t>
   </si>
   <si>
+    <t>Al Wasl</t>
+  </si>
+  <si>
     <t>Al Wahda</t>
   </si>
   <si>
-    <t>Al Wasl</t>
-  </si>
-  <si>
     <t>Atalanta</t>
   </si>
   <si>
@@ -277,57 +286,57 @@
     <t>Xerez Deportivo</t>
   </si>
   <si>
+    <t>Al Jazeera</t>
+  </si>
+  <si>
     <t>Al Faisaly</t>
   </si>
   <si>
-    <t>Al Jazeera</t>
-  </si>
-  <si>
     <t>Al Najma</t>
   </si>
   <si>
     <t>Al Feiha</t>
   </si>
   <si>
+    <t>Petrojet</t>
+  </si>
+  <si>
+    <t>National Bank of Egypt</t>
+  </si>
+  <si>
     <t>Al Masry</t>
   </si>
   <si>
-    <t>Petrojet</t>
-  </si>
-  <si>
-    <t>National Bank of Egypt</t>
+    <t>Millwall</t>
+  </si>
+  <si>
+    <t>Norwich City</t>
   </si>
   <si>
     <t>Sheffield United</t>
   </si>
   <si>
-    <t>Norwich City</t>
-  </si>
-  <si>
-    <t>Millwall</t>
-  </si>
-  <si>
     <t>Real Madrid</t>
   </si>
   <si>
+    <t>PSG</t>
+  </si>
+  <si>
+    <t>Juventus</t>
+  </si>
+  <si>
     <t>Stoke City</t>
   </si>
   <si>
-    <t>PSG</t>
-  </si>
-  <si>
-    <t>Juventus</t>
+    <t>RSB Berkane</t>
+  </si>
+  <si>
+    <t>Bragantino</t>
   </si>
   <si>
     <t>Remo</t>
   </si>
   <si>
-    <t>Bragantino</t>
-  </si>
-  <si>
-    <t>RSB Berkane</t>
-  </si>
-  <si>
     <t>Cruzeiro</t>
   </si>
   <si>
@@ -349,33 +358,36 @@
     <t>Rayong</t>
   </si>
   <si>
+    <t>ES Tunis</t>
+  </si>
+  <si>
+    <t>Mornar</t>
+  </si>
+  <si>
+    <t>Kedus Giorgis</t>
+  </si>
+  <si>
+    <t>Bokelj</t>
+  </si>
+  <si>
+    <t>Petrovac</t>
+  </si>
+  <si>
+    <t>Jedinstvo</t>
+  </si>
+  <si>
     <t>Budućnost</t>
   </si>
   <si>
-    <t>Mornar</t>
-  </si>
-  <si>
-    <t>Jedinstvo</t>
-  </si>
-  <si>
-    <t>Kedus Giorgis</t>
-  </si>
-  <si>
-    <t>Petrovac</t>
-  </si>
-  <si>
-    <t>Bokelj</t>
-  </si>
-  <si>
     <t>PSM</t>
   </si>
   <si>
+    <t>Shabab Al Ahli Dubai</t>
+  </si>
+  <si>
     <t>Ajman</t>
   </si>
   <si>
-    <t>Shabab Al Ahli Dubai</t>
-  </si>
-  <si>
     <t>Borussia Dortmund</t>
   </si>
   <si>
@@ -391,55 +403,55 @@
     <t>Real Jaén CF</t>
   </si>
   <si>
+    <t>Al Ramtha</t>
+  </si>
+  <si>
     <t>Sama Al Sarhan</t>
   </si>
   <si>
-    <t>Al Ramtha</t>
-  </si>
-  <si>
     <t>Al Nassr</t>
   </si>
   <si>
     <t>Neom SC</t>
   </si>
   <si>
+    <t>Al Ittihad</t>
+  </si>
+  <si>
+    <t>Pharco</t>
+  </si>
+  <si>
     <t>Coca-Cola</t>
   </si>
   <si>
-    <t>Al Ittihad</t>
-  </si>
-  <si>
-    <t>Pharco</t>
+    <t>Birmingham City</t>
+  </si>
+  <si>
+    <t>Sheffield Wednesday</t>
   </si>
   <si>
     <t>Coventry City</t>
   </si>
   <si>
-    <t>Sheffield Wednesday</t>
-  </si>
-  <si>
-    <t>Birmingham City</t>
-  </si>
-  <si>
     <t>Benfica</t>
   </si>
   <si>
+    <t>Monaco</t>
+  </si>
+  <si>
+    <t>Galatasaray</t>
+  </si>
+  <si>
     <t>Oxford United</t>
   </si>
   <si>
-    <t>Monaco</t>
-  </si>
-  <si>
-    <t>Galatasaray</t>
+    <t>Raja Casablanca</t>
+  </si>
+  <si>
+    <t>Atlético PR</t>
   </si>
   <si>
     <t>Internacional</t>
-  </si>
-  <si>
-    <t>Atlético PR</t>
-  </si>
-  <si>
-    <t>Raja Casablanca</t>
   </si>
   <si>
     <t>Corinthians</t>
@@ -824,7 +836,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI39"/>
+  <dimension ref="A1:AI40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:35">
@@ -942,16 +954,16 @@
         <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -966,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L2">
         <v>1.75</v>
@@ -1049,16 +1061,16 @@
         <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1073,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L3">
         <v>2.96</v>
@@ -1156,16 +1168,16 @@
         <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1180,7 +1192,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -1252,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AI4" s="3">
-        <v>46078.41666666666</v>
+        <v>46078.375</v>
       </c>
     </row>
     <row r="5" spans="1:35">
@@ -1260,19 +1272,19 @@
         <v>46078</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1287,7 +1299,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -1367,19 +1379,19 @@
         <v>46078</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F6" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1394,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -1474,19 +1486,19 @@
         <v>46078</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F7" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1501,7 +1513,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -1581,19 +1593,19 @@
         <v>46078</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F8" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1608,7 +1620,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -1688,19 +1700,19 @@
         <v>46078</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F9" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1715,7 +1727,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -1801,13 +1813,13 @@
         <v>56</v>
       </c>
       <c r="D10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F10" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1822,7 +1834,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -1894,7 +1906,7 @@
         <v>0</v>
       </c>
       <c r="AI10" s="3">
-        <v>46078.4375</v>
+        <v>46078.41666666666</v>
       </c>
     </row>
     <row r="11" spans="1:35">
@@ -1905,16 +1917,16 @@
         <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E11" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F11" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1929,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -2001,7 +2013,7 @@
         <v>0</v>
       </c>
       <c r="AI11" s="3">
-        <v>46078.60416666666</v>
+        <v>46078.4375</v>
       </c>
     </row>
     <row r="12" spans="1:35">
@@ -2009,19 +2021,19 @@
         <v>46078</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E12" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F12" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2036,7 +2048,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -2119,16 +2131,16 @@
         <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F13" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2143,16 +2155,16 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L13">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M13">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N13">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -2191,10 +2203,10 @@
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB13">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC13">
         <v>0</v>
@@ -2215,7 +2227,7 @@
         <v>0</v>
       </c>
       <c r="AI13" s="3">
-        <v>46078.61458333334</v>
+        <v>46078.60416666666</v>
       </c>
     </row>
     <row r="14" spans="1:35">
@@ -2226,16 +2238,16 @@
         <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D14" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E14" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F14" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2250,16 +2262,16 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L14">
-        <v>2.48</v>
+        <v>2.19</v>
       </c>
       <c r="M14">
-        <v>2.7</v>
+        <v>3.78</v>
       </c>
       <c r="N14">
-        <v>3.07</v>
+        <v>3.41</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -2292,16 +2304,16 @@
         <v>0</v>
       </c>
       <c r="Y14">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>3.5</v>
+        <v>1.79</v>
       </c>
       <c r="AB14">
-        <v>1.28</v>
+        <v>1.91</v>
       </c>
       <c r="AC14">
         <v>0</v>
@@ -2322,7 +2334,7 @@
         <v>0</v>
       </c>
       <c r="AI14" s="3">
-        <v>46078.625</v>
+        <v>46078.61458333334</v>
       </c>
     </row>
     <row r="15" spans="1:35">
@@ -2330,19 +2342,19 @@
         <v>46078</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E15" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F15" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2357,16 +2369,16 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L15">
-        <v>3.1</v>
+        <v>2.48</v>
       </c>
       <c r="M15">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="N15">
-        <v>2.2</v>
+        <v>3.07</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -2399,16 +2411,16 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA15">
-        <v>2.37</v>
+        <v>3.5</v>
       </c>
       <c r="AB15">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="AC15">
         <v>0</v>
@@ -2437,19 +2449,19 @@
         <v>46078</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D16" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E16" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F16" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2464,76 +2476,76 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L16">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="M16">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="N16">
-        <v>2.69</v>
+        <v>2.2</v>
       </c>
       <c r="O16">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q16">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R16">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z16">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>1.89</v>
+        <v>2.37</v>
       </c>
       <c r="AB16">
-        <v>1.87</v>
+        <v>1.53</v>
       </c>
       <c r="AC16">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="AD16">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE16">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH16">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3">
         <v>46078.625</v>
@@ -2547,16 +2559,16 @@
         <v>42</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D17" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E17" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F17" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2571,79 +2583,79 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="L17">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="M17">
-        <v>2.65</v>
+        <v>3.25</v>
       </c>
       <c r="N17">
-        <v>3.1</v>
+        <v>2.69</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA17">
-        <v>2.75</v>
+        <v>1.89</v>
       </c>
       <c r="AB17">
-        <v>1.4</v>
+        <v>1.87</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI17" s="3">
-        <v>46078.64583333334</v>
+        <v>46078.625</v>
       </c>
     </row>
     <row r="18" spans="1:35">
@@ -2654,16 +2666,16 @@
         <v>43</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D18" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E18" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F18" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2678,16 +2690,16 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -2726,10 +2738,10 @@
         <v>0</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC18">
         <v>0</v>
@@ -2750,7 +2762,7 @@
         <v>0</v>
       </c>
       <c r="AI18" s="3">
-        <v>46078.65625</v>
+        <v>46078.64583333334</v>
       </c>
     </row>
     <row r="19" spans="1:35">
@@ -2758,19 +2770,19 @@
         <v>46078</v>
       </c>
       <c r="B19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D19" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E19" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F19" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2785,7 +2797,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -2868,16 +2880,16 @@
         <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D20" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E20" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F20" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2892,7 +2904,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -2964,7 +2976,7 @@
         <v>0</v>
       </c>
       <c r="AI20" s="3">
-        <v>46078.66666666666</v>
+        <v>46078.65625</v>
       </c>
     </row>
     <row r="21" spans="1:35">
@@ -2972,19 +2984,19 @@
         <v>46078</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D21" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E21" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F21" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -2999,7 +3011,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -3082,16 +3094,16 @@
         <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D22" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E22" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F22" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3106,7 +3118,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -3178,7 +3190,7 @@
         <v>0</v>
       </c>
       <c r="AI22" s="3">
-        <v>46078.6875</v>
+        <v>46078.66666666666</v>
       </c>
     </row>
     <row r="23" spans="1:35">
@@ -3186,19 +3198,19 @@
         <v>46078</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D23" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E23" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F23" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3213,7 +3225,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -3293,19 +3305,19 @@
         <v>46078</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C24" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D24" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F24" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3320,7 +3332,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -3403,16 +3415,16 @@
         <v>46</v>
       </c>
       <c r="C25" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D25" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E25" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F25" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3427,16 +3439,16 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L25">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M25">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N25">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O25">
         <v>0</v>
@@ -3475,10 +3487,10 @@
         <v>0</v>
       </c>
       <c r="AA25">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB25">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC25">
         <v>0</v>
@@ -3499,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="AI25" s="3">
-        <v>46078.69791666666</v>
+        <v>46078.6875</v>
       </c>
     </row>
     <row r="26" spans="1:35">
@@ -3507,19 +3519,19 @@
         <v>46078</v>
       </c>
       <c r="B26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D26" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E26" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F26" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3534,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L26">
-        <v>1.24</v>
+        <v>2.41</v>
       </c>
       <c r="M26">
-        <v>6</v>
+        <v>3.34</v>
       </c>
       <c r="N26">
-        <v>10.5</v>
+        <v>2.83</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -3582,16 +3594,16 @@
         <v>0</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC26">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD26">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE26">
         <v>0</v>
@@ -3614,19 +3626,19 @@
         <v>46078</v>
       </c>
       <c r="B27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C27" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D27" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E27" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F27" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3641,16 +3653,16 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L27">
-        <v>2.41</v>
+        <v>1.24</v>
       </c>
       <c r="M27">
-        <v>3.34</v>
+        <v>6</v>
       </c>
       <c r="N27">
-        <v>2.83</v>
+        <v>10.5</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -3689,16 +3701,16 @@
         <v>0</v>
       </c>
       <c r="AA27">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB27">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE27">
         <v>0</v>
@@ -3724,16 +3736,16 @@
         <v>47</v>
       </c>
       <c r="C28" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D28" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E28" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F28" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3748,16 +3760,16 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L28">
-        <v>1.53</v>
+        <v>2.28</v>
       </c>
       <c r="M28">
-        <v>4.68</v>
+        <v>3.68</v>
       </c>
       <c r="N28">
-        <v>6.86</v>
+        <v>2.8</v>
       </c>
       <c r="O28">
         <v>0</v>
@@ -3796,10 +3808,10 @@
         <v>0</v>
       </c>
       <c r="AA28">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AB28">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC28">
         <v>0</v>
@@ -3820,7 +3832,7 @@
         <v>0</v>
       </c>
       <c r="AI28" s="3">
-        <v>46078.70833333334</v>
+        <v>46078.69791666666</v>
       </c>
     </row>
     <row r="29" spans="1:35">
@@ -3828,19 +3840,19 @@
         <v>46078</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C29" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D29" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E29" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F29" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3855,16 +3867,16 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L29">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="M29">
-        <v>3.54</v>
+        <v>4.68</v>
       </c>
       <c r="N29">
-        <v>4.08</v>
+        <v>6.86</v>
       </c>
       <c r="O29">
         <v>0</v>
@@ -3903,10 +3915,10 @@
         <v>0</v>
       </c>
       <c r="AA29">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AB29">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC29">
         <v>0</v>
@@ -3935,19 +3947,19 @@
         <v>46078</v>
       </c>
       <c r="B30" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D30" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E30" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F30" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -3962,7 +3974,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L30">
         <v>1.33</v>
@@ -4042,19 +4054,19 @@
         <v>46078</v>
       </c>
       <c r="B31" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C31" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D31" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E31" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F31" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -4069,7 +4081,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L31">
         <v>1.63</v>
@@ -4152,16 +4164,16 @@
         <v>48</v>
       </c>
       <c r="C32" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E32" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F32" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -4176,16 +4188,16 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L32">
-        <v>2.97</v>
+        <v>1.85</v>
       </c>
       <c r="M32">
-        <v>3.27</v>
+        <v>3.54</v>
       </c>
       <c r="N32">
-        <v>2.5</v>
+        <v>4.08</v>
       </c>
       <c r="O32">
         <v>0</v>
@@ -4224,10 +4236,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AB32">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -4248,7 +4260,7 @@
         <v>0</v>
       </c>
       <c r="AI32" s="3">
-        <v>46078.79166666666</v>
+        <v>46078.70833333334</v>
       </c>
     </row>
     <row r="33" spans="1:35">
@@ -4256,19 +4268,19 @@
         <v>46078</v>
       </c>
       <c r="B33" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C33" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D33" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F33" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -4283,16 +4295,16 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L33">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M33">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N33">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -4331,10 +4343,10 @@
         <v>0</v>
       </c>
       <c r="AA33">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB33">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC33">
         <v>0</v>
@@ -4363,19 +4375,19 @@
         <v>46078</v>
       </c>
       <c r="B34" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C34" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D34" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E34" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F34" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4390,16 +4402,16 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O34">
         <v>0</v>
@@ -4438,10 +4450,10 @@
         <v>0</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC34">
         <v>0</v>
@@ -4473,16 +4485,16 @@
         <v>49</v>
       </c>
       <c r="C35" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D35" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E35" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F35" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4497,16 +4509,16 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L35">
-        <v>1.92</v>
+        <v>2.97</v>
       </c>
       <c r="M35">
-        <v>3.6</v>
+        <v>3.27</v>
       </c>
       <c r="N35">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="O35">
         <v>0</v>
@@ -4545,10 +4557,10 @@
         <v>0</v>
       </c>
       <c r="AA35">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AB35">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="AC35">
         <v>0</v>
@@ -4569,7 +4581,7 @@
         <v>0</v>
       </c>
       <c r="AI35" s="3">
-        <v>46078.83333333334</v>
+        <v>46078.79166666666</v>
       </c>
     </row>
     <row r="36" spans="1:35">
@@ -4580,16 +4592,16 @@
         <v>50</v>
       </c>
       <c r="C36" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D36" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E36" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F36" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -4604,16 +4616,16 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O36">
         <v>0</v>
@@ -4652,10 +4664,10 @@
         <v>0</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC36">
         <v>0</v>
@@ -4676,7 +4688,7 @@
         <v>0</v>
       </c>
       <c r="AI36" s="3">
-        <v>46078.875</v>
+        <v>46078.83333333334</v>
       </c>
     </row>
     <row r="37" spans="1:35">
@@ -4684,19 +4696,19 @@
         <v>46078</v>
       </c>
       <c r="B37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C37" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D37" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F37" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -4711,7 +4723,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -4794,16 +4806,16 @@
         <v>51</v>
       </c>
       <c r="C38" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D38" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E38" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F38" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -4818,16 +4830,16 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L38">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M38">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="N38">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="O38">
         <v>0</v>
@@ -4866,10 +4878,10 @@
         <v>0</v>
       </c>
       <c r="AA38">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB38">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC38">
         <v>0</v>
@@ -4890,7 +4902,7 @@
         <v>0</v>
       </c>
       <c r="AI38" s="3">
-        <v>46078.89583333334</v>
+        <v>46078.875</v>
       </c>
     </row>
     <row r="39" spans="1:35">
@@ -4898,19 +4910,19 @@
         <v>46078</v>
       </c>
       <c r="B39" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C39" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D39" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E39" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F39" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -4925,78 +4937,185 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L39">
+        <v>1.71</v>
+      </c>
+      <c r="M39">
+        <v>3.79</v>
+      </c>
+      <c r="N39">
+        <v>5.14</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>0</v>
+      </c>
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <v>0</v>
+      </c>
+      <c r="U39">
+        <v>0</v>
+      </c>
+      <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <v>0</v>
+      </c>
+      <c r="X39">
+        <v>0</v>
+      </c>
+      <c r="Y39">
+        <v>0</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+      <c r="AA39">
+        <v>1.95</v>
+      </c>
+      <c r="AB39">
+        <v>1.73</v>
+      </c>
+      <c r="AC39">
+        <v>0</v>
+      </c>
+      <c r="AD39">
+        <v>0</v>
+      </c>
+      <c r="AE39">
+        <v>0</v>
+      </c>
+      <c r="AF39">
+        <v>0</v>
+      </c>
+      <c r="AG39">
+        <v>0</v>
+      </c>
+      <c r="AH39">
+        <v>0</v>
+      </c>
+      <c r="AI39" s="3">
+        <v>46078.89583333334</v>
+      </c>
+    </row>
+    <row r="40" spans="1:35">
+      <c r="A40" s="2">
+        <v>46078</v>
+      </c>
+      <c r="B40" t="s">
+        <v>52</v>
+      </c>
+      <c r="C40" t="s">
+        <v>69</v>
+      </c>
+      <c r="D40" t="s">
+        <v>72</v>
+      </c>
+      <c r="E40" t="s">
+        <v>111</v>
+      </c>
+      <c r="F40" t="s">
+        <v>150</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40" t="s">
+        <v>151</v>
+      </c>
+      <c r="L40">
         <v>2.2</v>
       </c>
-      <c r="M39">
+      <c r="M40">
         <v>3.44</v>
       </c>
-      <c r="N39">
+      <c r="N40">
         <v>3.37</v>
       </c>
-      <c r="O39">
-        <v>0</v>
-      </c>
-      <c r="P39">
-        <v>0</v>
-      </c>
-      <c r="Q39">
-        <v>0</v>
-      </c>
-      <c r="R39">
-        <v>0</v>
-      </c>
-      <c r="S39">
-        <v>0</v>
-      </c>
-      <c r="T39">
-        <v>0</v>
-      </c>
-      <c r="U39">
-        <v>0</v>
-      </c>
-      <c r="V39">
-        <v>0</v>
-      </c>
-      <c r="W39">
-        <v>0</v>
-      </c>
-      <c r="X39">
-        <v>0</v>
-      </c>
-      <c r="Y39">
-        <v>0</v>
-      </c>
-      <c r="Z39">
-        <v>0</v>
-      </c>
-      <c r="AA39">
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>0</v>
+      </c>
+      <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40">
+        <v>0</v>
+      </c>
+      <c r="T40">
+        <v>0</v>
+      </c>
+      <c r="U40">
+        <v>0</v>
+      </c>
+      <c r="V40">
+        <v>0</v>
+      </c>
+      <c r="W40">
+        <v>0</v>
+      </c>
+      <c r="X40">
+        <v>0</v>
+      </c>
+      <c r="Y40">
+        <v>0</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+      <c r="AA40">
         <v>1.98</v>
       </c>
-      <c r="AB39">
+      <c r="AB40">
         <v>1.71</v>
       </c>
-      <c r="AC39">
-        <v>0</v>
-      </c>
-      <c r="AD39">
-        <v>0</v>
-      </c>
-      <c r="AE39">
-        <v>0</v>
-      </c>
-      <c r="AF39">
-        <v>0</v>
-      </c>
-      <c r="AG39">
-        <v>0</v>
-      </c>
-      <c r="AH39">
-        <v>0</v>
-      </c>
-      <c r="AI39" s="3">
+      <c r="AC40">
+        <v>0</v>
+      </c>
+      <c r="AD40">
+        <v>0</v>
+      </c>
+      <c r="AE40">
+        <v>0</v>
+      </c>
+      <c r="AF40">
+        <v>0</v>
+      </c>
+      <c r="AG40">
+        <v>0</v>
+      </c>
+      <c r="AH40">
+        <v>0</v>
+      </c>
+      <c r="AI40" s="3">
         <v>46078.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.1</v>
+        <v>2.48</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="N16" t="n">
-        <v>2.2</v>
+        <v>3.07</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2364,16 +2364,16 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.37</v>
+        <v>3.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="M17" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>3.07</v>
+        <v>2.69</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.93</v>
+        <v>3.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.5</v>
+        <v>1.89</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.28</v>
+        <v>1.87</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46078.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2559,77 +2559,77 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="N18" t="n">
-        <v>2.69</v>
+        <v>2.2</v>
       </c>
       <c r="O18" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.89</v>
+        <v>2.37</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.87</v>
+        <v>1.53</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46078.625</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="M27" t="n">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="N27" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.93</v>
+        <v>1.55</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.28</v>
+        <v>2.41</v>
       </c>
       <c r="M29" t="n">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="N29" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="M30" t="n">
-        <v>3.54</v>
+        <v>4.68</v>
       </c>
       <c r="N30" t="n">
-        <v>4.08</v>
+        <v>6.86</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="M31" t="n">
-        <v>4.58</v>
+        <v>6.14</v>
       </c>
       <c r="N31" t="n">
-        <v>5.49</v>
+        <v>9.85</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="M32" t="n">
-        <v>4.68</v>
+        <v>3.54</v>
       </c>
       <c r="N32" t="n">
-        <v>6.86</v>
+        <v>4.08</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="M33" t="n">
-        <v>6.14</v>
+        <v>4.58</v>
       </c>
       <c r="N33" t="n">
-        <v>9.85</v>
+        <v>5.49</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.97</v>
+        <v>2.17</v>
       </c>
       <c r="M34" t="n">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
       <c r="N34" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.17</v>
+        <v>2.97</v>
       </c>
       <c r="M36" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="N36" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="M40" t="n">
-        <v>3.44</v>
+        <v>3.79</v>
       </c>
       <c r="N40" t="n">
-        <v>3.37</v>
+        <v>5.14</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,55 +5300,55 @@
         </is>
       </c>
       <c r="L41" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="N41" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB41" t="n">
         <v>1.71</v>
-      </c>
-      <c r="M41" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="N41" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" t="n">
-        <v>0</v>
-      </c>
-      <c r="W41" t="n">
-        <v>0</v>
-      </c>
-      <c r="X41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.73</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.48</v>
+        <v>3.1</v>
       </c>
       <c r="M16" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="N16" t="n">
-        <v>3.07</v>
+        <v>2.2</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2364,16 +2364,16 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.5</v>
+        <v>2.37</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.1</v>
+        <v>2.48</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="N18" t="n">
-        <v>2.2</v>
+        <v>3.07</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2602,16 +2602,16 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.37</v>
+        <v>3.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="M30" t="n">
-        <v>4.68</v>
+        <v>6.14</v>
       </c>
       <c r="N30" t="n">
-        <v>6.86</v>
+        <v>9.85</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="M31" t="n">
-        <v>6.14</v>
+        <v>4.58</v>
       </c>
       <c r="N31" t="n">
-        <v>9.85</v>
+        <v>5.49</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="M33" t="n">
-        <v>4.58</v>
+        <v>4.68</v>
       </c>
       <c r="N33" t="n">
-        <v>5.49</v>
+        <v>6.86</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,7 +4393,7 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AB33" t="n">
         <v>2.15</v>
@@ -4431,22 +4431,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,22 +4550,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,55 +5181,55 @@
         </is>
       </c>
       <c r="L40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="N40" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB40" t="n">
         <v>1.71</v>
-      </c>
-      <c r="M40" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="N40" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.73</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="M41" t="n">
-        <v>3.44</v>
+        <v>3.79</v>
       </c>
       <c r="N41" t="n">
-        <v>3.37</v>
+        <v>5.14</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="N17" t="n">
-        <v>2.69</v>
+        <v>3.07</v>
       </c>
       <c r="O17" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.4</v>
+        <v>1.93</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.89</v>
+        <v>3.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.87</v>
+        <v>1.28</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46078.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="M18" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>3.07</v>
+        <v>2.69</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.93</v>
+        <v>3.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.5</v>
+        <v>1.89</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.28</v>
+        <v>1.87</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46078.625</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.28</v>
+        <v>2.41</v>
       </c>
       <c r="M27" t="n">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="N27" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.24</v>
+        <v>2.28</v>
       </c>
       <c r="M28" t="n">
-        <v>6</v>
+        <v>3.68</v>
       </c>
       <c r="N28" t="n">
-        <v>10.5</v>
+        <v>2.8</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.41</v>
+        <v>1.24</v>
       </c>
       <c r="M29" t="n">
-        <v>3.34</v>
+        <v>6</v>
       </c>
       <c r="N29" t="n">
-        <v>2.83</v>
+        <v>10.5</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.33</v>
+        <v>1.85</v>
       </c>
       <c r="M30" t="n">
-        <v>6.14</v>
+        <v>3.54</v>
       </c>
       <c r="N30" t="n">
-        <v>9.85</v>
+        <v>4.08</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="M31" t="n">
-        <v>4.58</v>
+        <v>4.68</v>
       </c>
       <c r="N31" t="n">
-        <v>5.49</v>
+        <v>6.86</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,7 +4155,7 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AB31" t="n">
         <v>2.15</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="M32" t="n">
-        <v>3.54</v>
+        <v>4.58</v>
       </c>
       <c r="N32" t="n">
-        <v>4.08</v>
+        <v>5.49</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="M33" t="n">
-        <v>4.68</v>
+        <v>6.14</v>
       </c>
       <c r="N33" t="n">
-        <v>6.86</v>
+        <v>9.85</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4431,22 +4431,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.17</v>
+        <v>2.97</v>
       </c>
       <c r="M35" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="N35" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>2.2</v>
+        <v>2.69</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.37</v>
+        <v>1.89</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46078.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="N18" t="n">
-        <v>2.69</v>
+        <v>2.2</v>
       </c>
       <c r="O18" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.89</v>
+        <v>2.37</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.87</v>
+        <v>1.53</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46078.625</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="M27" t="n">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="N27" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.93</v>
+        <v>1.55</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.28</v>
+        <v>2.41</v>
       </c>
       <c r="M28" t="n">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="N28" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.85</v>
+        <v>1.33</v>
       </c>
       <c r="M30" t="n">
-        <v>3.54</v>
+        <v>6.14</v>
       </c>
       <c r="N30" t="n">
-        <v>4.08</v>
+        <v>9.85</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="M31" t="n">
-        <v>4.68</v>
+        <v>4.58</v>
       </c>
       <c r="N31" t="n">
-        <v>6.86</v>
+        <v>5.49</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,7 +4155,7 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AB31" t="n">
         <v>2.15</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="M32" t="n">
-        <v>4.58</v>
+        <v>3.54</v>
       </c>
       <c r="N32" t="n">
-        <v>5.49</v>
+        <v>4.08</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="M33" t="n">
-        <v>6.14</v>
+        <v>4.68</v>
       </c>
       <c r="N33" t="n">
-        <v>9.85</v>
+        <v>6.86</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4431,22 +4431,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.97</v>
+        <v>2.17</v>
       </c>
       <c r="M35" t="n">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
       <c r="N35" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="N16" t="n">
-        <v>2.69</v>
+        <v>3.07</v>
       </c>
       <c r="O16" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.4</v>
+        <v>1.93</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.89</v>
+        <v>3.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.87</v>
+        <v>1.28</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46078.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="M17" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>3.07</v>
+        <v>2.69</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.93</v>
+        <v>3.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.5</v>
+        <v>1.89</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.28</v>
+        <v>1.87</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46078.625</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="M30" t="n">
-        <v>6.14</v>
+        <v>4.58</v>
       </c>
       <c r="N30" t="n">
-        <v>9.85</v>
+        <v>5.49</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="M31" t="n">
-        <v>4.58</v>
+        <v>4.68</v>
       </c>
       <c r="N31" t="n">
-        <v>5.49</v>
+        <v>6.86</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,7 +4155,7 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AB31" t="n">
         <v>2.15</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.85</v>
+        <v>1.33</v>
       </c>
       <c r="M32" t="n">
-        <v>3.54</v>
+        <v>6.14</v>
       </c>
       <c r="N32" t="n">
-        <v>4.08</v>
+        <v>9.85</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="M33" t="n">
-        <v>4.68</v>
+        <v>3.54</v>
       </c>
       <c r="N33" t="n">
-        <v>6.86</v>
+        <v>4.08</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,22 +4431,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,22 +4550,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G39" t="n">

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI41"/>
+  <dimension ref="A1:AI40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1442,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>46078.41666666666</v>
+        <v>46078.4375</v>
       </c>
     </row>
     <row r="9">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1561,7 +1561,7 @@
         <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>46078.41666666666</v>
+        <v>46078.4375</v>
       </c>
     </row>
     <row r="10">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>46078.41666666666</v>
+        <v>46078.5</v>
       </c>
     </row>
     <row r="11">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>46078.4375</v>
+        <v>46078.5</v>
       </c>
     </row>
     <row r="12">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
-        <v>2.69</v>
+        <v>2.2</v>
       </c>
       <c r="O17" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.89</v>
+        <v>2.37</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.87</v>
+        <v>1.53</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46078.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>2.2</v>
+        <v>2.69</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.37</v>
+        <v>1.89</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46078.625</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="M30" t="n">
-        <v>4.58</v>
+        <v>4.68</v>
       </c>
       <c r="N30" t="n">
-        <v>5.49</v>
+        <v>6.86</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,7 +4036,7 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AB30" t="n">
         <v>2.15</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="M31" t="n">
-        <v>4.68</v>
+        <v>3.54</v>
       </c>
       <c r="N31" t="n">
-        <v>6.86</v>
+        <v>4.08</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="M32" t="n">
-        <v>6.14</v>
+        <v>4.58</v>
       </c>
       <c r="N32" t="n">
-        <v>9.85</v>
+        <v>5.49</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.85</v>
+        <v>1.33</v>
       </c>
       <c r="M33" t="n">
-        <v>3.54</v>
+        <v>6.14</v>
       </c>
       <c r="N33" t="n">
-        <v>4.08</v>
+        <v>9.85</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4550,22 +4550,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.92</v>
+        <v>2.68</v>
       </c>
       <c r="M37" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="N37" t="n">
-        <v>4.1</v>
+        <v>2.85</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
-        <v>46078.83333333334</v>
+        <v>46078.8125</v>
       </c>
     </row>
     <row r="38">
@@ -4902,27 +4902,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="AI38" s="3" t="n">
-        <v>46078.875</v>
+        <v>46078.83333333334</v>
       </c>
     </row>
     <row r="39">
@@ -5021,27 +5021,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5131,7 +5131,7 @@
         <v>0</v>
       </c>
       <c r="AI39" s="3" t="n">
-        <v>46078.875</v>
+        <v>46078.89583333334</v>
       </c>
     </row>
     <row r="40">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="M40" t="n">
-        <v>3.44</v>
+        <v>3.79</v>
       </c>
       <c r="N40" t="n">
-        <v>3.37</v>
+        <v>5.14</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5250,125 +5250,6 @@
         <v>0</v>
       </c>
       <c r="AI40" s="3" t="n">
-        <v>46078.89583333334</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>46078</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Palmeiras</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Fluminense</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L41" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="M41" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="N41" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" t="n">
-        <v>0</v>
-      </c>
-      <c r="W41" t="n">
-        <v>0</v>
-      </c>
-      <c r="X41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI41" s="3" t="n">
         <v>46078.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.56</v>
+        <v>2.44</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>2.72</v>
       </c>
       <c r="N26" t="n">
-        <v>6.45</v>
+        <v>3.11</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.28</v>
+        <v>2.41</v>
       </c>
       <c r="M27" t="n">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="N27" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.41</v>
+        <v>1.24</v>
       </c>
       <c r="M28" t="n">
-        <v>3.34</v>
+        <v>6</v>
       </c>
       <c r="N28" t="n">
-        <v>2.83</v>
+        <v>10.5</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.24</v>
+        <v>2.28</v>
       </c>
       <c r="M29" t="n">
-        <v>6</v>
+        <v>3.68</v>
       </c>
       <c r="N29" t="n">
-        <v>10.5</v>
+        <v>2.8</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="M30" t="n">
-        <v>4.68</v>
+        <v>6.14</v>
       </c>
       <c r="N30" t="n">
-        <v>6.86</v>
+        <v>9.85</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="M32" t="n">
-        <v>4.58</v>
+        <v>4.68</v>
       </c>
       <c r="N32" t="n">
-        <v>5.49</v>
+        <v>6.86</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,7 +4274,7 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AB32" t="n">
         <v>2.15</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="M33" t="n">
-        <v>6.14</v>
+        <v>4.58</v>
       </c>
       <c r="N33" t="n">
-        <v>9.85</v>
+        <v>5.49</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="M39" t="n">
-        <v>3.44</v>
+        <v>3.79</v>
       </c>
       <c r="N39" t="n">
-        <v>3.37</v>
+        <v>5.14</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,55 +5181,55 @@
         </is>
       </c>
       <c r="L40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="N40" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB40" t="n">
         <v>1.71</v>
-      </c>
-      <c r="M40" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="N40" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.73</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="M16" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>3.07</v>
+        <v>2.69</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.93</v>
+        <v>3.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.5</v>
+        <v>1.89</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.28</v>
+        <v>1.87</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46078.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="N18" t="n">
-        <v>2.69</v>
+        <v>3.07</v>
       </c>
       <c r="O18" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.4</v>
+        <v>1.93</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.89</v>
+        <v>3.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.87</v>
+        <v>1.28</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46078.625</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.41</v>
+        <v>1.24</v>
       </c>
       <c r="M27" t="n">
-        <v>3.34</v>
+        <v>6</v>
       </c>
       <c r="N27" t="n">
-        <v>2.83</v>
+        <v>10.5</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.24</v>
+        <v>2.41</v>
       </c>
       <c r="M28" t="n">
-        <v>6</v>
+        <v>3.34</v>
       </c>
       <c r="N28" t="n">
-        <v>10.5</v>
+        <v>2.83</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="M30" t="n">
-        <v>6.14</v>
+        <v>4.58</v>
       </c>
       <c r="N30" t="n">
-        <v>9.85</v>
+        <v>5.49</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.85</v>
+        <v>1.33</v>
       </c>
       <c r="M31" t="n">
-        <v>3.54</v>
+        <v>6.14</v>
       </c>
       <c r="N31" t="n">
-        <v>4.08</v>
+        <v>9.85</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="M33" t="n">
-        <v>4.58</v>
+        <v>3.54</v>
       </c>
       <c r="N33" t="n">
-        <v>5.49</v>
+        <v>4.08</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.17</v>
+        <v>2.97</v>
       </c>
       <c r="M34" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="N34" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.97</v>
+        <v>2.17</v>
       </c>
       <c r="M35" t="n">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
       <c r="N35" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="N16" t="n">
-        <v>2.69</v>
+        <v>3.07</v>
       </c>
       <c r="O16" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.4</v>
+        <v>1.93</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.89</v>
+        <v>3.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.87</v>
+        <v>1.28</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46078.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="M18" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>3.07</v>
+        <v>2.69</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.93</v>
+        <v>3.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.5</v>
+        <v>1.89</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.28</v>
+        <v>1.87</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46078.625</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.24</v>
+        <v>2.28</v>
       </c>
       <c r="M27" t="n">
-        <v>6</v>
+        <v>3.68</v>
       </c>
       <c r="N27" t="n">
-        <v>10.5</v>
+        <v>2.8</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.28</v>
+        <v>1.24</v>
       </c>
       <c r="M29" t="n">
-        <v>3.68</v>
+        <v>6</v>
       </c>
       <c r="N29" t="n">
-        <v>2.8</v>
+        <v>10.5</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="M30" t="n">
-        <v>4.58</v>
+        <v>4.68</v>
       </c>
       <c r="N30" t="n">
-        <v>5.49</v>
+        <v>6.86</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,7 +4036,7 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AB30" t="n">
         <v>2.15</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="M31" t="n">
-        <v>6.14</v>
+        <v>4.58</v>
       </c>
       <c r="N31" t="n">
-        <v>9.85</v>
+        <v>5.49</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="M32" t="n">
-        <v>4.68</v>
+        <v>6.14</v>
       </c>
       <c r="N32" t="n">
-        <v>6.86</v>
+        <v>9.85</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.97</v>
+        <v>2.17</v>
       </c>
       <c r="M34" t="n">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
       <c r="N34" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.17</v>
+        <v>2.97</v>
       </c>
       <c r="M35" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="N35" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,55 +5062,55 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="N39" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB39" t="n">
         <v>1.71</v>
-      </c>
-      <c r="M39" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="N39" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.73</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="M40" t="n">
-        <v>3.44</v>
+        <v>3.79</v>
       </c>
       <c r="N40" t="n">
-        <v>3.37</v>
+        <v>5.14</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.28</v>
+        <v>1.24</v>
       </c>
       <c r="M27" t="n">
-        <v>3.68</v>
+        <v>6</v>
       </c>
       <c r="N27" t="n">
-        <v>2.8</v>
+        <v>10.5</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="M28" t="n">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="N28" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.93</v>
+        <v>1.55</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.24</v>
+        <v>2.41</v>
       </c>
       <c r="M29" t="n">
-        <v>6</v>
+        <v>3.34</v>
       </c>
       <c r="N29" t="n">
-        <v>10.5</v>
+        <v>2.83</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="M30" t="n">
-        <v>4.68</v>
+        <v>4.58</v>
       </c>
       <c r="N30" t="n">
-        <v>6.86</v>
+        <v>5.49</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,7 +4036,7 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AB30" t="n">
         <v>2.15</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="M31" t="n">
-        <v>4.58</v>
+        <v>4.68</v>
       </c>
       <c r="N31" t="n">
-        <v>5.49</v>
+        <v>6.86</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,7 +4155,7 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AB31" t="n">
         <v>2.15</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.33</v>
+        <v>1.85</v>
       </c>
       <c r="M32" t="n">
-        <v>6.14</v>
+        <v>3.54</v>
       </c>
       <c r="N32" t="n">
-        <v>9.85</v>
+        <v>4.08</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.85</v>
+        <v>1.33</v>
       </c>
       <c r="M33" t="n">
-        <v>3.54</v>
+        <v>6.14</v>
       </c>
       <c r="N33" t="n">
-        <v>4.08</v>
+        <v>9.85</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4431,22 +4431,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.48</v>
+        <v>3.1</v>
       </c>
       <c r="M16" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="N16" t="n">
-        <v>3.07</v>
+        <v>2.2</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2364,16 +2364,16 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.5</v>
+        <v>2.37</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.1</v>
+        <v>2.48</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="N17" t="n">
-        <v>2.2</v>
+        <v>3.07</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2483,16 +2483,16 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.37</v>
+        <v>3.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.56</v>
+        <v>2.44</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>2.72</v>
       </c>
       <c r="N24" t="n">
-        <v>6.45</v>
+        <v>3.11</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.24</v>
+        <v>2.41</v>
       </c>
       <c r="M27" t="n">
-        <v>6</v>
+        <v>3.34</v>
       </c>
       <c r="N27" t="n">
-        <v>10.5</v>
+        <v>2.83</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.28</v>
+        <v>1.24</v>
       </c>
       <c r="M28" t="n">
-        <v>3.68</v>
+        <v>6</v>
       </c>
       <c r="N28" t="n">
-        <v>2.8</v>
+        <v>10.5</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="M29" t="n">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="N29" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.93</v>
+        <v>1.55</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="M30" t="n">
-        <v>4.58</v>
+        <v>4.68</v>
       </c>
       <c r="N30" t="n">
-        <v>5.49</v>
+        <v>6.86</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,7 +4036,7 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AB30" t="n">
         <v>2.15</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="M31" t="n">
-        <v>4.68</v>
+        <v>3.54</v>
       </c>
       <c r="N31" t="n">
-        <v>6.86</v>
+        <v>4.08</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="M32" t="n">
-        <v>3.54</v>
+        <v>4.58</v>
       </c>
       <c r="N32" t="n">
-        <v>4.08</v>
+        <v>5.49</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4431,22 +4431,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.97</v>
+        <v>2.17</v>
       </c>
       <c r="M35" t="n">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
       <c r="N35" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2321,77 +2321,77 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>2.2</v>
+        <v>2.69</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.37</v>
+        <v>1.89</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46078.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.48</v>
+        <v>3.1</v>
       </c>
       <c r="M17" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
-        <v>3.07</v>
+        <v>2.2</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2483,16 +2483,16 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.5</v>
+        <v>2.37</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2559,77 +2559,77 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="N18" t="n">
-        <v>2.69</v>
+        <v>3.07</v>
       </c>
       <c r="O18" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.4</v>
+        <v>1.93</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.89</v>
+        <v>3.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.87</v>
+        <v>1.28</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46078.625</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.24</v>
+        <v>2.28</v>
       </c>
       <c r="M28" t="n">
-        <v>6</v>
+        <v>3.68</v>
       </c>
       <c r="N28" t="n">
-        <v>10.5</v>
+        <v>2.8</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.28</v>
+        <v>1.24</v>
       </c>
       <c r="M29" t="n">
-        <v>3.68</v>
+        <v>6</v>
       </c>
       <c r="N29" t="n">
-        <v>2.8</v>
+        <v>10.5</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="M30" t="n">
-        <v>4.68</v>
+        <v>4.58</v>
       </c>
       <c r="N30" t="n">
-        <v>6.86</v>
+        <v>5.49</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,7 +4036,7 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AB30" t="n">
         <v>2.15</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="M31" t="n">
-        <v>3.54</v>
+        <v>4.68</v>
       </c>
       <c r="N31" t="n">
-        <v>4.08</v>
+        <v>6.86</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="M32" t="n">
-        <v>4.58</v>
+        <v>3.54</v>
       </c>
       <c r="N32" t="n">
-        <v>5.49</v>
+        <v>4.08</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4550,22 +4550,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="M39" t="n">
-        <v>3.44</v>
+        <v>3.79</v>
       </c>
       <c r="N39" t="n">
-        <v>3.37</v>
+        <v>5.14</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,55 +5181,55 @@
         </is>
       </c>
       <c r="L40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="N40" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB40" t="n">
         <v>1.71</v>
-      </c>
-      <c r="M40" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="N40" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.73</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2321,77 +2321,77 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="N16" t="n">
-        <v>2.69</v>
+        <v>3.07</v>
       </c>
       <c r="O16" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.4</v>
+        <v>1.93</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.89</v>
+        <v>3.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.87</v>
+        <v>1.28</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46078.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2440,77 +2440,77 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>2.2</v>
+        <v>2.69</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.37</v>
+        <v>1.89</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46078.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.48</v>
+        <v>3.1</v>
       </c>
       <c r="M18" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="N18" t="n">
-        <v>3.07</v>
+        <v>2.2</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2602,16 +2602,16 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.5</v>
+        <v>2.37</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.28</v>
+        <v>1.24</v>
       </c>
       <c r="M28" t="n">
-        <v>3.68</v>
+        <v>6</v>
       </c>
       <c r="N28" t="n">
-        <v>2.8</v>
+        <v>10.5</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.24</v>
+        <v>2.28</v>
       </c>
       <c r="M29" t="n">
-        <v>6</v>
+        <v>3.68</v>
       </c>
       <c r="N29" t="n">
-        <v>10.5</v>
+        <v>2.8</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="M30" t="n">
-        <v>4.58</v>
+        <v>3.54</v>
       </c>
       <c r="N30" t="n">
-        <v>5.49</v>
+        <v>4.08</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="M31" t="n">
-        <v>4.68</v>
+        <v>6.14</v>
       </c>
       <c r="N31" t="n">
-        <v>6.86</v>
+        <v>9.85</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="M32" t="n">
-        <v>3.54</v>
+        <v>4.58</v>
       </c>
       <c r="N32" t="n">
-        <v>4.08</v>
+        <v>5.49</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="M33" t="n">
-        <v>6.14</v>
+        <v>4.68</v>
       </c>
       <c r="N33" t="n">
-        <v>9.85</v>
+        <v>6.86</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.97</v>
+        <v>2.17</v>
       </c>
       <c r="M34" t="n">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
       <c r="N34" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,22 +4550,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,55 +5062,55 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="N39" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB39" t="n">
         <v>1.71</v>
-      </c>
-      <c r="M39" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="N39" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.73</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="M40" t="n">
-        <v>3.44</v>
+        <v>3.79</v>
       </c>
       <c r="N40" t="n">
-        <v>3.37</v>
+        <v>5.14</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.48</v>
+        <v>3.1</v>
       </c>
       <c r="M16" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="N16" t="n">
-        <v>3.07</v>
+        <v>2.2</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2364,16 +2364,16 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.5</v>
+        <v>2.37</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2440,77 +2440,77 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="N17" t="n">
-        <v>2.69</v>
+        <v>3.07</v>
       </c>
       <c r="O17" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.4</v>
+        <v>1.93</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.89</v>
+        <v>3.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.87</v>
+        <v>1.28</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46078.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2559,77 +2559,77 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>2.2</v>
+        <v>2.69</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.37</v>
+        <v>1.89</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46078.625</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="M27" t="n">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="N27" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.93</v>
+        <v>1.55</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.28</v>
+        <v>2.41</v>
       </c>
       <c r="M29" t="n">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="N29" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="M31" t="n">
-        <v>6.14</v>
+        <v>4.58</v>
       </c>
       <c r="N31" t="n">
-        <v>9.85</v>
+        <v>5.49</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="M32" t="n">
-        <v>4.58</v>
+        <v>6.14</v>
       </c>
       <c r="N32" t="n">
-        <v>5.49</v>
+        <v>9.85</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4431,22 +4431,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="M39" t="n">
-        <v>3.44</v>
+        <v>3.79</v>
       </c>
       <c r="N39" t="n">
-        <v>3.37</v>
+        <v>5.14</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,55 +5181,55 @@
         </is>
       </c>
       <c r="L40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="N40" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB40" t="n">
         <v>1.71</v>
-      </c>
-      <c r="M40" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="N40" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.73</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>46078.41666666666</v>
+        <v>46078.4375</v>
       </c>
     </row>
     <row r="8">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1561,7 +1561,7 @@
         <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>46078.4375</v>
+        <v>46078.45833333334</v>
       </c>
     </row>
     <row r="10">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2321,77 +2321,77 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>2.2</v>
+        <v>2.69</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.37</v>
+        <v>1.89</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46078.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2559,77 +2559,77 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="N18" t="n">
-        <v>2.69</v>
+        <v>2.2</v>
       </c>
       <c r="O18" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.89</v>
+        <v>2.37</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.87</v>
+        <v>1.53</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46078.625</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.44</v>
+        <v>1.56</v>
       </c>
       <c r="M24" t="n">
-        <v>2.72</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>3.11</v>
+        <v>6.45</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.56</v>
+        <v>2.44</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>2.72</v>
       </c>
       <c r="N25" t="n">
-        <v>6.45</v>
+        <v>3.11</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.24</v>
+        <v>2.41</v>
       </c>
       <c r="M28" t="n">
-        <v>6</v>
+        <v>3.34</v>
       </c>
       <c r="N28" t="n">
-        <v>10.5</v>
+        <v>2.83</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.41</v>
+        <v>1.24</v>
       </c>
       <c r="M29" t="n">
-        <v>3.34</v>
+        <v>6</v>
       </c>
       <c r="N29" t="n">
-        <v>2.83</v>
+        <v>10.5</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.85</v>
+        <v>1.33</v>
       </c>
       <c r="M30" t="n">
-        <v>3.54</v>
+        <v>6.14</v>
       </c>
       <c r="N30" t="n">
-        <v>4.08</v>
+        <v>9.85</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="M32" t="n">
-        <v>6.14</v>
+        <v>4.68</v>
       </c>
       <c r="N32" t="n">
-        <v>9.85</v>
+        <v>6.86</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="M33" t="n">
-        <v>4.68</v>
+        <v>3.54</v>
       </c>
       <c r="N33" t="n">
-        <v>6.86</v>
+        <v>4.08</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,22 +4431,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,22 +4550,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,55 +5062,55 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="N39" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB39" t="n">
         <v>1.71</v>
-      </c>
-      <c r="M39" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="N39" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.73</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="M40" t="n">
-        <v>3.44</v>
+        <v>3.79</v>
       </c>
       <c r="N40" t="n">
-        <v>3.37</v>
+        <v>5.14</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.48</v>
+        <v>3.1</v>
       </c>
       <c r="M17" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
-        <v>3.07</v>
+        <v>2.2</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2483,16 +2483,16 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.5</v>
+        <v>2.37</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.1</v>
+        <v>2.48</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="N18" t="n">
-        <v>2.2</v>
+        <v>3.07</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2602,16 +2602,16 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.37</v>
+        <v>3.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.56</v>
+        <v>2.44</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>2.72</v>
       </c>
       <c r="N24" t="n">
-        <v>6.45</v>
+        <v>3.11</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.44</v>
+        <v>1.56</v>
       </c>
       <c r="M25" t="n">
-        <v>2.72</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>3.11</v>
+        <v>6.45</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.28</v>
+        <v>1.24</v>
       </c>
       <c r="M27" t="n">
-        <v>3.68</v>
+        <v>6</v>
       </c>
       <c r="N27" t="n">
-        <v>2.8</v>
+        <v>10.5</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="M28" t="n">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="N28" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.93</v>
+        <v>1.55</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.24</v>
+        <v>2.41</v>
       </c>
       <c r="M29" t="n">
-        <v>6</v>
+        <v>3.34</v>
       </c>
       <c r="N29" t="n">
-        <v>10.5</v>
+        <v>2.83</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.33</v>
+        <v>1.85</v>
       </c>
       <c r="M30" t="n">
-        <v>6.14</v>
+        <v>3.54</v>
       </c>
       <c r="N30" t="n">
-        <v>9.85</v>
+        <v>4.08</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="M31" t="n">
-        <v>4.58</v>
+        <v>6.14</v>
       </c>
       <c r="N31" t="n">
-        <v>5.49</v>
+        <v>9.85</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="M33" t="n">
-        <v>3.54</v>
+        <v>4.58</v>
       </c>
       <c r="N33" t="n">
-        <v>4.08</v>
+        <v>5.49</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.97</v>
+        <v>2.17</v>
       </c>
       <c r="M34" t="n">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
       <c r="N34" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,22 +4550,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.56</v>
+        <v>2.44</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>2.72</v>
       </c>
       <c r="N25" t="n">
-        <v>6.45</v>
+        <v>3.11</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.24</v>
+        <v>2.41</v>
       </c>
       <c r="M27" t="n">
-        <v>6</v>
+        <v>3.34</v>
       </c>
       <c r="N27" t="n">
-        <v>10.5</v>
+        <v>2.83</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.41</v>
+        <v>1.24</v>
       </c>
       <c r="M29" t="n">
-        <v>3.34</v>
+        <v>6</v>
       </c>
       <c r="N29" t="n">
-        <v>2.83</v>
+        <v>10.5</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.85</v>
+        <v>1.33</v>
       </c>
       <c r="M30" t="n">
-        <v>3.54</v>
+        <v>6.14</v>
       </c>
       <c r="N30" t="n">
-        <v>4.08</v>
+        <v>9.85</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="M31" t="n">
-        <v>6.14</v>
+        <v>4.58</v>
       </c>
       <c r="N31" t="n">
-        <v>9.85</v>
+        <v>5.49</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="M33" t="n">
-        <v>4.58</v>
+        <v>3.54</v>
       </c>
       <c r="N33" t="n">
-        <v>5.49</v>
+        <v>4.08</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,22 +4431,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="N16" t="n">
-        <v>2.69</v>
+        <v>3.07</v>
       </c>
       <c r="O16" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.4</v>
+        <v>1.93</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.89</v>
+        <v>3.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.87</v>
+        <v>1.28</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46078.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="M18" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>3.07</v>
+        <v>2.69</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.93</v>
+        <v>3.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.5</v>
+        <v>1.89</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.28</v>
+        <v>1.87</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46078.625</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="M27" t="n">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="N27" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.93</v>
+        <v>1.55</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.28</v>
+        <v>2.41</v>
       </c>
       <c r="M28" t="n">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="N28" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="M30" t="n">
-        <v>6.14</v>
+        <v>4.68</v>
       </c>
       <c r="N30" t="n">
-        <v>9.85</v>
+        <v>6.86</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="M31" t="n">
-        <v>4.58</v>
+        <v>3.54</v>
       </c>
       <c r="N31" t="n">
-        <v>5.49</v>
+        <v>4.08</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="M32" t="n">
-        <v>4.68</v>
+        <v>6.14</v>
       </c>
       <c r="N32" t="n">
-        <v>6.86</v>
+        <v>9.85</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="M33" t="n">
-        <v>3.54</v>
+        <v>4.58</v>
       </c>
       <c r="N33" t="n">
-        <v>4.08</v>
+        <v>5.49</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,22 +4431,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.97</v>
+        <v>2.17</v>
       </c>
       <c r="M35" t="n">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
       <c r="N35" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="M39" t="n">
-        <v>3.44</v>
+        <v>3.79</v>
       </c>
       <c r="N39" t="n">
-        <v>3.37</v>
+        <v>5.14</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,55 +5181,55 @@
         </is>
       </c>
       <c r="L40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="N40" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB40" t="n">
         <v>1.71</v>
-      </c>
-      <c r="M40" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="N40" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.73</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="M16" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>3.07</v>
+        <v>2.69</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.93</v>
+        <v>3.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.5</v>
+        <v>1.89</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.28</v>
+        <v>1.87</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46078.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="N18" t="n">
-        <v>2.69</v>
+        <v>3.07</v>
       </c>
       <c r="O18" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.4</v>
+        <v>1.93</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.89</v>
+        <v>3.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.87</v>
+        <v>1.28</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46078.625</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.44</v>
+        <v>1.56</v>
       </c>
       <c r="M25" t="n">
-        <v>2.72</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>3.11</v>
+        <v>6.45</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.56</v>
+        <v>2.44</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>2.72</v>
       </c>
       <c r="N26" t="n">
-        <v>6.45</v>
+        <v>3.11</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.28</v>
+        <v>2.41</v>
       </c>
       <c r="M27" t="n">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="N27" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="M28" t="n">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="N28" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.93</v>
+        <v>1.55</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="M30" t="n">
-        <v>4.68</v>
+        <v>6.14</v>
       </c>
       <c r="N30" t="n">
-        <v>6.86</v>
+        <v>9.85</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="M32" t="n">
-        <v>6.14</v>
+        <v>4.58</v>
       </c>
       <c r="N32" t="n">
-        <v>9.85</v>
+        <v>5.49</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="M33" t="n">
-        <v>4.58</v>
+        <v>4.68</v>
       </c>
       <c r="N33" t="n">
-        <v>5.49</v>
+        <v>6.86</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,7 +4393,7 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AB33" t="n">
         <v>2.15</v>
@@ -4431,22 +4431,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46078.4375</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2215,40 +2215,40 @@
         <v>3.41</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA15" t="n">
         <v>1.79</v>
@@ -2257,22 +2257,22 @@
         <v>1.91</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46078.61458333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46078.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46078.6875</v>
@@ -3524,64 +3524,64 @@
         <v>3.11</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46078.6875</v>
@@ -3643,40 +3643,40 @@
         <v>2.83</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA27" t="n">
         <v>1.93</v>
@@ -3685,22 +3685,22 @@
         <v>1.77</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46078.69791666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.28</v>
+        <v>1.24</v>
       </c>
       <c r="M28" t="n">
-        <v>3.68</v>
+        <v>6</v>
       </c>
       <c r="N28" t="n">
-        <v>2.8</v>
+        <v>10.5</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.24</v>
+        <v>2.28</v>
       </c>
       <c r="M29" t="n">
-        <v>6</v>
+        <v>3.68</v>
       </c>
       <c r="N29" t="n">
-        <v>10.5</v>
+        <v>2.8</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -4000,46 +4000,46 @@
         <v>9.85</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC30" t="n">
         <v>1.87</v>
@@ -4048,16 +4048,16 @@
         <v>1.83</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="M32" t="n">
-        <v>4.58</v>
+        <v>4.68</v>
       </c>
       <c r="N32" t="n">
-        <v>5.49</v>
+        <v>6.86</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AB32" t="n">
         <v>2.15</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="M33" t="n">
-        <v>4.68</v>
+        <v>4.58</v>
       </c>
       <c r="N33" t="n">
-        <v>6.86</v>
+        <v>5.49</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AB33" t="n">
         <v>2.15</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.17</v>
+        <v>2.97</v>
       </c>
       <c r="M35" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="N35" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.97</v>
+        <v>2.17</v>
       </c>
       <c r="M36" t="n">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
       <c r="N36" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,55 +5062,55 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="N39" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB39" t="n">
         <v>1.71</v>
-      </c>
-      <c r="M39" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="N39" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.73</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="M40" t="n">
-        <v>3.44</v>
+        <v>3.79</v>
       </c>
       <c r="N40" t="n">
-        <v>3.37</v>
+        <v>5.14</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="P24" t="n">
         <v>1.95</v>
       </c>
       <c r="Q24" t="n">
-        <v>7.1</v>
+        <v>4.2</v>
       </c>
       <c r="R24" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="S24" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="T24" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U24" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V24" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X24" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.65</v>
+        <v>4.26</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46078.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O25" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="P25" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S25" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="T25" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="U25" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V25" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="W25" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.26</v>
+        <v>5.25</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46078.6875</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.44</v>
+        <v>1.56</v>
       </c>
       <c r="M26" t="n">
-        <v>2.72</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>3.11</v>
+        <v>6.45</v>
       </c>
       <c r="O26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T26" t="n">
         <v>3.4</v>
       </c>
-      <c r="P26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.6</v>
-      </c>
       <c r="U26" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W26" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X26" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>5.25</v>
+        <v>4.65</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46078.6875</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.24</v>
+        <v>2.28</v>
       </c>
       <c r="M28" t="n">
-        <v>6</v>
+        <v>3.68</v>
       </c>
       <c r="N28" t="n">
-        <v>10.5</v>
+        <v>2.8</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.28</v>
+        <v>1.24</v>
       </c>
       <c r="M29" t="n">
-        <v>3.68</v>
+        <v>6</v>
       </c>
       <c r="N29" t="n">
-        <v>2.8</v>
+        <v>10.5</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="M30" t="n">
-        <v>6.14</v>
+        <v>4.58</v>
       </c>
       <c r="N30" t="n">
-        <v>9.85</v>
+        <v>5.49</v>
       </c>
       <c r="O30" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="P30" t="n">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="Q30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R30" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W30" t="n">
         <v>1.17</v>
       </c>
-      <c r="S30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V30" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.25</v>
-      </c>
       <c r="X30" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Z30" t="n">
-        <v>7.25</v>
+        <v>5.3</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.29</v>
+        <v>1.63</v>
       </c>
       <c r="AB30" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AH30" t="n">
-        <v>3.7</v>
+        <v>2.45</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="M31" t="n">
-        <v>3.54</v>
+        <v>4.68</v>
       </c>
       <c r="N31" t="n">
-        <v>4.08</v>
+        <v>6.86</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="M32" t="n">
-        <v>4.68</v>
+        <v>6.14</v>
       </c>
       <c r="N32" t="n">
-        <v>6.86</v>
+        <v>9.85</v>
       </c>
       <c r="O32" t="n">
-        <v>1.93</v>
+        <v>1.58</v>
       </c>
       <c r="P32" t="n">
-        <v>2.62</v>
+        <v>3.25</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="R32" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="S32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V32" t="n">
         <v>3.6</v>
       </c>
-      <c r="T32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V32" t="n">
-        <v>4.5</v>
-      </c>
       <c r="W32" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X32" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.25</v>
+        <v>7.25</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.61</v>
+        <v>1.29</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.81</v>
+        <v>3.7</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="M33" t="n">
-        <v>4.58</v>
+        <v>3.54</v>
       </c>
       <c r="N33" t="n">
-        <v>5.49</v>
+        <v>4.08</v>
       </c>
       <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
         <v>1.95</v>
       </c>
-      <c r="P33" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>5</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V33" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AB33" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46078.70833333334</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="M39" t="n">
-        <v>3.44</v>
+        <v>3.79</v>
       </c>
       <c r="N39" t="n">
-        <v>3.37</v>
+        <v>5.14</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,55 +5181,55 @@
         </is>
       </c>
       <c r="L40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="N40" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB40" t="n">
         <v>1.71</v>
-      </c>
-      <c r="M40" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="N40" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.73</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46078.4375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46078.4375</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="N16" t="n">
-        <v>2.69</v>
+        <v>2.2</v>
       </c>
       <c r="O16" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.89</v>
+        <v>2.37</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.87</v>
+        <v>1.53</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46078.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>2.2</v>
+        <v>2.69</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.37</v>
+        <v>1.89</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46078.625</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O24" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="P24" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S24" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="T24" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="U24" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V24" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="W24" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.26</v>
+        <v>5.25</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46078.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="P25" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="R25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB25" t="n">
         <v>1.57</v>
       </c>
-      <c r="S25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V25" t="n">
-        <v>10</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AC25" t="n">
-        <v>5.25</v>
+        <v>4.26</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AF25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.62</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46078.6875</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.28</v>
+        <v>1.24</v>
       </c>
       <c r="M28" t="n">
-        <v>3.68</v>
+        <v>6</v>
       </c>
       <c r="N28" t="n">
-        <v>2.8</v>
+        <v>10.5</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.24</v>
+        <v>2.28</v>
       </c>
       <c r="M29" t="n">
-        <v>6</v>
+        <v>3.68</v>
       </c>
       <c r="N29" t="n">
-        <v>10.5</v>
+        <v>2.8</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="M30" t="n">
-        <v>4.58</v>
+        <v>6.14</v>
       </c>
       <c r="N30" t="n">
-        <v>5.49</v>
+        <v>9.85</v>
       </c>
       <c r="O30" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="P30" t="n">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="Q30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R30" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="S30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V30" t="n">
         <v>3.6</v>
       </c>
-      <c r="T30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V30" t="n">
-        <v>4.6</v>
-      </c>
       <c r="W30" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X30" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Z30" t="n">
-        <v>5.3</v>
+        <v>7.25</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.63</v>
+        <v>1.29</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.45</v>
+        <v>3.7</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,22 +4110,22 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="M31" t="n">
-        <v>4.68</v>
+        <v>4.58</v>
       </c>
       <c r="N31" t="n">
-        <v>6.86</v>
+        <v>5.49</v>
       </c>
       <c r="O31" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="P31" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="R31" t="n">
         <v>1.23</v>
@@ -4137,10 +4137,10 @@
         <v>2.1</v>
       </c>
       <c r="U31" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="V31" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="W31" t="n">
         <v>1.17</v>
@@ -4149,13 +4149,13 @@
         <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AB31" t="n">
         <v>2.15</v>
@@ -4167,16 +4167,16 @@
         <v>1.63</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AG31" t="n">
         <v>1.18</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.81</v>
+        <v>2.45</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="M32" t="n">
-        <v>6.14</v>
+        <v>4.68</v>
       </c>
       <c r="N32" t="n">
-        <v>9.85</v>
+        <v>6.86</v>
       </c>
       <c r="O32" t="n">
-        <v>1.58</v>
+        <v>1.93</v>
       </c>
       <c r="P32" t="n">
-        <v>3.25</v>
+        <v>2.62</v>
       </c>
       <c r="Q32" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="R32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W32" t="n">
         <v>1.17</v>
       </c>
-      <c r="S32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T32" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.25</v>
-      </c>
       <c r="X32" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z32" t="n">
-        <v>7.25</v>
+        <v>5.25</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.29</v>
+        <v>1.61</v>
       </c>
       <c r="AB32" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AH32" t="n">
-        <v>3.7</v>
+        <v>2.81</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4431,22 +4431,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4595,40 +4595,40 @@
         <v>2.5</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA35" t="n">
         <v>2.2</v>
@@ -4637,22 +4637,22 @@
         <v>1.58</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4833,40 +4833,40 @@
         <v>2.85</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA37" t="n">
         <v>2.3</v>
@@ -4875,22 +4875,22 @@
         <v>1.53</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46078.8125</v>
@@ -4952,40 +4952,40 @@
         <v>4.1</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA38" t="n">
         <v>2</v>
@@ -4994,22 +4994,22 @@
         <v>1.71</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46078.83333333334</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="N39" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V39" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB39" t="n">
         <v>1.71</v>
       </c>
-      <c r="M39" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="N39" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB39" t="n">
+      <c r="AC39" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE39" t="n">
         <v>1.73</v>
       </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0</v>
-      </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46078.89583333334</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="M40" t="n">
-        <v>3.44</v>
+        <v>3.79</v>
       </c>
       <c r="N40" t="n">
-        <v>3.37</v>
+        <v>5.14</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46078.89583333334</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.1</v>
+        <v>2.48</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="N16" t="n">
-        <v>2.2</v>
+        <v>3.07</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2364,16 +2364,16 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.37</v>
+        <v>3.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
-        <v>2.69</v>
+        <v>2.2</v>
       </c>
       <c r="O17" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.89</v>
+        <v>2.37</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.87</v>
+        <v>1.53</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46078.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="M18" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>3.07</v>
+        <v>2.69</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.93</v>
+        <v>3.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.5</v>
+        <v>1.89</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.28</v>
+        <v>1.87</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46078.625</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="O25" t="n">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="P25" t="n">
         <v>1.95</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.2</v>
+        <v>7.1</v>
       </c>
       <c r="R25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V25" t="n">
+        <v>9</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB25" t="n">
         <v>1.5</v>
       </c>
-      <c r="S25" t="n">
+      <c r="AC25" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE25" t="n">
         <v>2.4</v>
       </c>
-      <c r="T25" t="n">
-        <v>3</v>
-      </c>
-      <c r="U25" t="n">
+      <c r="AF25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG25" t="n">
         <v>1.3</v>
       </c>
-      <c r="V25" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH25" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46078.6875</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="P26" t="n">
         <v>1.95</v>
       </c>
       <c r="Q26" t="n">
-        <v>7.1</v>
+        <v>4.2</v>
       </c>
       <c r="R26" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="S26" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="T26" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U26" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V26" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X26" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.65</v>
+        <v>4.26</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46078.6875</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="M27" t="n">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="N27" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="O27" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.93</v>
+        <v>1.55</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46078.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.28</v>
+        <v>2.41</v>
       </c>
       <c r="M29" t="n">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="N29" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S29" t="n">
         <v>2.8</v>
       </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46078.69791666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="M31" t="n">
-        <v>4.58</v>
+        <v>3.54</v>
       </c>
       <c r="N31" t="n">
-        <v>5.49</v>
+        <v>4.08</v>
       </c>
       <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
         <v>1.95</v>
       </c>
-      <c r="P31" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>5</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AB31" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,22 +4229,22 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="M32" t="n">
-        <v>4.68</v>
+        <v>4.58</v>
       </c>
       <c r="N32" t="n">
-        <v>6.86</v>
+        <v>5.49</v>
       </c>
       <c r="O32" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="P32" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="R32" t="n">
         <v>1.23</v>
@@ -4256,10 +4256,10 @@
         <v>2.1</v>
       </c>
       <c r="U32" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="V32" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="W32" t="n">
         <v>1.17</v>
@@ -4268,13 +4268,13 @@
         <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AB32" t="n">
         <v>2.15</v>
@@ -4286,16 +4286,16 @@
         <v>1.63</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AG32" t="n">
         <v>1.18</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.81</v>
+        <v>2.45</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="M33" t="n">
-        <v>3.54</v>
+        <v>4.68</v>
       </c>
       <c r="N33" t="n">
-        <v>4.08</v>
+        <v>6.86</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.17</v>
+        <v>2.97</v>
       </c>
       <c r="M34" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="N34" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="O34" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="P34" t="n">
         <v>2.05</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="R34" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S34" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T34" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V34" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG34" t="n">
         <v>1.33</v>
       </c>
-      <c r="V34" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH34" t="n">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.97</v>
+        <v>2.17</v>
       </c>
       <c r="M35" t="n">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
       <c r="N35" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="O35" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="P35" t="n">
         <v>2.05</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="R35" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S35" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T35" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U35" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V35" t="n">
-        <v>7.75</v>
+        <v>8.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X35" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46078.79166666666</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,28 +5062,28 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="M39" t="n">
-        <v>3.44</v>
+        <v>3.79</v>
       </c>
       <c r="N39" t="n">
-        <v>3.37</v>
+        <v>5.14</v>
       </c>
       <c r="O39" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="P39" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="R39" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S39" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="T39" t="n">
         <v>2.8</v>
@@ -5098,37 +5098,37 @@
         <v>1.08</v>
       </c>
       <c r="X39" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD39" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z39" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD39" t="n">
+      <c r="AE39" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG39" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE39" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH39" t="n">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46078.89583333334</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,28 +5181,28 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="M40" t="n">
-        <v>3.79</v>
+        <v>3.44</v>
       </c>
       <c r="N40" t="n">
-        <v>5.14</v>
+        <v>3.37</v>
       </c>
       <c r="O40" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="P40" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="R40" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S40" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="T40" t="n">
         <v>2.8</v>
@@ -5217,37 +5217,37 @@
         <v>1.08</v>
       </c>
       <c r="X40" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD40" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z40" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB40" t="n">
+      <c r="AE40" t="n">
         <v>1.73</v>
       </c>
-      <c r="AC40" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF40" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46078.89583333334</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI40"/>
+  <dimension ref="A1:AI41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="M16" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>3.07</v>
+        <v>2.69</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.93</v>
+        <v>3.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.5</v>
+        <v>1.89</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.28</v>
+        <v>1.87</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46078.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.1</v>
+        <v>5.93</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="N17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O17" t="n">
+        <v>5</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="T17" t="n">
         <v>2.2</v>
       </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.37</v>
+        <v>1.43</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.53</v>
+        <v>2.73</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46078.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="N18" t="n">
-        <v>2.69</v>
+        <v>3.07</v>
       </c>
       <c r="O18" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.4</v>
+        <v>1.93</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.89</v>
+        <v>3.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.87</v>
+        <v>1.28</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46078.625</v>
@@ -2641,12 +2641,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.42</v>
+        <v>3.1</v>
       </c>
       <c r="M19" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="N19" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.75</v>
+        <v>2.37</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2751,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>46078.64583333334</v>
+        <v>46078.625</v>
       </c>
     </row>
     <row r="20">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
-        <v>46078.65625</v>
+        <v>46078.64583333334</v>
       </c>
     </row>
     <row r="21">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3108,7 +3108,7 @@
         <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>46078.66666666666</v>
+        <v>46078.65625</v>
       </c>
     </row>
     <row r="23">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,76 +3277,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>46078.6875</v>
+        <v>46078.66666666666</v>
       </c>
     </row>
     <row r="25">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.56</v>
+        <v>2.44</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>2.72</v>
       </c>
       <c r="N25" t="n">
-        <v>6.45</v>
+        <v>3.11</v>
       </c>
       <c r="O25" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="P25" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Q25" t="n">
-        <v>7.1</v>
+        <v>3.75</v>
       </c>
       <c r="R25" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="S25" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="T25" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U25" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W25" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.65</v>
+        <v>5.25</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46078.6875</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="O26" t="n">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="P26" t="n">
         <v>1.95</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.2</v>
+        <v>7.1</v>
       </c>
       <c r="R26" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V26" t="n">
+        <v>9</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB26" t="n">
         <v>1.5</v>
       </c>
-      <c r="S26" t="n">
+      <c r="AC26" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE26" t="n">
         <v>2.4</v>
       </c>
-      <c r="T26" t="n">
-        <v>3</v>
-      </c>
-      <c r="U26" t="n">
+      <c r="AF26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG26" t="n">
         <v>1.3</v>
       </c>
-      <c r="V26" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH26" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46078.6875</v>
@@ -3593,12 +3593,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,76 +3634,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V27" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z27" t="n">
         <v>2.8</v>
       </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
       <c r="AA27" t="n">
-        <v>1.55</v>
+        <v>2.25</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>46078.69791666666</v>
+        <v>46078.6875</v>
       </c>
     </row>
     <row r="28">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.24</v>
+        <v>2.41</v>
       </c>
       <c r="M28" t="n">
-        <v>6</v>
+        <v>3.34</v>
       </c>
       <c r="N28" t="n">
-        <v>10.5</v>
+        <v>2.83</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.5</v>
+        <v>1.93</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.62</v>
+        <v>1.77</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.6</v>
+        <v>1.29</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46078.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="M29" t="n">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="N29" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="O29" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="P29" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R29" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S29" t="n">
-        <v>2.8</v>
+        <v>3.22</v>
       </c>
       <c r="T29" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="U29" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="V29" t="n">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="W29" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X29" t="n">
         <v>1.03</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AG29" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH29" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46078.69791666666</v>
@@ -3950,12 +3950,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,76 +3991,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="M30" t="n">
-        <v>6.14</v>
+        <v>6</v>
       </c>
       <c r="N30" t="n">
-        <v>9.85</v>
+        <v>10.5</v>
       </c>
       <c r="O30" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="P30" t="n">
-        <v>3.25</v>
+        <v>2.62</v>
       </c>
       <c r="Q30" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="R30" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="S30" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="T30" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V30" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE30" t="n">
         <v>1.85</v>
       </c>
-      <c r="U30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V30" t="n">
+      <c r="AF30" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AH30" t="n">
         <v>3.6</v>
       </c>
-      <c r="W30" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AI30" s="3" t="n">
-        <v>46078.70833333334</v>
+        <v>46078.69791666666</v>
       </c>
     </row>
     <row r="31">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="M31" t="n">
-        <v>3.54</v>
+        <v>4.68</v>
       </c>
       <c r="N31" t="n">
-        <v>4.08</v>
+        <v>6.86</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="M32" t="n">
-        <v>4.58</v>
+        <v>3.54</v>
       </c>
       <c r="N32" t="n">
-        <v>5.49</v>
+        <v>4.08</v>
       </c>
       <c r="O32" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA32" t="n">
         <v>1.95</v>
       </c>
-      <c r="P32" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>5</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AB32" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.2</v>
+        <v>3.92</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.63</v>
+        <v>1.18</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.6</v>
+        <v>2.03</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.3</v>
+        <v>1.72</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,22 +4348,22 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="M33" t="n">
-        <v>4.68</v>
+        <v>4.58</v>
       </c>
       <c r="N33" t="n">
-        <v>6.86</v>
+        <v>5.49</v>
       </c>
       <c r="O33" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="P33" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="R33" t="n">
         <v>1.23</v>
@@ -4375,10 +4375,10 @@
         <v>2.1</v>
       </c>
       <c r="U33" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="V33" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="W33" t="n">
         <v>1.17</v>
@@ -4387,13 +4387,13 @@
         <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AB33" t="n">
         <v>2.15</v>
@@ -4405,16 +4405,16 @@
         <v>1.63</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AG33" t="n">
         <v>1.18</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.81</v>
+        <v>2.45</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4426,27 +4426,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,76 +4467,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.97</v>
+        <v>1.33</v>
       </c>
       <c r="M34" t="n">
-        <v>3.27</v>
+        <v>6.14</v>
       </c>
       <c r="N34" t="n">
-        <v>2.5</v>
+        <v>9.85</v>
       </c>
       <c r="O34" t="n">
-        <v>3.5</v>
+        <v>1.58</v>
       </c>
       <c r="P34" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>6</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF34" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q34" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V34" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AG34" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.36</v>
+        <v>3.7</v>
       </c>
       <c r="AI34" s="3" t="n">
-        <v>46078.79166666666</v>
+        <v>46078.70833333334</v>
       </c>
     </row>
     <row r="35">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,76 +4824,76 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.68</v>
+        <v>2.97</v>
       </c>
       <c r="M37" t="n">
-        <v>3.15</v>
+        <v>3.27</v>
       </c>
       <c r="N37" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="O37" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P37" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q37" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V37" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z37" t="n">
         <v>3.1</v>
       </c>
-      <c r="R37" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T37" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V37" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AA37" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AC37" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AI37" s="3" t="n">
-        <v>46078.8125</v>
+        <v>46078.79166666666</v>
       </c>
     </row>
     <row r="38">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,76 +4943,76 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.92</v>
+        <v>2.68</v>
       </c>
       <c r="M38" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O38" t="n">
         <v>3.6</v>
       </c>
-      <c r="N38" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O38" t="n">
-        <v>2.45</v>
-      </c>
       <c r="P38" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q38" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="R38" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V38" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH38" t="n">
         <v>1.4</v>
       </c>
-      <c r="S38" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V38" t="n">
-        <v>7</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AI38" s="3" t="n">
-        <v>46078.83333333334</v>
+        <v>46078.8125</v>
       </c>
     </row>
     <row r="39">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,40 +5062,40 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.71</v>
+        <v>1.92</v>
       </c>
       <c r="M39" t="n">
-        <v>3.79</v>
+        <v>3.6</v>
       </c>
       <c r="N39" t="n">
-        <v>5.14</v>
+        <v>4.1</v>
       </c>
       <c r="O39" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="P39" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="R39" t="n">
         <v>1.4</v>
       </c>
       <c r="S39" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="T39" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="U39" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V39" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W39" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X39" t="n">
         <v>1.06</v>
@@ -5104,25 +5104,25 @@
         <v>1.3</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AC39" t="n">
         <v>3.3</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG39" t="n">
         <v>1.3</v>
@@ -5131,7 +5131,7 @@
         <v>1.88</v>
       </c>
       <c r="AI39" s="3" t="n">
-        <v>46078.89583333334</v>
+        <v>46078.83333333334</v>
       </c>
     </row>
     <row r="40">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,28 +5181,28 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="M40" t="n">
-        <v>3.44</v>
+        <v>3.79</v>
       </c>
       <c r="N40" t="n">
-        <v>3.37</v>
+        <v>5.14</v>
       </c>
       <c r="O40" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="P40" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="R40" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S40" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="T40" t="n">
         <v>2.8</v>
@@ -5217,39 +5217,158 @@
         <v>1.08</v>
       </c>
       <c r="X40" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AI40" s="3" t="n">
+        <v>46078.89583333334</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="N41" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="O41" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V41" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X41" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y40" t="n">
+      <c r="Y41" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z40" t="n">
+      <c r="Z41" t="n">
         <v>3.3</v>
       </c>
-      <c r="AA40" t="n">
+      <c r="AA41" t="n">
         <v>1.98</v>
       </c>
-      <c r="AB40" t="n">
+      <c r="AB41" t="n">
         <v>1.71</v>
       </c>
-      <c r="AC40" t="n">
+      <c r="AC41" t="n">
         <v>3.2</v>
       </c>
-      <c r="AD40" t="n">
+      <c r="AD41" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE40" t="n">
+      <c r="AE41" t="n">
         <v>1.73</v>
       </c>
-      <c r="AF40" t="n">
+      <c r="AF41" t="n">
         <v>2</v>
       </c>
-      <c r="AG40" t="n">
+      <c r="AG41" t="n">
         <v>1.33</v>
       </c>
-      <c r="AH40" t="n">
+      <c r="AH41" t="n">
         <v>1.62</v>
       </c>
-      <c r="AI40" s="3" t="n">
+      <c r="AI41" s="3" t="n">
         <v>46078.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="N16" t="n">
-        <v>2.69</v>
+        <v>3.07</v>
       </c>
       <c r="O16" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.4</v>
+        <v>1.93</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.89</v>
+        <v>3.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.87</v>
+        <v>1.28</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46078.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5.93</v>
+        <v>3.1</v>
       </c>
       <c r="M17" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
-        <v>1.44</v>
+        <v>2.2</v>
       </c>
       <c r="O17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.97</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.43</v>
+        <v>2.37</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.73</v>
+        <v>1.53</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46078.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="M18" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>3.07</v>
+        <v>2.69</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.93</v>
+        <v>3.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.5</v>
+        <v>1.89</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.28</v>
+        <v>1.87</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46078.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.1</v>
+        <v>5.93</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="N19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O19" t="n">
+        <v>5</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="T19" t="n">
         <v>2.2</v>
       </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.37</v>
+        <v>1.43</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.53</v>
+        <v>2.73</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46078.625</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="P25" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="R25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB25" t="n">
         <v>1.57</v>
       </c>
-      <c r="S25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V25" t="n">
-        <v>10</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AC25" t="n">
-        <v>5.25</v>
+        <v>4.26</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AF25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.62</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46078.6875</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O27" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="P27" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="R27" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S27" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="T27" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="U27" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V27" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="W27" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X27" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.26</v>
+        <v>5.25</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46078.6875</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="M28" t="n">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="N28" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="O28" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="P28" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S28" t="n">
-        <v>2.8</v>
+        <v>3.22</v>
       </c>
       <c r="T28" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="U28" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="V28" t="n">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="W28" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X28" t="n">
         <v>1.03</v>
       </c>
       <c r="Y28" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AG28" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH28" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46078.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.28</v>
+        <v>2.41</v>
       </c>
       <c r="M29" t="n">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="N29" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S29" t="n">
         <v>2.8</v>
       </c>
-      <c r="O29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.22</v>
-      </c>
       <c r="T29" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="U29" t="n">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="V29" t="n">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
         <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.44</v>
+        <v>1.93</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46078.69791666666</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="M33" t="n">
-        <v>4.58</v>
+        <v>6.14</v>
       </c>
       <c r="N33" t="n">
-        <v>5.49</v>
+        <v>9.85</v>
       </c>
       <c r="O33" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="P33" t="n">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="Q33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R33" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="S33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V33" t="n">
         <v>3.6</v>
       </c>
-      <c r="T33" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V33" t="n">
-        <v>4.6</v>
-      </c>
       <c r="W33" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.3</v>
+        <v>7.25</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.63</v>
+        <v>1.29</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.45</v>
+        <v>3.7</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="M34" t="n">
-        <v>6.14</v>
+        <v>4.58</v>
       </c>
       <c r="N34" t="n">
-        <v>9.85</v>
+        <v>5.49</v>
       </c>
       <c r="O34" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="P34" t="n">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="Q34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R34" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V34" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W34" t="n">
         <v>1.17</v>
       </c>
-      <c r="S34" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T34" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V34" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.25</v>
-      </c>
       <c r="X34" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Z34" t="n">
-        <v>7.25</v>
+        <v>5.3</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.29</v>
+        <v>1.63</v>
       </c>
       <c r="AB34" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AH34" t="n">
-        <v>3.7</v>
+        <v>2.45</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4550,22 +4550,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.97</v>
+        <v>2.17</v>
       </c>
       <c r="M37" t="n">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
       <c r="N37" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="O37" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="P37" t="n">
         <v>2.05</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="R37" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S37" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T37" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U37" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V37" t="n">
-        <v>7.75</v>
+        <v>8.5</v>
       </c>
       <c r="W37" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X37" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46078.79166666666</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2321,77 +2321,77 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="M16" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>3.07</v>
+        <v>2.69</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.93</v>
+        <v>3.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.5</v>
+        <v>1.89</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.28</v>
+        <v>1.87</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46078.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2440,77 +2440,77 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.1</v>
+        <v>5.93</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="N17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O17" t="n">
+        <v>5</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="T17" t="n">
         <v>2.2</v>
       </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.37</v>
+        <v>1.43</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.53</v>
+        <v>2.73</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46078.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="N18" t="n">
-        <v>2.69</v>
+        <v>2.2</v>
       </c>
       <c r="O18" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.89</v>
+        <v>2.37</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.87</v>
+        <v>1.53</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46078.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5.93</v>
+        <v>2.48</v>
       </c>
       <c r="M19" t="n">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="N19" t="n">
-        <v>1.44</v>
+        <v>3.07</v>
       </c>
       <c r="O19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.15</v>
+        <v>1.75</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.97</v>
+        <v>1.93</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.43</v>
+        <v>3.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.73</v>
+        <v>1.28</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46078.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.28</v>
+        <v>2.41</v>
       </c>
       <c r="M28" t="n">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="N28" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S28" t="n">
         <v>2.8</v>
       </c>
-      <c r="O28" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.22</v>
-      </c>
       <c r="T28" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="U28" t="n">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="V28" t="n">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X28" t="n">
         <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.44</v>
+        <v>1.93</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46078.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="M29" t="n">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="N29" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="O29" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="P29" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R29" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S29" t="n">
-        <v>2.8</v>
+        <v>3.22</v>
       </c>
       <c r="T29" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="U29" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="V29" t="n">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="W29" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X29" t="n">
         <v>1.03</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AG29" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH29" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46078.69791666666</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,22 +4110,22 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="M31" t="n">
-        <v>4.68</v>
+        <v>4.58</v>
       </c>
       <c r="N31" t="n">
-        <v>6.86</v>
+        <v>5.49</v>
       </c>
       <c r="O31" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="P31" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="R31" t="n">
         <v>1.23</v>
@@ -4137,10 +4137,10 @@
         <v>2.1</v>
       </c>
       <c r="U31" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="V31" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="W31" t="n">
         <v>1.17</v>
@@ -4149,13 +4149,13 @@
         <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AB31" t="n">
         <v>2.15</v>
@@ -4167,16 +4167,16 @@
         <v>1.63</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AG31" t="n">
         <v>1.18</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.81</v>
+        <v>2.45</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="M32" t="n">
-        <v>3.54</v>
+        <v>4.68</v>
       </c>
       <c r="N32" t="n">
-        <v>4.08</v>
+        <v>6.86</v>
       </c>
       <c r="O32" t="n">
-        <v>2.38</v>
+        <v>1.93</v>
       </c>
       <c r="P32" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T32" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3.22</v>
-      </c>
       <c r="U32" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="V32" t="n">
-        <v>8.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="W32" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="X32" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.8</v>
+        <v>5.25</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.92</v>
+        <v>2.2</v>
       </c>
       <c r="AD32" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG32" t="n">
         <v>1.18</v>
       </c>
-      <c r="AE32" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH32" t="n">
-        <v>1.95</v>
+        <v>2.81</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="M34" t="n">
-        <v>4.58</v>
+        <v>3.54</v>
       </c>
       <c r="N34" t="n">
-        <v>5.49</v>
+        <v>4.08</v>
       </c>
       <c r="O34" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V34" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA34" t="n">
         <v>1.95</v>
       </c>
-      <c r="P34" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>5</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V34" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AB34" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.2</v>
+        <v>3.92</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.63</v>
+        <v>1.18</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.6</v>
+        <v>2.03</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.3</v>
+        <v>1.72</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4550,22 +4550,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4788,22 +4788,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46078.79166666666</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="M16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O16" t="n">
+        <v>5</v>
+      </c>
+      <c r="P16" t="n">
         <v>2.5</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="O16" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.15</v>
-      </c>
       <c r="Q16" t="n">
-        <v>3.28</v>
+        <v>1.89</v>
       </c>
       <c r="R16" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>2.77</v>
+        <v>3.66</v>
       </c>
       <c r="T16" t="n">
-        <v>2.93</v>
+        <v>2.2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.39</v>
+        <v>1.68</v>
       </c>
       <c r="V16" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.4</v>
+        <v>5.97</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.89</v>
+        <v>1.43</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.87</v>
+        <v>2.73</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.33</v>
+        <v>2.23</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.3</v>
+        <v>1.71</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.11</v>
+        <v>2.42</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>2.72</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46078.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5.93</v>
+        <v>2.5</v>
       </c>
       <c r="M17" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V17" t="n">
+        <v>6</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.44</v>
-      </c>
-      <c r="O17" t="n">
-        <v>5</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>5.97</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.11</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46078.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="O25" t="n">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="P25" t="n">
         <v>1.95</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.2</v>
+        <v>7.1</v>
       </c>
       <c r="R25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V25" t="n">
+        <v>9</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB25" t="n">
         <v>1.5</v>
       </c>
-      <c r="S25" t="n">
+      <c r="AC25" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE25" t="n">
         <v>2.4</v>
       </c>
-      <c r="T25" t="n">
-        <v>3</v>
-      </c>
-      <c r="U25" t="n">
+      <c r="AF25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG25" t="n">
         <v>1.3</v>
       </c>
-      <c r="V25" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH25" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46078.6875</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.56</v>
+        <v>2.44</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>2.72</v>
       </c>
       <c r="N26" t="n">
-        <v>6.45</v>
+        <v>3.11</v>
       </c>
       <c r="O26" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="P26" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Q26" t="n">
-        <v>7.1</v>
+        <v>3.75</v>
       </c>
       <c r="R26" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="S26" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="T26" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U26" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W26" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X26" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.65</v>
+        <v>5.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46078.6875</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="P27" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="R27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V27" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB27" t="n">
         <v>1.57</v>
       </c>
-      <c r="S27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V27" t="n">
-        <v>10</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AC27" t="n">
-        <v>5.25</v>
+        <v>4.26</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AF27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.62</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46078.6875</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="M28" t="n">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="N28" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="O28" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="P28" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S28" t="n">
-        <v>2.8</v>
+        <v>3.22</v>
       </c>
       <c r="T28" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="U28" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="V28" t="n">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="W28" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X28" t="n">
         <v>1.03</v>
       </c>
       <c r="Y28" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AG28" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH28" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46078.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.28</v>
+        <v>2.41</v>
       </c>
       <c r="M29" t="n">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="N29" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S29" t="n">
         <v>2.8</v>
       </c>
-      <c r="O29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.22</v>
-      </c>
       <c r="T29" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="U29" t="n">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="V29" t="n">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
         <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.44</v>
+        <v>1.93</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46078.69791666666</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,22 +4110,22 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="M31" t="n">
-        <v>4.58</v>
+        <v>4.68</v>
       </c>
       <c r="N31" t="n">
-        <v>5.49</v>
+        <v>6.86</v>
       </c>
       <c r="O31" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="P31" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="Q31" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="R31" t="n">
         <v>1.23</v>
@@ -4137,10 +4137,10 @@
         <v>2.1</v>
       </c>
       <c r="U31" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="V31" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="W31" t="n">
         <v>1.17</v>
@@ -4149,13 +4149,13 @@
         <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AB31" t="n">
         <v>2.15</v>
@@ -4167,16 +4167,16 @@
         <v>1.63</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AG31" t="n">
         <v>1.18</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.45</v>
+        <v>2.81</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="M32" t="n">
-        <v>4.68</v>
+        <v>3.54</v>
       </c>
       <c r="N32" t="n">
-        <v>6.86</v>
+        <v>4.08</v>
       </c>
       <c r="O32" t="n">
-        <v>1.93</v>
+        <v>2.38</v>
       </c>
       <c r="P32" t="n">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="R32" t="n">
-        <v>1.23</v>
+        <v>1.47</v>
       </c>
       <c r="S32" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="T32" t="n">
-        <v>2.1</v>
+        <v>3.22</v>
       </c>
       <c r="U32" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="V32" t="n">
-        <v>4.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W32" t="n">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="X32" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.25</v>
+        <v>2.8</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.2</v>
+        <v>3.92</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.63</v>
+        <v>1.18</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.65</v>
+        <v>2.03</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.81</v>
+        <v>1.95</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="M33" t="n">
-        <v>6.14</v>
+        <v>4.58</v>
       </c>
       <c r="N33" t="n">
-        <v>9.85</v>
+        <v>5.49</v>
       </c>
       <c r="O33" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="P33" t="n">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="Q33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R33" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V33" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W33" t="n">
         <v>1.17</v>
       </c>
-      <c r="S33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V33" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.25</v>
-      </c>
       <c r="X33" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Z33" t="n">
-        <v>7.25</v>
+        <v>5.3</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.29</v>
+        <v>1.63</v>
       </c>
       <c r="AB33" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AH33" t="n">
-        <v>3.7</v>
+        <v>2.45</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M34" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="N34" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="P34" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>6</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T34" t="n">
         <v>1.85</v>
       </c>
-      <c r="M34" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="N34" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="O34" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T34" t="n">
-        <v>3.22</v>
-      </c>
       <c r="U34" t="n">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="V34" t="n">
-        <v>8.199999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="W34" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="X34" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.4</v>
+        <v>1.07</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.8</v>
+        <v>7.25</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.95</v>
+        <v>1.29</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.75</v>
+        <v>3.4</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.92</v>
+        <v>1.87</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.18</v>
+        <v>1.83</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.03</v>
+        <v>1.66</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.95</v>
+        <v>3.7</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4550,22 +4550,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.97</v>
+        <v>2.17</v>
       </c>
       <c r="M36" t="n">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
       <c r="N36" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="O36" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="P36" t="n">
         <v>2.05</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="R36" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S36" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T36" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U36" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V36" t="n">
-        <v>7.75</v>
+        <v>8.5</v>
       </c>
       <c r="W36" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X36" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4788,22 +4788,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46078.79166666666</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2440,77 +2440,77 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="N17" t="n">
-        <v>2.69</v>
+        <v>3.07</v>
       </c>
       <c r="O17" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.4</v>
+        <v>1.93</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.89</v>
+        <v>3.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.87</v>
+        <v>1.28</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46078.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2559,77 +2559,77 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>2.2</v>
+        <v>2.69</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.37</v>
+        <v>1.89</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46078.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.48</v>
+        <v>3.1</v>
       </c>
       <c r="M19" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="N19" t="n">
-        <v>3.07</v>
+        <v>2.2</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2721,16 +2721,16 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.5</v>
+        <v>2.37</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3167,64 +3167,64 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46078.66666666666</v>
@@ -3286,64 +3286,64 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46078.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="P25" t="n">
         <v>1.95</v>
       </c>
       <c r="Q25" t="n">
-        <v>7.1</v>
+        <v>4.2</v>
       </c>
       <c r="R25" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="S25" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="T25" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U25" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V25" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X25" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.65</v>
+        <v>4.26</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46078.6875</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="O27" t="n">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="P27" t="n">
         <v>1.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.2</v>
+        <v>7.1</v>
       </c>
       <c r="R27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V27" t="n">
+        <v>9</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB27" t="n">
         <v>1.5</v>
       </c>
-      <c r="S27" t="n">
+      <c r="AC27" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE27" t="n">
         <v>2.4</v>
       </c>
-      <c r="T27" t="n">
-        <v>3</v>
-      </c>
-      <c r="U27" t="n">
+      <c r="AF27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG27" t="n">
         <v>1.3</v>
       </c>
-      <c r="V27" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH27" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46078.6875</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.41</v>
+        <v>1.24</v>
       </c>
       <c r="M29" t="n">
-        <v>3.34</v>
+        <v>6</v>
       </c>
       <c r="N29" t="n">
-        <v>2.83</v>
+        <v>10.5</v>
       </c>
       <c r="O29" t="n">
-        <v>2.87</v>
+        <v>1.66</v>
       </c>
       <c r="P29" t="n">
-        <v>2.15</v>
+        <v>2.62</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.25</v>
+        <v>8.4</v>
       </c>
       <c r="R29" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="S29" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="T29" t="n">
-        <v>2.8</v>
+        <v>2.22</v>
       </c>
       <c r="U29" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="V29" t="n">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
       <c r="W29" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X29" t="n">
         <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.2</v>
+        <v>5.4</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.93</v>
+        <v>1.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.77</v>
+        <v>2.62</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.29</v>
+        <v>1.6</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.53</v>
+        <v>3.6</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46078.69791666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.24</v>
+        <v>2.41</v>
       </c>
       <c r="M30" t="n">
-        <v>6</v>
+        <v>3.34</v>
       </c>
       <c r="N30" t="n">
-        <v>10.5</v>
+        <v>2.83</v>
       </c>
       <c r="O30" t="n">
-        <v>1.66</v>
+        <v>2.87</v>
       </c>
       <c r="P30" t="n">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="Q30" t="n">
-        <v>8.4</v>
+        <v>3.25</v>
       </c>
       <c r="R30" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="S30" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="T30" t="n">
-        <v>2.22</v>
+        <v>2.8</v>
       </c>
       <c r="U30" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="V30" t="n">
-        <v>4.9</v>
+        <v>6.5</v>
       </c>
       <c r="W30" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X30" t="n">
         <v>1.03</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="Z30" t="n">
-        <v>5.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.5</v>
+        <v>1.93</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.62</v>
+        <v>1.77</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.6</v>
+        <v>1.29</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>3.6</v>
+        <v>1.53</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46078.69791666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="M31" t="n">
-        <v>4.68</v>
+        <v>3.54</v>
       </c>
       <c r="N31" t="n">
-        <v>6.86</v>
+        <v>4.08</v>
       </c>
       <c r="O31" t="n">
-        <v>1.93</v>
+        <v>2.38</v>
       </c>
       <c r="P31" t="n">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="R31" t="n">
-        <v>1.23</v>
+        <v>1.47</v>
       </c>
       <c r="S31" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="T31" t="n">
-        <v>2.1</v>
+        <v>3.22</v>
       </c>
       <c r="U31" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="V31" t="n">
-        <v>4.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W31" t="n">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.25</v>
+        <v>2.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.2</v>
+        <v>3.92</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.63</v>
+        <v>1.18</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.65</v>
+        <v>2.03</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.81</v>
+        <v>1.95</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="M32" t="n">
-        <v>3.54</v>
+        <v>4.58</v>
       </c>
       <c r="N32" t="n">
-        <v>4.08</v>
+        <v>5.49</v>
       </c>
       <c r="O32" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="P32" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>5</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T32" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3.22</v>
-      </c>
       <c r="U32" t="n">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="V32" t="n">
-        <v>8.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="W32" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="X32" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.4</v>
+        <v>1.09</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.92</v>
+        <v>2.2</v>
       </c>
       <c r="AD32" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG32" t="n">
         <v>1.18</v>
       </c>
-      <c r="AE32" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH32" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,22 +4348,22 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="M33" t="n">
-        <v>4.58</v>
+        <v>4.68</v>
       </c>
       <c r="N33" t="n">
-        <v>5.49</v>
+        <v>6.86</v>
       </c>
       <c r="O33" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="P33" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="Q33" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="R33" t="n">
         <v>1.23</v>
@@ -4375,10 +4375,10 @@
         <v>2.1</v>
       </c>
       <c r="U33" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="V33" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="W33" t="n">
         <v>1.17</v>
@@ -4387,13 +4387,13 @@
         <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AB33" t="n">
         <v>2.15</v>
@@ -4405,16 +4405,16 @@
         <v>1.63</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AG33" t="n">
         <v>1.18</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.45</v>
+        <v>2.81</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4550,22 +4550,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.17</v>
+        <v>2.97</v>
       </c>
       <c r="M36" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="N36" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="O36" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="P36" t="n">
         <v>2.05</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="R36" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S36" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T36" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V36" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG36" t="n">
         <v>1.33</v>
       </c>
-      <c r="V36" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH36" t="n">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4788,22 +4788,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46078.79166666666</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.93</v>
+        <v>2.5</v>
       </c>
       <c r="M16" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V16" t="n">
+        <v>6</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.44</v>
-      </c>
-      <c r="O16" t="n">
-        <v>5</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>5.97</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.11</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46078.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.48</v>
+        <v>3.1</v>
       </c>
       <c r="M17" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
-        <v>3.07</v>
+        <v>2.2</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2483,16 +2483,16 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.5</v>
+        <v>2.37</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="M18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O18" t="n">
+        <v>5</v>
+      </c>
+      <c r="P18" t="n">
         <v>2.5</v>
       </c>
-      <c r="M18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="O18" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.15</v>
-      </c>
       <c r="Q18" t="n">
-        <v>3.28</v>
+        <v>1.89</v>
       </c>
       <c r="R18" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>2.77</v>
+        <v>3.66</v>
       </c>
       <c r="T18" t="n">
-        <v>2.93</v>
+        <v>2.2</v>
       </c>
       <c r="U18" t="n">
-        <v>1.39</v>
+        <v>1.68</v>
       </c>
       <c r="V18" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.4</v>
+        <v>5.97</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.89</v>
+        <v>1.43</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.87</v>
+        <v>2.73</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.33</v>
+        <v>2.23</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>1.71</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.11</v>
+        <v>2.42</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>2.72</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46078.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.1</v>
+        <v>2.48</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="N19" t="n">
-        <v>2.2</v>
+        <v>3.07</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2721,16 +2721,16 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.37</v>
+        <v>3.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="O25" t="n">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="P25" t="n">
         <v>1.95</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.2</v>
+        <v>7.1</v>
       </c>
       <c r="R25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V25" t="n">
+        <v>9</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB25" t="n">
         <v>1.5</v>
       </c>
-      <c r="S25" t="n">
+      <c r="AC25" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE25" t="n">
         <v>2.4</v>
       </c>
-      <c r="T25" t="n">
-        <v>3</v>
-      </c>
-      <c r="U25" t="n">
+      <c r="AF25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG25" t="n">
         <v>1.3</v>
       </c>
-      <c r="V25" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH25" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46078.6875</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="P27" t="n">
         <v>1.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>7.1</v>
+        <v>4.2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="S27" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="T27" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U27" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V27" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X27" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.65</v>
+        <v>4.26</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46078.6875</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.28</v>
+        <v>2.41</v>
       </c>
       <c r="M28" t="n">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="N28" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S28" t="n">
         <v>2.8</v>
       </c>
-      <c r="O28" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.22</v>
-      </c>
       <c r="T28" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="U28" t="n">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="V28" t="n">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X28" t="n">
         <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.44</v>
+        <v>1.93</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46078.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.24</v>
+        <v>2.28</v>
       </c>
       <c r="M29" t="n">
-        <v>6</v>
+        <v>3.68</v>
       </c>
       <c r="N29" t="n">
-        <v>10.5</v>
+        <v>2.8</v>
       </c>
       <c r="O29" t="n">
-        <v>1.66</v>
+        <v>2.75</v>
       </c>
       <c r="P29" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>8.4</v>
+        <v>3</v>
       </c>
       <c r="R29" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="S29" t="n">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="T29" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="U29" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="V29" t="n">
-        <v>4.9</v>
+        <v>5.25</v>
       </c>
       <c r="W29" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X29" t="n">
         <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z29" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA29" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD29" t="n">
         <v>1.5</v>
       </c>
-      <c r="AB29" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD29" t="n">
+      <c r="AE29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH29" t="n">
         <v>1.6</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>3.6</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46078.69791666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.41</v>
+        <v>1.24</v>
       </c>
       <c r="M30" t="n">
-        <v>3.34</v>
+        <v>6</v>
       </c>
       <c r="N30" t="n">
-        <v>2.83</v>
+        <v>10.5</v>
       </c>
       <c r="O30" t="n">
-        <v>2.87</v>
+        <v>1.66</v>
       </c>
       <c r="P30" t="n">
-        <v>2.15</v>
+        <v>2.62</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.25</v>
+        <v>8.4</v>
       </c>
       <c r="R30" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="S30" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="T30" t="n">
-        <v>2.8</v>
+        <v>2.22</v>
       </c>
       <c r="U30" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="V30" t="n">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
       <c r="W30" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X30" t="n">
         <v>1.03</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.2</v>
+        <v>5.4</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.93</v>
+        <v>1.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.77</v>
+        <v>2.62</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.29</v>
+        <v>1.6</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.53</v>
+        <v>3.6</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46078.69791666666</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,22 +4229,22 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="M32" t="n">
-        <v>4.58</v>
+        <v>4.68</v>
       </c>
       <c r="N32" t="n">
-        <v>5.49</v>
+        <v>6.86</v>
       </c>
       <c r="O32" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="P32" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="Q32" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="R32" t="n">
         <v>1.23</v>
@@ -4256,10 +4256,10 @@
         <v>2.1</v>
       </c>
       <c r="U32" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="V32" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="W32" t="n">
         <v>1.17</v>
@@ -4268,13 +4268,13 @@
         <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AB32" t="n">
         <v>2.15</v>
@@ -4286,16 +4286,16 @@
         <v>1.63</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AG32" t="n">
         <v>1.18</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.45</v>
+        <v>2.81</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="M33" t="n">
-        <v>4.68</v>
+        <v>6.14</v>
       </c>
       <c r="N33" t="n">
-        <v>6.86</v>
+        <v>9.85</v>
       </c>
       <c r="O33" t="n">
-        <v>1.93</v>
+        <v>1.58</v>
       </c>
       <c r="P33" t="n">
-        <v>2.62</v>
+        <v>3.25</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="R33" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="S33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V33" t="n">
         <v>3.6</v>
       </c>
-      <c r="T33" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V33" t="n">
-        <v>4.5</v>
-      </c>
       <c r="W33" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.25</v>
+        <v>7.25</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.61</v>
+        <v>1.29</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.81</v>
+        <v>3.7</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="M34" t="n">
-        <v>6.14</v>
+        <v>4.58</v>
       </c>
       <c r="N34" t="n">
-        <v>9.85</v>
+        <v>5.49</v>
       </c>
       <c r="O34" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="P34" t="n">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="Q34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R34" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V34" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W34" t="n">
         <v>1.17</v>
       </c>
-      <c r="S34" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T34" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V34" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.25</v>
-      </c>
       <c r="X34" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Z34" t="n">
-        <v>7.25</v>
+        <v>5.3</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.29</v>
+        <v>1.63</v>
       </c>
       <c r="AB34" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AH34" t="n">
-        <v>3.7</v>
+        <v>2.45</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.17</v>
+        <v>2.97</v>
       </c>
       <c r="M35" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="N35" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="O35" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="P35" t="n">
         <v>2.05</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="R35" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S35" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T35" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V35" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG35" t="n">
         <v>1.33</v>
       </c>
-      <c r="V35" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH35" t="n">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4788,22 +4788,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46078.79166666666</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,28 +5181,28 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="M40" t="n">
-        <v>3.79</v>
+        <v>3.44</v>
       </c>
       <c r="N40" t="n">
-        <v>5.14</v>
+        <v>3.37</v>
       </c>
       <c r="O40" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="P40" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="R40" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S40" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="T40" t="n">
         <v>2.8</v>
@@ -5217,37 +5217,37 @@
         <v>1.08</v>
       </c>
       <c r="X40" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD40" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z40" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB40" t="n">
+      <c r="AE40" t="n">
         <v>1.73</v>
       </c>
-      <c r="AC40" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF40" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46078.89583333334</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,28 +5300,28 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="M41" t="n">
-        <v>3.44</v>
+        <v>3.79</v>
       </c>
       <c r="N41" t="n">
-        <v>3.37</v>
+        <v>5.14</v>
       </c>
       <c r="O41" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="P41" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="R41" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S41" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="T41" t="n">
         <v>2.8</v>
@@ -5336,37 +5336,37 @@
         <v>1.08</v>
       </c>
       <c r="X41" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD41" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z41" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD41" t="n">
+      <c r="AE41" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG41" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE41" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH41" t="n">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46078.89583333334</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46078.4375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46078.4375</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="M16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O16" t="n">
+        <v>5</v>
+      </c>
+      <c r="P16" t="n">
         <v>2.5</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="O16" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.15</v>
-      </c>
       <c r="Q16" t="n">
-        <v>3.28</v>
+        <v>1.89</v>
       </c>
       <c r="R16" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>2.77</v>
+        <v>3.66</v>
       </c>
       <c r="T16" t="n">
-        <v>2.93</v>
+        <v>2.2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.39</v>
+        <v>1.68</v>
       </c>
       <c r="V16" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.4</v>
+        <v>5.97</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.89</v>
+        <v>1.43</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.87</v>
+        <v>2.73</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.33</v>
+        <v>2.23</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.3</v>
+        <v>1.71</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.11</v>
+        <v>2.42</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>2.72</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46078.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2440,77 +2440,77 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>2.2</v>
+        <v>2.69</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.37</v>
+        <v>1.89</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46078.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2559,77 +2559,77 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>5.93</v>
+        <v>2.48</v>
       </c>
       <c r="M18" t="n">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="N18" t="n">
-        <v>1.44</v>
+        <v>3.07</v>
       </c>
       <c r="O18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.15</v>
+        <v>1.75</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.97</v>
+        <v>1.93</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.43</v>
+        <v>3.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.73</v>
+        <v>1.28</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46078.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.48</v>
+        <v>3.1</v>
       </c>
       <c r="M19" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="N19" t="n">
-        <v>3.07</v>
+        <v>2.2</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2721,16 +2721,16 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.5</v>
+        <v>2.37</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="P25" t="n">
         <v>1.95</v>
       </c>
       <c r="Q25" t="n">
-        <v>7.1</v>
+        <v>4.2</v>
       </c>
       <c r="R25" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="S25" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="T25" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U25" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V25" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X25" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.65</v>
+        <v>4.26</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46078.6875</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="O27" t="n">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="P27" t="n">
         <v>1.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.2</v>
+        <v>7.1</v>
       </c>
       <c r="R27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V27" t="n">
+        <v>9</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB27" t="n">
         <v>1.5</v>
       </c>
-      <c r="S27" t="n">
+      <c r="AC27" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE27" t="n">
         <v>2.4</v>
       </c>
-      <c r="T27" t="n">
-        <v>3</v>
-      </c>
-      <c r="U27" t="n">
+      <c r="AF27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG27" t="n">
         <v>1.3</v>
       </c>
-      <c r="V27" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH27" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46078.6875</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.28</v>
+        <v>1.24</v>
       </c>
       <c r="M29" t="n">
-        <v>3.68</v>
+        <v>6</v>
       </c>
       <c r="N29" t="n">
-        <v>2.8</v>
+        <v>10.5</v>
       </c>
       <c r="O29" t="n">
-        <v>2.75</v>
+        <v>1.66</v>
       </c>
       <c r="P29" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="Q29" t="n">
-        <v>3</v>
+        <v>8.4</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="S29" t="n">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="T29" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="U29" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="V29" t="n">
-        <v>5.25</v>
+        <v>4.9</v>
       </c>
       <c r="W29" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X29" t="n">
         <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.44</v>
+        <v>1.81</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46078.69791666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.24</v>
+        <v>2.28</v>
       </c>
       <c r="M30" t="n">
-        <v>6</v>
+        <v>3.68</v>
       </c>
       <c r="N30" t="n">
-        <v>10.5</v>
+        <v>2.8</v>
       </c>
       <c r="O30" t="n">
-        <v>1.66</v>
+        <v>2.75</v>
       </c>
       <c r="P30" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>8.4</v>
+        <v>3</v>
       </c>
       <c r="R30" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="S30" t="n">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="T30" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="U30" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="V30" t="n">
-        <v>4.9</v>
+        <v>5.25</v>
       </c>
       <c r="W30" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X30" t="n">
         <v>1.03</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z30" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA30" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD30" t="n">
         <v>1.5</v>
       </c>
-      <c r="AB30" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD30" t="n">
+      <c r="AE30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH30" t="n">
         <v>1.6</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>3.6</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46078.69791666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M31" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="N31" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="P31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>6</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T31" t="n">
         <v>1.85</v>
       </c>
-      <c r="M31" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="N31" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3.22</v>
-      </c>
       <c r="U31" t="n">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="V31" t="n">
-        <v>8.199999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="W31" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="X31" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.4</v>
+        <v>1.07</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.8</v>
+        <v>7.25</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.95</v>
+        <v>1.29</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.75</v>
+        <v>3.4</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.92</v>
+        <v>1.87</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.18</v>
+        <v>1.83</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.03</v>
+        <v>1.66</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.95</v>
+        <v>3.7</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="M32" t="n">
-        <v>4.68</v>
+        <v>3.54</v>
       </c>
       <c r="N32" t="n">
-        <v>6.86</v>
+        <v>4.08</v>
       </c>
       <c r="O32" t="n">
-        <v>1.93</v>
+        <v>2.38</v>
       </c>
       <c r="P32" t="n">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="R32" t="n">
-        <v>1.23</v>
+        <v>1.47</v>
       </c>
       <c r="S32" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="T32" t="n">
-        <v>2.1</v>
+        <v>3.22</v>
       </c>
       <c r="U32" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="V32" t="n">
-        <v>4.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W32" t="n">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="X32" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.25</v>
+        <v>2.8</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.2</v>
+        <v>3.92</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.63</v>
+        <v>1.18</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.65</v>
+        <v>2.03</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.81</v>
+        <v>1.95</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="M33" t="n">
-        <v>6.14</v>
+        <v>4.68</v>
       </c>
       <c r="N33" t="n">
-        <v>9.85</v>
+        <v>6.86</v>
       </c>
       <c r="O33" t="n">
-        <v>1.58</v>
+        <v>1.93</v>
       </c>
       <c r="P33" t="n">
-        <v>3.25</v>
+        <v>2.62</v>
       </c>
       <c r="Q33" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="R33" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W33" t="n">
         <v>1.17</v>
       </c>
-      <c r="S33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V33" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.25</v>
-      </c>
       <c r="X33" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z33" t="n">
-        <v>7.25</v>
+        <v>5.25</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.29</v>
+        <v>1.61</v>
       </c>
       <c r="AB33" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AH33" t="n">
-        <v>3.7</v>
+        <v>2.81</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.97</v>
+        <v>2.17</v>
       </c>
       <c r="M35" t="n">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
       <c r="N35" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="O35" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="P35" t="n">
         <v>2.05</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="R35" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S35" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T35" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U35" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V35" t="n">
-        <v>7.75</v>
+        <v>8.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X35" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.17</v>
+        <v>2.97</v>
       </c>
       <c r="M37" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="N37" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="O37" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="P37" t="n">
         <v>2.05</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="R37" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S37" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T37" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V37" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG37" t="n">
         <v>1.33</v>
       </c>
-      <c r="V37" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH37" t="n">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46078.79166666666</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,28 +5181,28 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="M40" t="n">
-        <v>3.44</v>
+        <v>3.79</v>
       </c>
       <c r="N40" t="n">
-        <v>3.37</v>
+        <v>5.14</v>
       </c>
       <c r="O40" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="P40" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="R40" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S40" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="T40" t="n">
         <v>2.8</v>
@@ -5217,37 +5217,37 @@
         <v>1.08</v>
       </c>
       <c r="X40" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD40" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z40" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD40" t="n">
+      <c r="AE40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG40" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE40" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH40" t="n">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46078.89583333334</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,28 +5300,28 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="M41" t="n">
-        <v>3.79</v>
+        <v>3.44</v>
       </c>
       <c r="N41" t="n">
-        <v>5.14</v>
+        <v>3.37</v>
       </c>
       <c r="O41" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="P41" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="R41" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S41" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="T41" t="n">
         <v>2.8</v>
@@ -5336,37 +5336,37 @@
         <v>1.08</v>
       </c>
       <c r="X41" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y41" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD41" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z41" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB41" t="n">
+      <c r="AE41" t="n">
         <v>1.73</v>
       </c>
-      <c r="AC41" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF41" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46078.89583333334</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46078.4375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46078.4375</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.93</v>
+        <v>2.5</v>
       </c>
       <c r="M16" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V16" t="n">
+        <v>6</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.44</v>
-      </c>
-      <c r="O16" t="n">
-        <v>5</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>5.97</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.11</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46078.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2440,77 +2440,77 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
-        <v>2.69</v>
+        <v>2.2</v>
       </c>
       <c r="O17" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.89</v>
+        <v>2.37</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.87</v>
+        <v>1.53</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46078.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2678,77 +2678,77 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.1</v>
+        <v>5.93</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="N19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O19" t="n">
+        <v>5</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="T19" t="n">
         <v>2.2</v>
       </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.37</v>
+        <v>1.43</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.53</v>
+        <v>2.73</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46078.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="O25" t="n">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="P25" t="n">
         <v>1.95</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.2</v>
+        <v>7.1</v>
       </c>
       <c r="R25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V25" t="n">
+        <v>9</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB25" t="n">
         <v>1.5</v>
       </c>
-      <c r="S25" t="n">
+      <c r="AC25" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE25" t="n">
         <v>2.4</v>
       </c>
-      <c r="T25" t="n">
-        <v>3</v>
-      </c>
-      <c r="U25" t="n">
+      <c r="AF25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG25" t="n">
         <v>1.3</v>
       </c>
-      <c r="V25" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH25" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46078.6875</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="P27" t="n">
         <v>1.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>7.1</v>
+        <v>4.2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="S27" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="T27" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U27" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V27" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X27" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.65</v>
+        <v>4.26</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46078.6875</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.41</v>
+        <v>1.24</v>
       </c>
       <c r="M28" t="n">
-        <v>3.34</v>
+        <v>6</v>
       </c>
       <c r="N28" t="n">
-        <v>2.83</v>
+        <v>10.5</v>
       </c>
       <c r="O28" t="n">
-        <v>2.87</v>
+        <v>1.66</v>
       </c>
       <c r="P28" t="n">
-        <v>2.15</v>
+        <v>2.62</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.25</v>
+        <v>8.4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="S28" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="T28" t="n">
-        <v>2.8</v>
+        <v>2.22</v>
       </c>
       <c r="U28" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="V28" t="n">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
       <c r="W28" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X28" t="n">
         <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.2</v>
+        <v>5.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.93</v>
+        <v>1.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.77</v>
+        <v>2.62</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.29</v>
+        <v>1.6</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.53</v>
+        <v>3.6</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46078.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.24</v>
+        <v>2.28</v>
       </c>
       <c r="M29" t="n">
-        <v>6</v>
+        <v>3.68</v>
       </c>
       <c r="N29" t="n">
-        <v>10.5</v>
+        <v>2.8</v>
       </c>
       <c r="O29" t="n">
-        <v>1.66</v>
+        <v>2.75</v>
       </c>
       <c r="P29" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>8.4</v>
+        <v>3</v>
       </c>
       <c r="R29" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="S29" t="n">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="T29" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="U29" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="V29" t="n">
-        <v>4.9</v>
+        <v>5.25</v>
       </c>
       <c r="W29" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X29" t="n">
         <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z29" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA29" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD29" t="n">
         <v>1.5</v>
       </c>
-      <c r="AB29" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD29" t="n">
+      <c r="AE29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH29" t="n">
         <v>1.6</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>3.6</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46078.69791666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.28</v>
+        <v>2.41</v>
       </c>
       <c r="M30" t="n">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="N30" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S30" t="n">
         <v>2.8</v>
       </c>
-      <c r="O30" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3.22</v>
-      </c>
       <c r="T30" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="U30" t="n">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="V30" t="n">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
       <c r="W30" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X30" t="n">
         <v>1.03</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.44</v>
+        <v>1.93</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46078.69791666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.33</v>
+        <v>1.85</v>
       </c>
       <c r="M31" t="n">
-        <v>6.14</v>
+        <v>3.54</v>
       </c>
       <c r="N31" t="n">
-        <v>9.85</v>
+        <v>4.08</v>
       </c>
       <c r="O31" t="n">
-        <v>1.58</v>
+        <v>2.38</v>
       </c>
       <c r="P31" t="n">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="R31" t="n">
-        <v>1.17</v>
+        <v>1.47</v>
       </c>
       <c r="S31" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="T31" t="n">
-        <v>1.85</v>
+        <v>3.22</v>
       </c>
       <c r="U31" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="V31" t="n">
-        <v>3.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W31" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="X31" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.07</v>
+        <v>1.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>7.25</v>
+        <v>2.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="AB31" t="n">
-        <v>3.4</v>
+        <v>1.75</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.87</v>
+        <v>3.92</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.83</v>
+        <v>1.18</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.66</v>
+        <v>2.03</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>3.7</v>
+        <v>1.95</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="M32" t="n">
-        <v>3.54</v>
+        <v>4.58</v>
       </c>
       <c r="N32" t="n">
-        <v>4.08</v>
+        <v>5.49</v>
       </c>
       <c r="O32" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="P32" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>5</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T32" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3.22</v>
-      </c>
       <c r="U32" t="n">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="V32" t="n">
-        <v>8.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="W32" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="X32" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.4</v>
+        <v>1.09</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.92</v>
+        <v>2.2</v>
       </c>
       <c r="AD32" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG32" t="n">
         <v>1.18</v>
       </c>
-      <c r="AE32" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH32" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="M33" t="n">
-        <v>4.68</v>
+        <v>6.14</v>
       </c>
       <c r="N33" t="n">
-        <v>6.86</v>
+        <v>9.85</v>
       </c>
       <c r="O33" t="n">
-        <v>1.93</v>
+        <v>1.58</v>
       </c>
       <c r="P33" t="n">
-        <v>2.62</v>
+        <v>3.25</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="R33" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="S33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V33" t="n">
         <v>3.6</v>
       </c>
-      <c r="T33" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V33" t="n">
-        <v>4.5</v>
-      </c>
       <c r="W33" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.25</v>
+        <v>7.25</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.61</v>
+        <v>1.29</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.81</v>
+        <v>3.7</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,22 +4467,22 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="M34" t="n">
-        <v>4.58</v>
+        <v>4.68</v>
       </c>
       <c r="N34" t="n">
-        <v>5.49</v>
+        <v>6.86</v>
       </c>
       <c r="O34" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="P34" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="Q34" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="R34" t="n">
         <v>1.23</v>
@@ -4494,10 +4494,10 @@
         <v>2.1</v>
       </c>
       <c r="U34" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="V34" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="W34" t="n">
         <v>1.17</v>
@@ -4506,13 +4506,13 @@
         <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z34" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AB34" t="n">
         <v>2.15</v>
@@ -4524,16 +4524,16 @@
         <v>1.63</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AG34" t="n">
         <v>1.18</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.45</v>
+        <v>2.81</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4550,22 +4550,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.97</v>
+        <v>2.17</v>
       </c>
       <c r="M37" t="n">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
       <c r="N37" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="O37" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="P37" t="n">
         <v>2.05</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="R37" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S37" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T37" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U37" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V37" t="n">
-        <v>7.75</v>
+        <v>8.5</v>
       </c>
       <c r="W37" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X37" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46078.79166666666</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,28 +5181,28 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="M40" t="n">
-        <v>3.79</v>
+        <v>3.44</v>
       </c>
       <c r="N40" t="n">
-        <v>5.14</v>
+        <v>3.37</v>
       </c>
       <c r="O40" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="P40" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="R40" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S40" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="T40" t="n">
         <v>2.8</v>
@@ -5217,37 +5217,37 @@
         <v>1.08</v>
       </c>
       <c r="X40" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD40" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z40" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB40" t="n">
+      <c r="AE40" t="n">
         <v>1.73</v>
       </c>
-      <c r="AC40" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF40" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46078.89583333334</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,28 +5300,28 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="M41" t="n">
-        <v>3.44</v>
+        <v>3.79</v>
       </c>
       <c r="N41" t="n">
-        <v>3.37</v>
+        <v>5.14</v>
       </c>
       <c r="O41" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="P41" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="R41" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S41" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="T41" t="n">
         <v>2.8</v>
@@ -5336,37 +5336,37 @@
         <v>1.08</v>
       </c>
       <c r="X41" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD41" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z41" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD41" t="n">
+      <c r="AE41" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG41" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE41" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH41" t="n">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46078.89583333334</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46078.4375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46078.4375</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2321,77 +2321,77 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L16" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="M16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O16" t="n">
+        <v>5</v>
+      </c>
+      <c r="P16" t="n">
         <v>2.5</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="O16" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.15</v>
-      </c>
       <c r="Q16" t="n">
-        <v>3.28</v>
+        <v>1.89</v>
       </c>
       <c r="R16" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>2.77</v>
+        <v>3.66</v>
       </c>
       <c r="T16" t="n">
-        <v>2.93</v>
+        <v>2.2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.39</v>
+        <v>1.68</v>
       </c>
       <c r="V16" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.4</v>
+        <v>5.97</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.89</v>
+        <v>1.43</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.87</v>
+        <v>2.73</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.33</v>
+        <v>2.23</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.3</v>
+        <v>1.71</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.11</v>
+        <v>2.42</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>2.72</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46078.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.1</v>
+        <v>2.48</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="N17" t="n">
-        <v>2.2</v>
+        <v>3.07</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2483,16 +2483,16 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.37</v>
+        <v>3.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.48</v>
+        <v>3.1</v>
       </c>
       <c r="M18" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="N18" t="n">
-        <v>3.07</v>
+        <v>2.2</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2602,16 +2602,16 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.5</v>
+        <v>2.37</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5.93</v>
+        <v>2.5</v>
       </c>
       <c r="M19" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V19" t="n">
+        <v>6</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.44</v>
-      </c>
-      <c r="O19" t="n">
-        <v>5</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>5.97</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.11</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46078.625</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.56</v>
+        <v>2.44</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>2.72</v>
       </c>
       <c r="N25" t="n">
-        <v>6.45</v>
+        <v>3.11</v>
       </c>
       <c r="O25" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="P25" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Q25" t="n">
-        <v>7.1</v>
+        <v>3.75</v>
       </c>
       <c r="R25" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="S25" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="T25" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U25" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W25" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.65</v>
+        <v>5.25</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46078.6875</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="P26" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="R26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V26" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB26" t="n">
         <v>1.57</v>
       </c>
-      <c r="S26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V26" t="n">
-        <v>10</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AC26" t="n">
-        <v>5.25</v>
+        <v>4.26</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AF26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH26" t="n">
         <v>1.62</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46078.6875</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="O27" t="n">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="P27" t="n">
         <v>1.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.2</v>
+        <v>7.1</v>
       </c>
       <c r="R27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V27" t="n">
+        <v>9</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB27" t="n">
         <v>1.5</v>
       </c>
-      <c r="S27" t="n">
+      <c r="AC27" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE27" t="n">
         <v>2.4</v>
       </c>
-      <c r="T27" t="n">
-        <v>3</v>
-      </c>
-      <c r="U27" t="n">
+      <c r="AF27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG27" t="n">
         <v>1.3</v>
       </c>
-      <c r="V27" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH27" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46078.6875</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.24</v>
+        <v>2.41</v>
       </c>
       <c r="M28" t="n">
-        <v>6</v>
+        <v>3.34</v>
       </c>
       <c r="N28" t="n">
-        <v>10.5</v>
+        <v>2.83</v>
       </c>
       <c r="O28" t="n">
-        <v>1.66</v>
+        <v>2.87</v>
       </c>
       <c r="P28" t="n">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="Q28" t="n">
-        <v>8.4</v>
+        <v>3.25</v>
       </c>
       <c r="R28" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="S28" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="T28" t="n">
-        <v>2.22</v>
+        <v>2.8</v>
       </c>
       <c r="U28" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="V28" t="n">
-        <v>4.9</v>
+        <v>6.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X28" t="n">
         <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.5</v>
+        <v>1.93</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.62</v>
+        <v>1.77</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.6</v>
+        <v>1.29</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>3.6</v>
+        <v>1.53</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46078.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.28</v>
+        <v>1.24</v>
       </c>
       <c r="M29" t="n">
-        <v>3.68</v>
+        <v>6</v>
       </c>
       <c r="N29" t="n">
-        <v>2.8</v>
+        <v>10.5</v>
       </c>
       <c r="O29" t="n">
-        <v>2.75</v>
+        <v>1.66</v>
       </c>
       <c r="P29" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="Q29" t="n">
-        <v>3</v>
+        <v>8.4</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="S29" t="n">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="T29" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="U29" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="V29" t="n">
-        <v>5.25</v>
+        <v>4.9</v>
       </c>
       <c r="W29" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X29" t="n">
         <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.44</v>
+        <v>1.81</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46078.69791666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="M30" t="n">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="N30" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="O30" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="P30" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R30" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S30" t="n">
-        <v>2.8</v>
+        <v>3.22</v>
       </c>
       <c r="T30" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="U30" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="V30" t="n">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="W30" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X30" t="n">
         <v>1.03</v>
       </c>
       <c r="Y30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AG30" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH30" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46078.69791666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="M31" t="n">
-        <v>3.54</v>
+        <v>4.68</v>
       </c>
       <c r="N31" t="n">
-        <v>4.08</v>
+        <v>6.86</v>
       </c>
       <c r="O31" t="n">
-        <v>2.38</v>
+        <v>1.93</v>
       </c>
       <c r="P31" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T31" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3.22</v>
-      </c>
       <c r="U31" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="V31" t="n">
-        <v>8.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="W31" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="X31" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.8</v>
+        <v>5.25</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.92</v>
+        <v>2.2</v>
       </c>
       <c r="AD31" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG31" t="n">
         <v>1.18</v>
       </c>
-      <c r="AE31" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH31" t="n">
-        <v>1.95</v>
+        <v>2.81</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.33</v>
+        <v>1.85</v>
       </c>
       <c r="M33" t="n">
-        <v>6.14</v>
+        <v>3.54</v>
       </c>
       <c r="N33" t="n">
-        <v>9.85</v>
+        <v>4.08</v>
       </c>
       <c r="O33" t="n">
-        <v>1.58</v>
+        <v>2.38</v>
       </c>
       <c r="P33" t="n">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q33" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="R33" t="n">
-        <v>1.17</v>
+        <v>1.47</v>
       </c>
       <c r="S33" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="T33" t="n">
-        <v>1.85</v>
+        <v>3.22</v>
       </c>
       <c r="U33" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="V33" t="n">
-        <v>3.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W33" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="X33" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.07</v>
+        <v>1.4</v>
       </c>
       <c r="Z33" t="n">
-        <v>7.25</v>
+        <v>2.8</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="AB33" t="n">
-        <v>3.4</v>
+        <v>1.75</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.87</v>
+        <v>3.92</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.83</v>
+        <v>1.18</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.66</v>
+        <v>2.03</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AH33" t="n">
-        <v>3.7</v>
+        <v>1.95</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="M34" t="n">
-        <v>4.68</v>
+        <v>6.14</v>
       </c>
       <c r="N34" t="n">
-        <v>6.86</v>
+        <v>9.85</v>
       </c>
       <c r="O34" t="n">
-        <v>1.93</v>
+        <v>1.58</v>
       </c>
       <c r="P34" t="n">
-        <v>2.62</v>
+        <v>3.25</v>
       </c>
       <c r="Q34" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="R34" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="S34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V34" t="n">
         <v>3.6</v>
       </c>
-      <c r="T34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V34" t="n">
-        <v>4.5</v>
-      </c>
       <c r="W34" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Z34" t="n">
-        <v>5.25</v>
+        <v>7.25</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.61</v>
+        <v>1.29</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.81</v>
+        <v>3.7</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4550,22 +4550,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.97</v>
+        <v>2.17</v>
       </c>
       <c r="M36" t="n">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
       <c r="N36" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="O36" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="P36" t="n">
         <v>2.05</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="R36" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S36" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T36" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U36" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V36" t="n">
-        <v>7.75</v>
+        <v>8.5</v>
       </c>
       <c r="W36" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X36" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4788,22 +4788,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46078.79166666666</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,28 +5181,28 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="M40" t="n">
-        <v>3.44</v>
+        <v>3.79</v>
       </c>
       <c r="N40" t="n">
-        <v>3.37</v>
+        <v>5.14</v>
       </c>
       <c r="O40" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="P40" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="R40" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S40" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="T40" t="n">
         <v>2.8</v>
@@ -5217,37 +5217,37 @@
         <v>1.08</v>
       </c>
       <c r="X40" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD40" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z40" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD40" t="n">
+      <c r="AE40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG40" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE40" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH40" t="n">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46078.89583333334</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,28 +5300,28 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="M41" t="n">
-        <v>3.79</v>
+        <v>3.44</v>
       </c>
       <c r="N41" t="n">
-        <v>5.14</v>
+        <v>3.37</v>
       </c>
       <c r="O41" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="P41" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="R41" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S41" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="T41" t="n">
         <v>2.8</v>
@@ -5336,37 +5336,37 @@
         <v>1.08</v>
       </c>
       <c r="X41" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y41" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD41" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z41" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB41" t="n">
+      <c r="AE41" t="n">
         <v>1.73</v>
       </c>
-      <c r="AC41" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF41" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46078.89583333334</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46078.4375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46078.4375</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2321,77 +2321,77 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.93</v>
+        <v>2.5</v>
       </c>
       <c r="M16" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V16" t="n">
+        <v>6</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.44</v>
-      </c>
-      <c r="O16" t="n">
-        <v>5</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>5.97</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.11</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46078.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.48</v>
+        <v>3.1</v>
       </c>
       <c r="M17" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
-        <v>3.07</v>
+        <v>2.2</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2483,16 +2483,16 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.5</v>
+        <v>2.37</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.1</v>
+        <v>2.48</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="N18" t="n">
-        <v>2.2</v>
+        <v>3.07</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2602,16 +2602,16 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.37</v>
+        <v>3.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2678,77 +2678,77 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L19" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="M19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O19" t="n">
+        <v>5</v>
+      </c>
+      <c r="P19" t="n">
         <v>2.5</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="O19" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.15</v>
-      </c>
       <c r="Q19" t="n">
-        <v>3.28</v>
+        <v>1.89</v>
       </c>
       <c r="R19" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>2.77</v>
+        <v>3.66</v>
       </c>
       <c r="T19" t="n">
-        <v>2.93</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.39</v>
+        <v>1.68</v>
       </c>
       <c r="V19" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="W19" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.4</v>
+        <v>5.97</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.89</v>
+        <v>1.43</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.87</v>
+        <v>2.73</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.33</v>
+        <v>2.23</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.3</v>
+        <v>1.71</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.11</v>
+        <v>2.42</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>2.72</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46078.625</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="P25" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="R25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB25" t="n">
         <v>1.57</v>
       </c>
-      <c r="S25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V25" t="n">
-        <v>10</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AC25" t="n">
-        <v>5.25</v>
+        <v>4.26</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AF25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.62</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46078.6875</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="O26" t="n">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="P26" t="n">
         <v>1.95</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.2</v>
+        <v>7.1</v>
       </c>
       <c r="R26" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V26" t="n">
+        <v>9</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB26" t="n">
         <v>1.5</v>
       </c>
-      <c r="S26" t="n">
+      <c r="AC26" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE26" t="n">
         <v>2.4</v>
       </c>
-      <c r="T26" t="n">
-        <v>3</v>
-      </c>
-      <c r="U26" t="n">
+      <c r="AF26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG26" t="n">
         <v>1.3</v>
       </c>
-      <c r="V26" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH26" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46078.6875</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.56</v>
+        <v>2.44</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>2.72</v>
       </c>
       <c r="N27" t="n">
-        <v>6.45</v>
+        <v>3.11</v>
       </c>
       <c r="O27" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="P27" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Q27" t="n">
-        <v>7.1</v>
+        <v>3.75</v>
       </c>
       <c r="R27" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="S27" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="T27" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U27" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X27" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.65</v>
+        <v>5.25</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46078.6875</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.41</v>
+        <v>1.24</v>
       </c>
       <c r="M28" t="n">
-        <v>3.34</v>
+        <v>6</v>
       </c>
       <c r="N28" t="n">
-        <v>2.83</v>
+        <v>10.5</v>
       </c>
       <c r="O28" t="n">
-        <v>2.87</v>
+        <v>1.66</v>
       </c>
       <c r="P28" t="n">
-        <v>2.15</v>
+        <v>2.62</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.25</v>
+        <v>8.4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="S28" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="T28" t="n">
-        <v>2.8</v>
+        <v>2.22</v>
       </c>
       <c r="U28" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="V28" t="n">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
       <c r="W28" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X28" t="n">
         <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.2</v>
+        <v>5.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.93</v>
+        <v>1.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.77</v>
+        <v>2.62</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.29</v>
+        <v>1.6</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.53</v>
+        <v>3.6</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46078.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.24</v>
+        <v>2.28</v>
       </c>
       <c r="M29" t="n">
-        <v>6</v>
+        <v>3.68</v>
       </c>
       <c r="N29" t="n">
-        <v>10.5</v>
+        <v>2.8</v>
       </c>
       <c r="O29" t="n">
-        <v>1.66</v>
+        <v>2.75</v>
       </c>
       <c r="P29" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>8.4</v>
+        <v>3</v>
       </c>
       <c r="R29" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="S29" t="n">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="T29" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="U29" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="V29" t="n">
-        <v>4.9</v>
+        <v>5.25</v>
       </c>
       <c r="W29" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X29" t="n">
         <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z29" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA29" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD29" t="n">
         <v>1.5</v>
       </c>
-      <c r="AB29" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD29" t="n">
+      <c r="AE29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH29" t="n">
         <v>1.6</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>3.6</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46078.69791666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.28</v>
+        <v>2.41</v>
       </c>
       <c r="M30" t="n">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="N30" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S30" t="n">
         <v>2.8</v>
       </c>
-      <c r="O30" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3.22</v>
-      </c>
       <c r="T30" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="U30" t="n">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="V30" t="n">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
       <c r="W30" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X30" t="n">
         <v>1.03</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.44</v>
+        <v>1.93</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46078.69791666666</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="M32" t="n">
-        <v>4.58</v>
+        <v>6.14</v>
       </c>
       <c r="N32" t="n">
-        <v>5.49</v>
+        <v>9.85</v>
       </c>
       <c r="O32" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="P32" t="n">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="Q32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R32" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="S32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V32" t="n">
         <v>3.6</v>
       </c>
-      <c r="T32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V32" t="n">
-        <v>4.6</v>
-      </c>
       <c r="W32" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X32" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.3</v>
+        <v>7.25</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.63</v>
+        <v>1.29</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.45</v>
+        <v>3.7</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="M33" t="n">
-        <v>3.54</v>
+        <v>4.58</v>
       </c>
       <c r="N33" t="n">
-        <v>4.08</v>
+        <v>5.49</v>
       </c>
       <c r="O33" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="P33" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>5</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T33" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q33" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T33" t="n">
-        <v>3.22</v>
-      </c>
       <c r="U33" t="n">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="V33" t="n">
-        <v>8.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="W33" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="X33" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.4</v>
+        <v>1.09</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.92</v>
+        <v>2.2</v>
       </c>
       <c r="AD33" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG33" t="n">
         <v>1.18</v>
       </c>
-      <c r="AE33" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH33" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.33</v>
+        <v>1.85</v>
       </c>
       <c r="M34" t="n">
-        <v>6.14</v>
+        <v>3.54</v>
       </c>
       <c r="N34" t="n">
-        <v>9.85</v>
+        <v>4.08</v>
       </c>
       <c r="O34" t="n">
-        <v>1.58</v>
+        <v>2.38</v>
       </c>
       <c r="P34" t="n">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q34" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="R34" t="n">
-        <v>1.17</v>
+        <v>1.47</v>
       </c>
       <c r="S34" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="T34" t="n">
-        <v>1.85</v>
+        <v>3.22</v>
       </c>
       <c r="U34" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="V34" t="n">
-        <v>3.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W34" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="X34" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.07</v>
+        <v>1.4</v>
       </c>
       <c r="Z34" t="n">
-        <v>7.25</v>
+        <v>2.8</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="AB34" t="n">
-        <v>3.4</v>
+        <v>1.75</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.87</v>
+        <v>3.92</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.83</v>
+        <v>1.18</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.66</v>
+        <v>2.03</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>3.7</v>
+        <v>1.95</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4550,22 +4550,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4788,22 +4788,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46078.79166666666</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46078.4375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46078.4375</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2321,77 +2321,77 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="N16" t="n">
-        <v>2.69</v>
+        <v>3.07</v>
       </c>
       <c r="O16" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.4</v>
+        <v>1.93</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.89</v>
+        <v>3.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.87</v>
+        <v>1.28</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46078.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2559,77 +2559,77 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.48</v>
+        <v>5.93</v>
       </c>
       <c r="M18" t="n">
-        <v>2.7</v>
+        <v>4.4</v>
       </c>
       <c r="N18" t="n">
-        <v>3.07</v>
+        <v>1.44</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.75</v>
+        <v>1.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.93</v>
+        <v>5.97</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.5</v>
+        <v>1.43</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.28</v>
+        <v>2.73</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46078.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5.93</v>
+        <v>2.5</v>
       </c>
       <c r="M19" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V19" t="n">
+        <v>6</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.44</v>
-      </c>
-      <c r="O19" t="n">
-        <v>5</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>5.97</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.11</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46078.625</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="M31" t="n">
-        <v>4.68</v>
+        <v>6.14</v>
       </c>
       <c r="N31" t="n">
-        <v>6.86</v>
+        <v>9.85</v>
       </c>
       <c r="O31" t="n">
-        <v>1.93</v>
+        <v>1.58</v>
       </c>
       <c r="P31" t="n">
-        <v>2.62</v>
+        <v>3.25</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="R31" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="S31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V31" t="n">
         <v>3.6</v>
       </c>
-      <c r="T31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V31" t="n">
-        <v>4.5</v>
-      </c>
       <c r="W31" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.25</v>
+        <v>7.25</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.61</v>
+        <v>1.29</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.81</v>
+        <v>3.7</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.33</v>
+        <v>1.85</v>
       </c>
       <c r="M32" t="n">
-        <v>6.14</v>
+        <v>3.54</v>
       </c>
       <c r="N32" t="n">
-        <v>9.85</v>
+        <v>4.08</v>
       </c>
       <c r="O32" t="n">
-        <v>1.58</v>
+        <v>2.38</v>
       </c>
       <c r="P32" t="n">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="R32" t="n">
-        <v>1.17</v>
+        <v>1.47</v>
       </c>
       <c r="S32" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="T32" t="n">
-        <v>1.85</v>
+        <v>3.22</v>
       </c>
       <c r="U32" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="V32" t="n">
-        <v>3.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W32" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="X32" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.07</v>
+        <v>1.4</v>
       </c>
       <c r="Z32" t="n">
-        <v>7.25</v>
+        <v>2.8</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="AB32" t="n">
-        <v>3.4</v>
+        <v>1.75</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.87</v>
+        <v>3.92</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.83</v>
+        <v>1.18</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.66</v>
+        <v>2.03</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>3.7</v>
+        <v>1.95</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,22 +4348,22 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="M33" t="n">
-        <v>4.58</v>
+        <v>4.68</v>
       </c>
       <c r="N33" t="n">
-        <v>5.49</v>
+        <v>6.86</v>
       </c>
       <c r="O33" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="P33" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="Q33" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="R33" t="n">
         <v>1.23</v>
@@ -4375,10 +4375,10 @@
         <v>2.1</v>
       </c>
       <c r="U33" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="V33" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="W33" t="n">
         <v>1.17</v>
@@ -4387,13 +4387,13 @@
         <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AB33" t="n">
         <v>2.15</v>
@@ -4405,16 +4405,16 @@
         <v>1.63</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AG33" t="n">
         <v>1.18</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.45</v>
+        <v>2.81</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="M34" t="n">
-        <v>3.54</v>
+        <v>4.58</v>
       </c>
       <c r="N34" t="n">
-        <v>4.08</v>
+        <v>5.49</v>
       </c>
       <c r="O34" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="P34" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>5</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T34" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q34" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T34" t="n">
-        <v>3.22</v>
-      </c>
       <c r="U34" t="n">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="V34" t="n">
-        <v>8.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="W34" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="X34" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.4</v>
+        <v>1.09</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.92</v>
+        <v>2.2</v>
       </c>
       <c r="AD34" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG34" t="n">
         <v>1.18</v>
       </c>
-      <c r="AE34" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH34" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4550,22 +4550,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.17</v>
+        <v>2.97</v>
       </c>
       <c r="M36" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="N36" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="O36" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="P36" t="n">
         <v>2.05</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="R36" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S36" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T36" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V36" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG36" t="n">
         <v>1.33</v>
       </c>
-      <c r="V36" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH36" t="n">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4788,22 +4788,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46078.79166666666</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46078.4375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46078.4375</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2440,77 +2440,77 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.1</v>
+        <v>5.93</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="N17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O17" t="n">
+        <v>5</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="T17" t="n">
         <v>2.2</v>
       </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.37</v>
+        <v>1.43</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.53</v>
+        <v>2.73</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46078.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2559,77 +2559,77 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>5.93</v>
+        <v>3.1</v>
       </c>
       <c r="M18" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="N18" t="n">
-        <v>1.44</v>
+        <v>2.2</v>
       </c>
       <c r="O18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.97</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.43</v>
+        <v>2.37</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.73</v>
+        <v>1.53</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46078.625</v>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="O25" t="n">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="P25" t="n">
         <v>1.95</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.2</v>
+        <v>7.1</v>
       </c>
       <c r="R25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V25" t="n">
+        <v>9</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB25" t="n">
         <v>1.5</v>
       </c>
-      <c r="S25" t="n">
+      <c r="AC25" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE25" t="n">
         <v>2.4</v>
       </c>
-      <c r="T25" t="n">
-        <v>3</v>
-      </c>
-      <c r="U25" t="n">
+      <c r="AF25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG25" t="n">
         <v>1.3</v>
       </c>
-      <c r="V25" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH25" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46078.6875</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.56</v>
+        <v>2.44</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>2.72</v>
       </c>
       <c r="N26" t="n">
-        <v>6.45</v>
+        <v>3.11</v>
       </c>
       <c r="O26" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="P26" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Q26" t="n">
-        <v>7.1</v>
+        <v>3.75</v>
       </c>
       <c r="R26" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="S26" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="T26" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U26" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W26" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X26" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.65</v>
+        <v>5.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46078.6875</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="P27" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="R27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V27" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB27" t="n">
         <v>1.57</v>
       </c>
-      <c r="S27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V27" t="n">
-        <v>10</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AC27" t="n">
-        <v>5.25</v>
+        <v>4.26</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AF27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.62</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46078.6875</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.24</v>
+        <v>2.41</v>
       </c>
       <c r="M28" t="n">
-        <v>6</v>
+        <v>3.34</v>
       </c>
       <c r="N28" t="n">
-        <v>10.5</v>
+        <v>2.83</v>
       </c>
       <c r="O28" t="n">
-        <v>1.66</v>
+        <v>2.87</v>
       </c>
       <c r="P28" t="n">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="Q28" t="n">
-        <v>8.4</v>
+        <v>3.25</v>
       </c>
       <c r="R28" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="S28" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="T28" t="n">
-        <v>2.22</v>
+        <v>2.8</v>
       </c>
       <c r="U28" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="V28" t="n">
-        <v>4.9</v>
+        <v>6.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X28" t="n">
         <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.5</v>
+        <v>1.93</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.62</v>
+        <v>1.77</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.6</v>
+        <v>1.29</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>3.6</v>
+        <v>1.53</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46078.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.28</v>
+        <v>1.24</v>
       </c>
       <c r="M29" t="n">
-        <v>3.68</v>
+        <v>6</v>
       </c>
       <c r="N29" t="n">
-        <v>2.8</v>
+        <v>10.5</v>
       </c>
       <c r="O29" t="n">
-        <v>2.75</v>
+        <v>1.66</v>
       </c>
       <c r="P29" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="Q29" t="n">
-        <v>3</v>
+        <v>8.4</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="S29" t="n">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="T29" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="U29" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="V29" t="n">
-        <v>5.25</v>
+        <v>4.9</v>
       </c>
       <c r="W29" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X29" t="n">
         <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.44</v>
+        <v>1.81</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46078.69791666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="M30" t="n">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="N30" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="O30" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="P30" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R30" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S30" t="n">
-        <v>2.8</v>
+        <v>3.22</v>
       </c>
       <c r="T30" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="U30" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="V30" t="n">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="W30" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X30" t="n">
         <v>1.03</v>
       </c>
       <c r="Y30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AG30" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH30" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46078.69791666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.33</v>
+        <v>1.85</v>
       </c>
       <c r="M31" t="n">
-        <v>6.14</v>
+        <v>3.54</v>
       </c>
       <c r="N31" t="n">
-        <v>9.85</v>
+        <v>4.08</v>
       </c>
       <c r="O31" t="n">
-        <v>1.58</v>
+        <v>2.38</v>
       </c>
       <c r="P31" t="n">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="R31" t="n">
-        <v>1.17</v>
+        <v>1.47</v>
       </c>
       <c r="S31" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="T31" t="n">
-        <v>1.85</v>
+        <v>3.22</v>
       </c>
       <c r="U31" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="V31" t="n">
-        <v>3.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W31" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="X31" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.07</v>
+        <v>1.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>7.25</v>
+        <v>2.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="AB31" t="n">
-        <v>3.4</v>
+        <v>1.75</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.87</v>
+        <v>3.92</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.83</v>
+        <v>1.18</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.66</v>
+        <v>2.03</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>3.7</v>
+        <v>1.95</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="M32" t="n">
-        <v>3.54</v>
+        <v>4.68</v>
       </c>
       <c r="N32" t="n">
-        <v>4.08</v>
+        <v>6.86</v>
       </c>
       <c r="O32" t="n">
-        <v>2.38</v>
+        <v>1.93</v>
       </c>
       <c r="P32" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T32" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3.22</v>
-      </c>
       <c r="U32" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="V32" t="n">
-        <v>8.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="W32" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="X32" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.8</v>
+        <v>5.25</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.92</v>
+        <v>2.2</v>
       </c>
       <c r="AD32" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG32" t="n">
         <v>1.18</v>
       </c>
-      <c r="AE32" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH32" t="n">
-        <v>1.95</v>
+        <v>2.81</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="M33" t="n">
-        <v>4.68</v>
+        <v>6.14</v>
       </c>
       <c r="N33" t="n">
-        <v>6.86</v>
+        <v>9.85</v>
       </c>
       <c r="O33" t="n">
-        <v>1.93</v>
+        <v>1.58</v>
       </c>
       <c r="P33" t="n">
-        <v>2.62</v>
+        <v>3.25</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="R33" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="S33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V33" t="n">
         <v>3.6</v>
       </c>
-      <c r="T33" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V33" t="n">
-        <v>4.5</v>
-      </c>
       <c r="W33" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.25</v>
+        <v>7.25</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.61</v>
+        <v>1.29</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.81</v>
+        <v>3.7</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.17</v>
+        <v>2.97</v>
       </c>
       <c r="M35" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="N35" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="O35" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="P35" t="n">
         <v>2.05</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="R35" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S35" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T35" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V35" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG35" t="n">
         <v>1.33</v>
       </c>
-      <c r="V35" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH35" t="n">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4788,22 +4788,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46078.79166666666</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46078.4375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46078.4375</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2321,77 +2321,77 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="M16" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>3.07</v>
+        <v>2.69</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.93</v>
+        <v>3.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.5</v>
+        <v>1.89</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.28</v>
+        <v>1.87</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46078.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2440,77 +2440,77 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5.93</v>
+        <v>3.1</v>
       </c>
       <c r="M17" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
-        <v>1.44</v>
+        <v>2.2</v>
       </c>
       <c r="O17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.97</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.43</v>
+        <v>2.37</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.73</v>
+        <v>1.53</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46078.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2559,77 +2559,77 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.1</v>
+        <v>5.93</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="N18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O18" t="n">
+        <v>5</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="T18" t="n">
         <v>2.2</v>
       </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.37</v>
+        <v>1.43</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.53</v>
+        <v>2.73</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46078.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2678,77 +2678,77 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="N19" t="n">
-        <v>2.69</v>
+        <v>3.07</v>
       </c>
       <c r="O19" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.4</v>
+        <v>1.93</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.89</v>
+        <v>3.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.87</v>
+        <v>1.28</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46078.625</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="P26" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="R26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V26" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB26" t="n">
         <v>1.57</v>
       </c>
-      <c r="S26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V26" t="n">
-        <v>10</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AC26" t="n">
-        <v>5.25</v>
+        <v>4.26</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AF26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH26" t="n">
         <v>1.62</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46078.6875</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O27" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="P27" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="R27" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S27" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="T27" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="U27" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V27" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="W27" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X27" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.26</v>
+        <v>5.25</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46078.6875</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.41</v>
+        <v>1.24</v>
       </c>
       <c r="M28" t="n">
-        <v>3.34</v>
+        <v>6</v>
       </c>
       <c r="N28" t="n">
-        <v>2.83</v>
+        <v>10.5</v>
       </c>
       <c r="O28" t="n">
-        <v>2.87</v>
+        <v>1.66</v>
       </c>
       <c r="P28" t="n">
-        <v>2.15</v>
+        <v>2.62</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.25</v>
+        <v>8.4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="S28" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="T28" t="n">
-        <v>2.8</v>
+        <v>2.22</v>
       </c>
       <c r="U28" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="V28" t="n">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
       <c r="W28" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X28" t="n">
         <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.2</v>
+        <v>5.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.93</v>
+        <v>1.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.77</v>
+        <v>2.62</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.29</v>
+        <v>1.6</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.53</v>
+        <v>3.6</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46078.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.24</v>
+        <v>2.41</v>
       </c>
       <c r="M29" t="n">
-        <v>6</v>
+        <v>3.34</v>
       </c>
       <c r="N29" t="n">
-        <v>10.5</v>
+        <v>2.83</v>
       </c>
       <c r="O29" t="n">
-        <v>1.66</v>
+        <v>2.87</v>
       </c>
       <c r="P29" t="n">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="Q29" t="n">
-        <v>8.4</v>
+        <v>3.25</v>
       </c>
       <c r="R29" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="S29" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="T29" t="n">
-        <v>2.22</v>
+        <v>2.8</v>
       </c>
       <c r="U29" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="V29" t="n">
-        <v>4.9</v>
+        <v>6.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
         <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>5.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.5</v>
+        <v>1.93</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.62</v>
+        <v>1.77</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.6</v>
+        <v>1.29</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>3.6</v>
+        <v>1.53</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46078.69791666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="M31" t="n">
-        <v>3.54</v>
+        <v>4.68</v>
       </c>
       <c r="N31" t="n">
-        <v>4.08</v>
+        <v>6.86</v>
       </c>
       <c r="O31" t="n">
-        <v>2.38</v>
+        <v>1.93</v>
       </c>
       <c r="P31" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T31" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3.22</v>
-      </c>
       <c r="U31" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="V31" t="n">
-        <v>8.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="W31" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="X31" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.8</v>
+        <v>5.25</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.92</v>
+        <v>2.2</v>
       </c>
       <c r="AD31" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG31" t="n">
         <v>1.18</v>
       </c>
-      <c r="AE31" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH31" t="n">
-        <v>1.95</v>
+        <v>2.81</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="M32" t="n">
-        <v>4.68</v>
+        <v>3.54</v>
       </c>
       <c r="N32" t="n">
-        <v>6.86</v>
+        <v>4.08</v>
       </c>
       <c r="O32" t="n">
-        <v>1.93</v>
+        <v>2.38</v>
       </c>
       <c r="P32" t="n">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="R32" t="n">
-        <v>1.23</v>
+        <v>1.47</v>
       </c>
       <c r="S32" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="T32" t="n">
-        <v>2.1</v>
+        <v>3.22</v>
       </c>
       <c r="U32" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="V32" t="n">
-        <v>4.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W32" t="n">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="X32" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.25</v>
+        <v>2.8</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.2</v>
+        <v>3.92</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.63</v>
+        <v>1.18</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.65</v>
+        <v>2.03</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.81</v>
+        <v>1.95</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="M33" t="n">
-        <v>6.14</v>
+        <v>4.58</v>
       </c>
       <c r="N33" t="n">
-        <v>9.85</v>
+        <v>5.49</v>
       </c>
       <c r="O33" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="P33" t="n">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="Q33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R33" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V33" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W33" t="n">
         <v>1.17</v>
       </c>
-      <c r="S33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V33" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.25</v>
-      </c>
       <c r="X33" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Z33" t="n">
-        <v>7.25</v>
+        <v>5.3</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.29</v>
+        <v>1.63</v>
       </c>
       <c r="AB33" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AH33" t="n">
-        <v>3.7</v>
+        <v>2.45</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="M34" t="n">
-        <v>4.58</v>
+        <v>6.14</v>
       </c>
       <c r="N34" t="n">
-        <v>5.49</v>
+        <v>9.85</v>
       </c>
       <c r="O34" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="P34" t="n">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="Q34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R34" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="S34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V34" t="n">
         <v>3.6</v>
       </c>
-      <c r="T34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V34" t="n">
-        <v>4.6</v>
-      </c>
       <c r="W34" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Z34" t="n">
-        <v>5.3</v>
+        <v>7.25</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.63</v>
+        <v>1.29</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.45</v>
+        <v>3.7</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.97</v>
+        <v>2.17</v>
       </c>
       <c r="M35" t="n">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
       <c r="N35" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="O35" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="P35" t="n">
         <v>2.05</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="R35" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S35" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T35" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U35" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V35" t="n">
-        <v>7.75</v>
+        <v>8.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X35" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.17</v>
+        <v>2.97</v>
       </c>
       <c r="M37" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="N37" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="O37" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="P37" t="n">
         <v>2.05</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="R37" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S37" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T37" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V37" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG37" t="n">
         <v>1.33</v>
       </c>
-      <c r="V37" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH37" t="n">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46078.79166666666</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,28 +5181,28 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="M40" t="n">
-        <v>3.79</v>
+        <v>3.44</v>
       </c>
       <c r="N40" t="n">
-        <v>5.14</v>
+        <v>3.37</v>
       </c>
       <c r="O40" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="P40" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="R40" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S40" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="T40" t="n">
         <v>2.8</v>
@@ -5217,37 +5217,37 @@
         <v>1.08</v>
       </c>
       <c r="X40" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD40" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z40" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB40" t="n">
+      <c r="AE40" t="n">
         <v>1.73</v>
       </c>
-      <c r="AC40" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF40" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46078.89583333334</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,28 +5300,28 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="M41" t="n">
-        <v>3.44</v>
+        <v>3.79</v>
       </c>
       <c r="N41" t="n">
-        <v>3.37</v>
+        <v>5.14</v>
       </c>
       <c r="O41" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="P41" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="R41" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S41" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="T41" t="n">
         <v>2.8</v>
@@ -5336,37 +5336,37 @@
         <v>1.08</v>
       </c>
       <c r="X41" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD41" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z41" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD41" t="n">
+      <c r="AE41" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG41" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE41" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH41" t="n">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46078.89583333334</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="M16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O16" t="n">
+        <v>5</v>
+      </c>
+      <c r="P16" t="n">
         <v>2.5</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="O16" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.15</v>
-      </c>
       <c r="Q16" t="n">
-        <v>3.28</v>
+        <v>1.89</v>
       </c>
       <c r="R16" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>2.77</v>
+        <v>3.66</v>
       </c>
       <c r="T16" t="n">
-        <v>2.93</v>
+        <v>2.2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.39</v>
+        <v>1.68</v>
       </c>
       <c r="V16" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.4</v>
+        <v>5.97</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.89</v>
+        <v>1.43</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.87</v>
+        <v>2.73</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.33</v>
+        <v>2.23</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.3</v>
+        <v>1.71</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.11</v>
+        <v>2.42</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>2.72</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46078.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>5.93</v>
+        <v>2.5</v>
       </c>
       <c r="M18" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V18" t="n">
+        <v>6</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.44</v>
-      </c>
-      <c r="O18" t="n">
-        <v>5</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>5.97</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.11</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46078.625</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3167,64 +3167,64 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>8</v>
+        <v>3.34</v>
       </c>
       <c r="P23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z23" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q23" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S23" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V23" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>7.7</v>
-      </c>
       <c r="AA23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.25</v>
       </c>
-      <c r="AB23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AC23" t="n">
+      <c r="AE23" t="n">
         <v>1.75</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AF23" t="n">
         <v>1.95</v>
       </c>
-      <c r="AE23" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AG23" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46078.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3286,64 +3286,64 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3.34</v>
+        <v>8</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.8</v>
+        <v>1.45</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="S24" t="n">
-        <v>2.62</v>
+        <v>5.1</v>
       </c>
       <c r="T24" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="U24" t="n">
-        <v>1.33</v>
+        <v>1.9</v>
       </c>
       <c r="V24" t="n">
-        <v>6.75</v>
+        <v>3.42</v>
       </c>
       <c r="W24" t="n">
-        <v>1.02</v>
+        <v>1.23</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.3</v>
+        <v>1.06</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.1</v>
+        <v>7.7</v>
       </c>
       <c r="AA24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD24" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB24" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE24" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.38</v>
+        <v>1.04</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46078.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="P25" t="n">
         <v>1.95</v>
       </c>
       <c r="Q25" t="n">
-        <v>7.1</v>
+        <v>4.2</v>
       </c>
       <c r="R25" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="S25" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="T25" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U25" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V25" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X25" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.65</v>
+        <v>4.26</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46078.6875</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O26" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="P26" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="R26" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S26" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="T26" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="U26" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V26" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="W26" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X26" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.26</v>
+        <v>5.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46078.6875</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.44</v>
+        <v>1.56</v>
       </c>
       <c r="M27" t="n">
-        <v>2.72</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>3.11</v>
+        <v>6.45</v>
       </c>
       <c r="O27" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T27" t="n">
         <v>3.4</v>
       </c>
-      <c r="P27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3.6</v>
-      </c>
       <c r="U27" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W27" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>5.25</v>
+        <v>4.65</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46078.6875</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.24</v>
+        <v>2.41</v>
       </c>
       <c r="M28" t="n">
-        <v>6</v>
+        <v>3.34</v>
       </c>
       <c r="N28" t="n">
-        <v>10.5</v>
+        <v>2.83</v>
       </c>
       <c r="O28" t="n">
-        <v>1.66</v>
+        <v>2.87</v>
       </c>
       <c r="P28" t="n">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="Q28" t="n">
-        <v>8.4</v>
+        <v>3.25</v>
       </c>
       <c r="R28" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="S28" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="T28" t="n">
-        <v>2.22</v>
+        <v>2.8</v>
       </c>
       <c r="U28" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="V28" t="n">
-        <v>4.9</v>
+        <v>6.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X28" t="n">
         <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.5</v>
+        <v>1.93</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.62</v>
+        <v>1.77</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.6</v>
+        <v>1.29</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>3.6</v>
+        <v>1.53</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46078.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="M29" t="n">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="N29" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="O29" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="P29" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R29" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S29" t="n">
-        <v>2.8</v>
+        <v>3.22</v>
       </c>
       <c r="T29" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="U29" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="V29" t="n">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="W29" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X29" t="n">
         <v>1.03</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AG29" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH29" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46078.69791666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.28</v>
+        <v>1.24</v>
       </c>
       <c r="M30" t="n">
-        <v>3.68</v>
+        <v>6</v>
       </c>
       <c r="N30" t="n">
-        <v>2.8</v>
+        <v>10.5</v>
       </c>
       <c r="O30" t="n">
-        <v>2.75</v>
+        <v>1.66</v>
       </c>
       <c r="P30" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="Q30" t="n">
-        <v>3</v>
+        <v>8.4</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="S30" t="n">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="T30" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="U30" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="V30" t="n">
-        <v>5.25</v>
+        <v>4.9</v>
       </c>
       <c r="W30" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X30" t="n">
         <v>1.03</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.44</v>
+        <v>1.81</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46078.69791666666</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="M33" t="n">
-        <v>4.58</v>
+        <v>6.14</v>
       </c>
       <c r="N33" t="n">
-        <v>5.49</v>
+        <v>9.85</v>
       </c>
       <c r="O33" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="P33" t="n">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="Q33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R33" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="S33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V33" t="n">
         <v>3.6</v>
       </c>
-      <c r="T33" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V33" t="n">
-        <v>4.6</v>
-      </c>
       <c r="W33" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.3</v>
+        <v>7.25</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.63</v>
+        <v>1.29</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.45</v>
+        <v>3.7</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="M34" t="n">
-        <v>6.14</v>
+        <v>4.58</v>
       </c>
       <c r="N34" t="n">
-        <v>9.85</v>
+        <v>5.49</v>
       </c>
       <c r="O34" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="P34" t="n">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="Q34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R34" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V34" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W34" t="n">
         <v>1.17</v>
       </c>
-      <c r="S34" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T34" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V34" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.25</v>
-      </c>
       <c r="X34" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Z34" t="n">
-        <v>7.25</v>
+        <v>5.3</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.29</v>
+        <v>1.63</v>
       </c>
       <c r="AB34" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AH34" t="n">
-        <v>3.7</v>
+        <v>2.45</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.17</v>
+        <v>2.97</v>
       </c>
       <c r="M35" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="N35" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="O35" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="P35" t="n">
         <v>2.05</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="R35" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S35" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T35" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V35" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG35" t="n">
         <v>1.33</v>
       </c>
-      <c r="V35" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH35" t="n">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.97</v>
+        <v>2.17</v>
       </c>
       <c r="M37" t="n">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
       <c r="N37" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="O37" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="P37" t="n">
         <v>2.05</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="R37" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S37" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T37" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U37" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V37" t="n">
-        <v>7.75</v>
+        <v>8.5</v>
       </c>
       <c r="W37" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X37" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46078.79166666666</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3167,64 +3167,64 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>3.34</v>
+        <v>8</v>
       </c>
       <c r="P23" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.8</v>
+        <v>1.45</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="S23" t="n">
-        <v>2.62</v>
+        <v>5.1</v>
       </c>
       <c r="T23" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="U23" t="n">
-        <v>1.33</v>
+        <v>1.9</v>
       </c>
       <c r="V23" t="n">
-        <v>6.75</v>
+        <v>3.42</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>1.23</v>
       </c>
       <c r="X23" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.3</v>
+        <v>1.06</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.1</v>
+        <v>7.7</v>
       </c>
       <c r="AA23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB23" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE23" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.38</v>
+        <v>1.04</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46078.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3286,64 +3286,64 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>8</v>
+        <v>3.34</v>
       </c>
       <c r="P24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V24" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z24" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q24" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S24" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V24" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>7.7</v>
-      </c>
       <c r="AA24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD24" t="n">
         <v>1.25</v>
       </c>
-      <c r="AB24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AC24" t="n">
+      <c r="AE24" t="n">
         <v>1.75</v>
       </c>
-      <c r="AD24" t="n">
+      <c r="AF24" t="n">
         <v>1.95</v>
       </c>
-      <c r="AE24" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AG24" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46078.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O25" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="P25" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S25" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="T25" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="U25" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V25" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="W25" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.26</v>
+        <v>5.25</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46078.6875</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="P26" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="R26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V26" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB26" t="n">
         <v>1.57</v>
       </c>
-      <c r="S26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V26" t="n">
-        <v>10</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AC26" t="n">
-        <v>5.25</v>
+        <v>4.26</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AF26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH26" t="n">
         <v>1.62</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46078.6875</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.41</v>
+        <v>1.24</v>
       </c>
       <c r="M28" t="n">
-        <v>3.34</v>
+        <v>6</v>
       </c>
       <c r="N28" t="n">
-        <v>2.83</v>
+        <v>10.5</v>
       </c>
       <c r="O28" t="n">
-        <v>2.87</v>
+        <v>1.66</v>
       </c>
       <c r="P28" t="n">
-        <v>2.15</v>
+        <v>2.62</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.25</v>
+        <v>8.4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="S28" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="T28" t="n">
-        <v>2.8</v>
+        <v>2.22</v>
       </c>
       <c r="U28" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="V28" t="n">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
       <c r="W28" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X28" t="n">
         <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.2</v>
+        <v>5.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.93</v>
+        <v>1.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.77</v>
+        <v>2.62</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.29</v>
+        <v>1.6</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.53</v>
+        <v>3.6</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46078.69791666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.24</v>
+        <v>2.41</v>
       </c>
       <c r="M30" t="n">
-        <v>6</v>
+        <v>3.34</v>
       </c>
       <c r="N30" t="n">
-        <v>10.5</v>
+        <v>2.83</v>
       </c>
       <c r="O30" t="n">
-        <v>1.66</v>
+        <v>2.87</v>
       </c>
       <c r="P30" t="n">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="Q30" t="n">
-        <v>8.4</v>
+        <v>3.25</v>
       </c>
       <c r="R30" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="S30" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="T30" t="n">
-        <v>2.22</v>
+        <v>2.8</v>
       </c>
       <c r="U30" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="V30" t="n">
-        <v>4.9</v>
+        <v>6.5</v>
       </c>
       <c r="W30" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X30" t="n">
         <v>1.03</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="Z30" t="n">
-        <v>5.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.5</v>
+        <v>1.93</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.62</v>
+        <v>1.77</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.6</v>
+        <v>1.29</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>3.6</v>
+        <v>1.53</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46078.69791666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="M31" t="n">
-        <v>4.68</v>
+        <v>3.54</v>
       </c>
       <c r="N31" t="n">
-        <v>6.86</v>
+        <v>4.08</v>
       </c>
       <c r="O31" t="n">
-        <v>1.93</v>
+        <v>2.38</v>
       </c>
       <c r="P31" t="n">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="R31" t="n">
-        <v>1.23</v>
+        <v>1.47</v>
       </c>
       <c r="S31" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="T31" t="n">
-        <v>2.1</v>
+        <v>3.22</v>
       </c>
       <c r="U31" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="V31" t="n">
-        <v>4.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W31" t="n">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.25</v>
+        <v>2.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.2</v>
+        <v>3.92</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.63</v>
+        <v>1.18</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.65</v>
+        <v>2.03</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.81</v>
+        <v>1.95</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M32" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="N32" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="P32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>6</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T32" t="n">
         <v>1.85</v>
       </c>
-      <c r="M32" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="N32" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="O32" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3.22</v>
-      </c>
       <c r="U32" t="n">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="V32" t="n">
-        <v>8.199999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="W32" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="X32" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.4</v>
+        <v>1.07</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.8</v>
+        <v>7.25</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.95</v>
+        <v>1.29</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.75</v>
+        <v>3.4</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.92</v>
+        <v>1.87</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.18</v>
+        <v>1.83</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.03</v>
+        <v>1.66</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.95</v>
+        <v>3.7</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="M33" t="n">
-        <v>6.14</v>
+        <v>4.58</v>
       </c>
       <c r="N33" t="n">
-        <v>9.85</v>
+        <v>5.49</v>
       </c>
       <c r="O33" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="P33" t="n">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="Q33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R33" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V33" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W33" t="n">
         <v>1.17</v>
       </c>
-      <c r="S33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V33" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.25</v>
-      </c>
       <c r="X33" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Z33" t="n">
-        <v>7.25</v>
+        <v>5.3</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.29</v>
+        <v>1.63</v>
       </c>
       <c r="AB33" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AH33" t="n">
-        <v>3.7</v>
+        <v>2.45</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,22 +4467,22 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="M34" t="n">
-        <v>4.58</v>
+        <v>4.68</v>
       </c>
       <c r="N34" t="n">
-        <v>5.49</v>
+        <v>6.86</v>
       </c>
       <c r="O34" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="P34" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="Q34" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="R34" t="n">
         <v>1.23</v>
@@ -4494,10 +4494,10 @@
         <v>2.1</v>
       </c>
       <c r="U34" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="V34" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="W34" t="n">
         <v>1.17</v>
@@ -4506,13 +4506,13 @@
         <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z34" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AB34" t="n">
         <v>2.15</v>
@@ -4524,16 +4524,16 @@
         <v>1.63</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AG34" t="n">
         <v>1.18</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.45</v>
+        <v>2.81</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.97</v>
+        <v>2.17</v>
       </c>
       <c r="M35" t="n">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
       <c r="N35" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="O35" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="P35" t="n">
         <v>2.05</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="R35" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S35" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T35" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U35" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V35" t="n">
-        <v>7.75</v>
+        <v>8.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X35" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4788,22 +4788,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46078.79166666666</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,28 +5181,28 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="M40" t="n">
-        <v>3.44</v>
+        <v>3.79</v>
       </c>
       <c r="N40" t="n">
-        <v>3.37</v>
+        <v>5.14</v>
       </c>
       <c r="O40" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="P40" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="R40" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S40" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="T40" t="n">
         <v>2.8</v>
@@ -5217,37 +5217,37 @@
         <v>1.08</v>
       </c>
       <c r="X40" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD40" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z40" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD40" t="n">
+      <c r="AE40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG40" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE40" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH40" t="n">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46078.89583333334</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,28 +5300,28 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="M41" t="n">
-        <v>3.79</v>
+        <v>3.44</v>
       </c>
       <c r="N41" t="n">
-        <v>5.14</v>
+        <v>3.37</v>
       </c>
       <c r="O41" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="P41" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="R41" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S41" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="T41" t="n">
         <v>2.8</v>
@@ -5336,37 +5336,37 @@
         <v>1.08</v>
       </c>
       <c r="X41" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y41" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD41" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z41" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB41" t="n">
+      <c r="AE41" t="n">
         <v>1.73</v>
       </c>
-      <c r="AC41" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF41" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46078.89583333334</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46078.4375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46078.4375</v>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="M15" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="N15" t="n">
-        <v>3.41</v>
+        <v>3.3</v>
       </c>
       <c r="O15" t="n">
         <v>2.62</v>
@@ -2221,7 +2221,7 @@
         <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="R15" t="n">
         <v>1.3</v>
@@ -2251,10 +2251,10 @@
         <v>4.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AC15" t="n">
         <v>2.62</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2321,77 +2321,77 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.93</v>
+        <v>3.1</v>
       </c>
       <c r="M16" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="N16" t="n">
-        <v>1.44</v>
+        <v>2.2</v>
       </c>
       <c r="O16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.97</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.43</v>
+        <v>2.37</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.73</v>
+        <v>1.53</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46078.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2440,77 +2440,77 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.1</v>
+        <v>5.93</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="N17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O17" t="n">
+        <v>5</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="T17" t="n">
         <v>2.2</v>
       </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.37</v>
+        <v>1.43</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.53</v>
+        <v>2.73</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46078.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2559,77 +2559,77 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="N18" t="n">
-        <v>2.69</v>
+        <v>3.07</v>
       </c>
       <c r="O18" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.4</v>
+        <v>1.93</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.89</v>
+        <v>3.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.87</v>
+        <v>1.28</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46078.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2678,77 +2678,77 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="M19" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>3.07</v>
+        <v>2.69</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.93</v>
+        <v>3.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.5</v>
+        <v>1.89</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.28</v>
+        <v>1.87</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46078.625</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3167,64 +3167,64 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>8</v>
+        <v>3.34</v>
       </c>
       <c r="P23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z23" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q23" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S23" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V23" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>7.7</v>
-      </c>
       <c r="AA23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.25</v>
       </c>
-      <c r="AB23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AC23" t="n">
+      <c r="AE23" t="n">
         <v>1.75</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AF23" t="n">
         <v>1.95</v>
       </c>
-      <c r="AE23" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AG23" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46078.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3286,64 +3286,64 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3.34</v>
+        <v>8</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.8</v>
+        <v>1.45</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="S24" t="n">
-        <v>2.62</v>
+        <v>5.1</v>
       </c>
       <c r="T24" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="U24" t="n">
-        <v>1.33</v>
+        <v>1.9</v>
       </c>
       <c r="V24" t="n">
-        <v>6.75</v>
+        <v>3.42</v>
       </c>
       <c r="W24" t="n">
-        <v>1.02</v>
+        <v>1.23</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.3</v>
+        <v>1.06</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.1</v>
+        <v>7.7</v>
       </c>
       <c r="AA24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD24" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB24" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE24" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.38</v>
+        <v>1.04</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46078.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.44</v>
+        <v>1.56</v>
       </c>
       <c r="M25" t="n">
-        <v>2.72</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>3.11</v>
+        <v>6.45</v>
       </c>
       <c r="O25" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T25" t="n">
         <v>3.4</v>
       </c>
-      <c r="P25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.6</v>
-      </c>
       <c r="U25" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W25" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X25" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>5.25</v>
+        <v>4.65</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46078.6875</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O26" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="P26" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="R26" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S26" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="T26" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="U26" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V26" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="W26" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X26" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.26</v>
+        <v>5.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46078.6875</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="P27" t="n">
         <v>1.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>7.1</v>
+        <v>4.2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="S27" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="T27" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U27" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V27" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X27" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.65</v>
+        <v>4.26</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46078.6875</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.24</v>
+        <v>2.41</v>
       </c>
       <c r="M28" t="n">
-        <v>6</v>
+        <v>3.34</v>
       </c>
       <c r="N28" t="n">
-        <v>10.5</v>
+        <v>2.83</v>
       </c>
       <c r="O28" t="n">
-        <v>1.66</v>
+        <v>2.87</v>
       </c>
       <c r="P28" t="n">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="Q28" t="n">
-        <v>8.4</v>
+        <v>3.25</v>
       </c>
       <c r="R28" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="S28" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="T28" t="n">
-        <v>2.22</v>
+        <v>2.8</v>
       </c>
       <c r="U28" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="V28" t="n">
-        <v>4.9</v>
+        <v>6.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X28" t="n">
         <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.5</v>
+        <v>1.93</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.62</v>
+        <v>1.77</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.6</v>
+        <v>1.29</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>3.6</v>
+        <v>1.53</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46078.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.28</v>
+        <v>1.24</v>
       </c>
       <c r="M29" t="n">
-        <v>3.68</v>
+        <v>6</v>
       </c>
       <c r="N29" t="n">
-        <v>2.8</v>
+        <v>10.5</v>
       </c>
       <c r="O29" t="n">
-        <v>2.75</v>
+        <v>1.66</v>
       </c>
       <c r="P29" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="Q29" t="n">
-        <v>3</v>
+        <v>8.4</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="S29" t="n">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="T29" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="U29" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="V29" t="n">
-        <v>5.25</v>
+        <v>4.9</v>
       </c>
       <c r="W29" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X29" t="n">
         <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.44</v>
+        <v>1.81</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46078.69791666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="M30" t="n">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="N30" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="O30" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="P30" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R30" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S30" t="n">
-        <v>2.8</v>
+        <v>3.22</v>
       </c>
       <c r="T30" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="U30" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="V30" t="n">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="W30" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X30" t="n">
         <v>1.03</v>
       </c>
       <c r="Y30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AG30" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH30" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46078.69791666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="M31" t="n">
-        <v>3.54</v>
+        <v>4.68</v>
       </c>
       <c r="N31" t="n">
-        <v>4.08</v>
+        <v>6.86</v>
       </c>
       <c r="O31" t="n">
-        <v>2.38</v>
+        <v>1.93</v>
       </c>
       <c r="P31" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T31" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3.22</v>
-      </c>
       <c r="U31" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="V31" t="n">
-        <v>8.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="W31" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="X31" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.8</v>
+        <v>5.25</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.92</v>
+        <v>2.2</v>
       </c>
       <c r="AD31" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG31" t="n">
         <v>1.18</v>
       </c>
-      <c r="AE31" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH31" t="n">
-        <v>1.95</v>
+        <v>2.81</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.33</v>
+        <v>1.85</v>
       </c>
       <c r="M32" t="n">
-        <v>6.14</v>
+        <v>3.54</v>
       </c>
       <c r="N32" t="n">
-        <v>9.85</v>
+        <v>4.08</v>
       </c>
       <c r="O32" t="n">
-        <v>1.58</v>
+        <v>2.38</v>
       </c>
       <c r="P32" t="n">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="R32" t="n">
-        <v>1.17</v>
+        <v>1.47</v>
       </c>
       <c r="S32" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="T32" t="n">
-        <v>1.85</v>
+        <v>3.22</v>
       </c>
       <c r="U32" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="V32" t="n">
-        <v>3.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W32" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="X32" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.07</v>
+        <v>1.4</v>
       </c>
       <c r="Z32" t="n">
-        <v>7.25</v>
+        <v>2.8</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="AB32" t="n">
-        <v>3.4</v>
+        <v>1.75</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.87</v>
+        <v>3.92</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.83</v>
+        <v>1.18</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.66</v>
+        <v>2.03</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>3.7</v>
+        <v>1.95</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="M34" t="n">
-        <v>4.68</v>
+        <v>6.14</v>
       </c>
       <c r="N34" t="n">
-        <v>6.86</v>
+        <v>9.85</v>
       </c>
       <c r="O34" t="n">
-        <v>1.93</v>
+        <v>1.58</v>
       </c>
       <c r="P34" t="n">
-        <v>2.62</v>
+        <v>3.25</v>
       </c>
       <c r="Q34" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="R34" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="S34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V34" t="n">
         <v>3.6</v>
       </c>
-      <c r="T34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V34" t="n">
-        <v>4.5</v>
-      </c>
       <c r="W34" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Z34" t="n">
-        <v>5.25</v>
+        <v>7.25</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.61</v>
+        <v>1.29</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.81</v>
+        <v>3.7</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.17</v>
+        <v>2.97</v>
       </c>
       <c r="M35" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="N35" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="O35" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="P35" t="n">
         <v>2.05</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="R35" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S35" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T35" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V35" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG35" t="n">
         <v>1.33</v>
       </c>
-      <c r="V35" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH35" t="n">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4788,22 +4788,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46078.79166666666</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,28 +5181,28 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="M40" t="n">
-        <v>3.79</v>
+        <v>3.44</v>
       </c>
       <c r="N40" t="n">
-        <v>5.14</v>
+        <v>3.37</v>
       </c>
       <c r="O40" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="P40" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="R40" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S40" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="T40" t="n">
         <v>2.8</v>
@@ -5217,37 +5217,37 @@
         <v>1.08</v>
       </c>
       <c r="X40" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD40" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z40" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB40" t="n">
+      <c r="AE40" t="n">
         <v>1.73</v>
       </c>
-      <c r="AC40" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF40" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46078.89583333334</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,28 +5300,28 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="M41" t="n">
-        <v>3.44</v>
+        <v>3.79</v>
       </c>
       <c r="N41" t="n">
-        <v>3.37</v>
+        <v>5.14</v>
       </c>
       <c r="O41" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="P41" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="R41" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S41" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="T41" t="n">
         <v>2.8</v>
@@ -5336,37 +5336,37 @@
         <v>1.08</v>
       </c>
       <c r="X41" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD41" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z41" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD41" t="n">
+      <c r="AE41" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG41" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE41" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH41" t="n">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46078.89583333334</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46078.4375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46078.4375</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.65</v>
+        <v>3.5</v>
       </c>
       <c r="M13" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>4.05</v>
+        <v>1.84</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.5</v>
+        <v>1.65</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N14" t="n">
-        <v>1.84</v>
+        <v>4.05</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2209,10 +2209,10 @@
         <v>2.08</v>
       </c>
       <c r="M15" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N15" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O15" t="n">
         <v>2.62</v>
@@ -2236,7 +2236,7 @@
         <v>1.47</v>
       </c>
       <c r="V15" t="n">
-        <v>5.5</v>
+        <v>5.85</v>
       </c>
       <c r="W15" t="n">
         <v>1.11</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2440,77 +2440,77 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5.93</v>
+        <v>2.39</v>
       </c>
       <c r="M17" t="n">
-        <v>4.4</v>
+        <v>2.73</v>
       </c>
       <c r="N17" t="n">
-        <v>1.44</v>
+        <v>3.17</v>
       </c>
       <c r="O17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.15</v>
+        <v>1.75</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.97</v>
+        <v>1.93</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.43</v>
+        <v>3.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.73</v>
+        <v>1.28</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46078.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2559,77 +2559,77 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="M18" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>3.07</v>
+        <v>2.69</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.93</v>
+        <v>3.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.5</v>
+        <v>1.89</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.28</v>
+        <v>1.87</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46078.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="M19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O19" t="n">
+        <v>5</v>
+      </c>
+      <c r="P19" t="n">
         <v>2.5</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="O19" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.15</v>
-      </c>
       <c r="Q19" t="n">
-        <v>3.28</v>
+        <v>1.89</v>
       </c>
       <c r="R19" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>2.77</v>
+        <v>3.66</v>
       </c>
       <c r="T19" t="n">
-        <v>2.93</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.39</v>
+        <v>1.68</v>
       </c>
       <c r="V19" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="W19" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.4</v>
+        <v>5.97</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.89</v>
+        <v>1.43</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.87</v>
+        <v>2.73</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.33</v>
+        <v>2.23</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.3</v>
+        <v>1.71</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.11</v>
+        <v>2.42</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>2.72</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46078.625</v>
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="M20" t="n">
         <v>2.65</v>
       </c>
       <c r="N20" t="n">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3167,64 +3167,64 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>3.34</v>
+        <v>8</v>
       </c>
       <c r="P23" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.8</v>
+        <v>1.45</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="S23" t="n">
-        <v>2.62</v>
+        <v>5.1</v>
       </c>
       <c r="T23" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="U23" t="n">
-        <v>1.33</v>
+        <v>1.9</v>
       </c>
       <c r="V23" t="n">
-        <v>6.75</v>
+        <v>3.42</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>1.23</v>
       </c>
       <c r="X23" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.3</v>
+        <v>1.06</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.1</v>
+        <v>7.7</v>
       </c>
       <c r="AA23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB23" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE23" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.38</v>
+        <v>1.04</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46078.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3286,64 +3286,64 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>8</v>
+        <v>3.34</v>
       </c>
       <c r="P24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V24" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z24" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q24" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S24" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V24" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>7.7</v>
-      </c>
       <c r="AA24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD24" t="n">
         <v>1.25</v>
       </c>
-      <c r="AB24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AC24" t="n">
+      <c r="AE24" t="n">
         <v>1.75</v>
       </c>
-      <c r="AD24" t="n">
+      <c r="AF24" t="n">
         <v>1.95</v>
       </c>
-      <c r="AE24" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AG24" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46078.66666666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="P26" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="R26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V26" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB26" t="n">
         <v>1.57</v>
       </c>
-      <c r="S26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V26" t="n">
-        <v>10</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AC26" t="n">
-        <v>5.25</v>
+        <v>4.26</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AF26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH26" t="n">
         <v>1.62</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46078.6875</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O27" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="P27" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="R27" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S27" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="T27" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="U27" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V27" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="W27" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X27" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.26</v>
+        <v>5.25</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46078.6875</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,70 +3753,70 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.41</v>
+        <v>2.29</v>
       </c>
       <c r="M28" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="N28" t="n">
-        <v>2.83</v>
+        <v>2.6</v>
       </c>
       <c r="O28" t="n">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="P28" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S28" t="n">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="T28" t="n">
-        <v>2.8</v>
+        <v>2.47</v>
       </c>
       <c r="U28" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="V28" t="n">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="W28" t="n">
         <v>1.08</v>
       </c>
       <c r="X28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG28" t="n">
         <v>1.3</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
         <v>1.53</v>
@@ -3872,37 +3872,37 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="M29" t="n">
-        <v>6</v>
+        <v>6.75</v>
       </c>
       <c r="N29" t="n">
-        <v>10.5</v>
+        <v>16.46</v>
       </c>
       <c r="O29" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="P29" t="n">
-        <v>2.62</v>
+        <v>3.06</v>
       </c>
       <c r="Q29" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="R29" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="S29" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="T29" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="U29" t="n">
         <v>1.62</v>
       </c>
       <c r="V29" t="n">
-        <v>4.9</v>
+        <v>4.75</v>
       </c>
       <c r="W29" t="n">
         <v>1.13</v>
@@ -3911,34 +3911,34 @@
         <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z29" t="n">
-        <v>5.4</v>
+        <v>4.95</v>
       </c>
       <c r="AA29" t="n">
         <v>1.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.85</v>
+        <v>2.28</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AH29" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46078.69791666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="M30" t="n">
-        <v>3.68</v>
+        <v>3.35</v>
       </c>
       <c r="N30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S30" t="n">
         <v>2.8</v>
       </c>
-      <c r="O30" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3</v>
-      </c>
-      <c r="R30" t="n">
+      <c r="T30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V30" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y30" t="n">
         <v>1.3</v>
       </c>
-      <c r="S30" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="V30" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.17</v>
-      </c>
       <c r="Z30" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.4</v>
+        <v>3.57</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.44</v>
+        <v>1.95</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46078.69791666666</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="M33" t="n">
-        <v>4.58</v>
+        <v>6.14</v>
       </c>
       <c r="N33" t="n">
-        <v>5.49</v>
+        <v>9.85</v>
       </c>
       <c r="O33" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="P33" t="n">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="Q33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R33" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="S33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V33" t="n">
         <v>3.6</v>
       </c>
-      <c r="T33" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V33" t="n">
-        <v>4.6</v>
-      </c>
       <c r="W33" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.3</v>
+        <v>7.25</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.63</v>
+        <v>1.29</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.45</v>
+        <v>3.7</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="M34" t="n">
-        <v>6.14</v>
+        <v>4.58</v>
       </c>
       <c r="N34" t="n">
-        <v>9.85</v>
+        <v>5.49</v>
       </c>
       <c r="O34" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="P34" t="n">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="Q34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R34" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V34" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W34" t="n">
         <v>1.17</v>
       </c>
-      <c r="S34" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T34" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V34" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.25</v>
-      </c>
       <c r="X34" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Z34" t="n">
-        <v>7.25</v>
+        <v>5.3</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.29</v>
+        <v>1.63</v>
       </c>
       <c r="AB34" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AH34" t="n">
-        <v>3.7</v>
+        <v>2.45</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.97</v>
+        <v>2.17</v>
       </c>
       <c r="M35" t="n">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
       <c r="N35" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="O35" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="P35" t="n">
         <v>2.05</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="R35" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S35" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T35" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U35" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V35" t="n">
-        <v>7.75</v>
+        <v>8.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X35" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.17</v>
+        <v>2.97</v>
       </c>
       <c r="M37" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="N37" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="O37" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="P37" t="n">
         <v>2.05</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="R37" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S37" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T37" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V37" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG37" t="n">
         <v>1.33</v>
       </c>
-      <c r="V37" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH37" t="n">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46078.79166666666</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,28 +5181,28 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="M40" t="n">
-        <v>3.44</v>
+        <v>3.79</v>
       </c>
       <c r="N40" t="n">
-        <v>3.37</v>
+        <v>5.14</v>
       </c>
       <c r="O40" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="P40" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="R40" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S40" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="T40" t="n">
         <v>2.8</v>
@@ -5217,37 +5217,37 @@
         <v>1.08</v>
       </c>
       <c r="X40" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD40" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z40" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD40" t="n">
+      <c r="AE40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG40" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE40" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH40" t="n">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46078.89583333334</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,28 +5300,28 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="M41" t="n">
-        <v>3.79</v>
+        <v>3.44</v>
       </c>
       <c r="N41" t="n">
-        <v>5.14</v>
+        <v>3.37</v>
       </c>
       <c r="O41" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="P41" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="R41" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S41" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="T41" t="n">
         <v>2.8</v>
@@ -5336,37 +5336,37 @@
         <v>1.08</v>
       </c>
       <c r="X41" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y41" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD41" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z41" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB41" t="n">
+      <c r="AE41" t="n">
         <v>1.73</v>
       </c>
-      <c r="AC41" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF41" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46078.89583333334</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="M3" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N3" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="O3" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="R3" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="S3" t="n">
-        <v>2.97</v>
+        <v>2.63</v>
       </c>
       <c r="T3" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="U3" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="V3" t="n">
-        <v>6</v>
+        <v>6.65</v>
       </c>
       <c r="W3" t="n">
         <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.84</v>
+        <v>3.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.83</v>
+        <v>3.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46078.35416666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="M7" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O7" t="n">
-        <v>2.54</v>
+        <v>2.31</v>
       </c>
       <c r="P7" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.67</v>
+        <v>5.31</v>
       </c>
       <c r="R7" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="T7" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="U7" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V7" t="n">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="W7" t="n">
         <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AA7" t="n">
         <v>2.04</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46078.4375</v>
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M12" t="n">
         <v>3.9</v>
-      </c>
-      <c r="M12" t="n">
-        <v>4</v>
       </c>
       <c r="N12" t="n">
         <v>1.7</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.5</v>
+        <v>1.65</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N13" t="n">
-        <v>1.84</v>
+        <v>4.05</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.65</v>
+        <v>3.5</v>
       </c>
       <c r="M14" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>4.05</v>
+        <v>1.84</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2206,19 +2206,19 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="M15" t="n">
         <v>3.6</v>
       </c>
       <c r="N15" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="O15" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="Q15" t="n">
         <v>3.65</v>
@@ -2227,43 +2227,43 @@
         <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="T15" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="U15" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="V15" t="n">
         <v>5.85</v>
       </c>
       <c r="W15" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AB15" t="n">
         <v>2.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AF15" t="n">
         <v>2.2</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2321,77 +2321,77 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L16" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V16" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AC16" t="n">
         <v>3.1</v>
       </c>
-      <c r="M16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46078.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.39</v>
+        <v>2.96</v>
       </c>
       <c r="M17" t="n">
-        <v>2.73</v>
+        <v>3.05</v>
       </c>
       <c r="N17" t="n">
-        <v>3.17</v>
+        <v>2.35</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AF17" t="n">
         <v>1.75</v>
       </c>
-      <c r="Z17" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46078.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="M18" t="n">
+        <v>6</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="O18" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB18" t="n">
         <v>2.5</v>
       </c>
-      <c r="M18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="O18" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P18" t="n">
+      <c r="AC18" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q18" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V18" t="n">
-        <v>6</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.33</v>
-      </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46078.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2678,77 +2678,77 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5.93</v>
+        <v>2.39</v>
       </c>
       <c r="M19" t="n">
-        <v>4.4</v>
+        <v>2.73</v>
       </c>
       <c r="N19" t="n">
-        <v>1.44</v>
+        <v>3.17</v>
       </c>
       <c r="O19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.15</v>
+        <v>1.75</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.97</v>
+        <v>1.93</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.43</v>
+        <v>3.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.73</v>
+        <v>1.28</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46078.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46078.65625</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>9.65</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46078.65625</v>
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="O23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P23" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="S23" t="n">
-        <v>5.1</v>
+        <v>5.25</v>
       </c>
       <c r="T23" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="U23" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="V23" t="n">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="W23" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.06</v>
       </c>
-      <c r="Z23" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46078.66666666666</v>
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O24" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="P24" t="n">
         <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S24" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="T24" t="n">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="U24" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V24" t="n">
-        <v>6.75</v>
+        <v>8</v>
       </c>
       <c r="W24" t="n">
         <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z24" t="n">
         <v>3.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE24" t="n">
         <v>1.75</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46078.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AB25" t="n">
         <v>1.56</v>
       </c>
-      <c r="M25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N25" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="O25" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V25" t="n">
-        <v>9</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AC25" t="n">
-        <v>4.65</v>
+        <v>4.28</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.3</v>
+        <v>1.52</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46078.6875</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O26" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="P26" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="R26" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S26" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="T26" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="U26" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V26" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="W26" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X26" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="Z26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA26" t="n">
         <v>2.8</v>
       </c>
-      <c r="AA26" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AB26" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.26</v>
+        <v>5.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46078.6875</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V27" t="n">
+        <v>9</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AA27" t="n">
         <v>2.44</v>
       </c>
-      <c r="M27" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="O27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V27" t="n">
-        <v>10</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AB27" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AC27" t="n">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.44</v>
+        <v>1.07</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.44</v>
+        <v>2.18</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46078.6875</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,70 +3753,70 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="M28" t="n">
         <v>3.2</v>
       </c>
       <c r="N28" t="n">
-        <v>2.6</v>
+        <v>2.89</v>
       </c>
       <c r="O28" t="n">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="P28" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="R28" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V28" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG28" t="n">
         <v>1.33</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V28" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
         <v>1.53</v>
@@ -3878,10 +3878,10 @@
         <v>6.75</v>
       </c>
       <c r="N29" t="n">
-        <v>16.46</v>
+        <v>16</v>
       </c>
       <c r="O29" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="P29" t="n">
         <v>3.06</v>
@@ -3893,7 +3893,7 @@
         <v>1.21</v>
       </c>
       <c r="S29" t="n">
-        <v>3.85</v>
+        <v>3.58</v>
       </c>
       <c r="T29" t="n">
         <v>2.21</v>
@@ -3902,7 +3902,7 @@
         <v>1.62</v>
       </c>
       <c r="V29" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="W29" t="n">
         <v>1.13</v>
@@ -3911,31 +3911,31 @@
         <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="AA29" t="n">
         <v>1.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AD29" t="n">
         <v>1.57</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="AF29" t="n">
         <v>1.67</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AH29" t="n">
         <v>4.4</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,70 +3991,70 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="M30" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N30" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="O30" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="P30" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R30" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S30" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="T30" t="n">
-        <v>2.8</v>
+        <v>2.47</v>
       </c>
       <c r="U30" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="V30" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="W30" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X30" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG30" t="n">
         <v>1.3</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
         <v>1.53</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,22 +4110,22 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="M31" t="n">
-        <v>4.68</v>
+        <v>4.58</v>
       </c>
       <c r="N31" t="n">
-        <v>6.86</v>
+        <v>5.49</v>
       </c>
       <c r="O31" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="P31" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="R31" t="n">
         <v>1.23</v>
@@ -4137,10 +4137,10 @@
         <v>2.1</v>
       </c>
       <c r="U31" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="V31" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="W31" t="n">
         <v>1.17</v>
@@ -4149,13 +4149,13 @@
         <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AB31" t="n">
         <v>2.15</v>
@@ -4167,16 +4167,16 @@
         <v>1.63</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AG31" t="n">
         <v>1.18</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.81</v>
+        <v>2.45</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="M32" t="n">
-        <v>3.54</v>
+        <v>4.68</v>
       </c>
       <c r="N32" t="n">
-        <v>4.08</v>
+        <v>6.86</v>
       </c>
       <c r="O32" t="n">
-        <v>2.38</v>
+        <v>1.93</v>
       </c>
       <c r="P32" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T32" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3.22</v>
-      </c>
       <c r="U32" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="V32" t="n">
-        <v>8.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="W32" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="X32" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.8</v>
+        <v>5.25</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.92</v>
+        <v>2.2</v>
       </c>
       <c r="AD32" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG32" t="n">
         <v>1.18</v>
       </c>
-      <c r="AE32" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH32" t="n">
-        <v>1.95</v>
+        <v>2.81</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.33</v>
+        <v>1.85</v>
       </c>
       <c r="M33" t="n">
-        <v>6.14</v>
+        <v>3.54</v>
       </c>
       <c r="N33" t="n">
-        <v>9.85</v>
+        <v>4.08</v>
       </c>
       <c r="O33" t="n">
-        <v>1.58</v>
+        <v>2.38</v>
       </c>
       <c r="P33" t="n">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q33" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="R33" t="n">
-        <v>1.17</v>
+        <v>1.47</v>
       </c>
       <c r="S33" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="T33" t="n">
-        <v>1.85</v>
+        <v>3.22</v>
       </c>
       <c r="U33" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="V33" t="n">
-        <v>3.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W33" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="X33" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.07</v>
+        <v>1.4</v>
       </c>
       <c r="Z33" t="n">
-        <v>7.25</v>
+        <v>2.8</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="AB33" t="n">
-        <v>3.4</v>
+        <v>1.75</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.87</v>
+        <v>3.92</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.83</v>
+        <v>1.18</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.66</v>
+        <v>2.03</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AH33" t="n">
-        <v>3.7</v>
+        <v>1.95</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="M34" t="n">
-        <v>4.58</v>
+        <v>6.14</v>
       </c>
       <c r="N34" t="n">
-        <v>5.49</v>
+        <v>9.85</v>
       </c>
       <c r="O34" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="P34" t="n">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="Q34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R34" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="S34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V34" t="n">
         <v>3.6</v>
       </c>
-      <c r="T34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V34" t="n">
-        <v>4.6</v>
-      </c>
       <c r="W34" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Z34" t="n">
-        <v>5.3</v>
+        <v>7.25</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.63</v>
+        <v>1.29</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.45</v>
+        <v>3.7</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4550,22 +4550,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46078.79166666666</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2321,77 +2321,77 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L16" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="M16" t="n">
         <v>2.73</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.2</v>
-      </c>
       <c r="N16" t="n">
-        <v>2.65</v>
+        <v>3.17</v>
       </c>
       <c r="O16" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.44</v>
+        <v>1.93</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.85</v>
+        <v>3.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.96</v>
+        <v>1.28</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46078.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2440,77 +2440,77 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.96</v>
+        <v>5.92</v>
       </c>
       <c r="M17" t="n">
-        <v>3.05</v>
+        <v>6</v>
       </c>
       <c r="N17" t="n">
-        <v>2.35</v>
+        <v>1.39</v>
       </c>
       <c r="O17" t="n">
-        <v>3.98</v>
+        <v>5.92</v>
       </c>
       <c r="P17" t="n">
-        <v>1.83</v>
+        <v>2.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.2</v>
+        <v>1.94</v>
       </c>
       <c r="R17" t="n">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>2.29</v>
+        <v>3.6</v>
       </c>
       <c r="T17" t="n">
-        <v>3.34</v>
+        <v>2.1</v>
       </c>
       <c r="U17" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="V17" t="n">
-        <v>9.5</v>
+        <v>4.6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="X17" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.56</v>
+        <v>5</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.37</v>
+        <v>1.48</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.52</v>
+        <v>2.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.4</v>
+        <v>2.15</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.14</v>
+        <v>1.62</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.93</v>
+        <v>1.62</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46078.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2559,77 +2559,77 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>5.92</v>
+        <v>2.96</v>
       </c>
       <c r="M18" t="n">
-        <v>6</v>
+        <v>3.05</v>
       </c>
       <c r="N18" t="n">
-        <v>1.39</v>
+        <v>2.35</v>
       </c>
       <c r="O18" t="n">
-        <v>5.92</v>
+        <v>3.98</v>
       </c>
       <c r="P18" t="n">
-        <v>2.6</v>
+        <v>1.83</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.94</v>
+        <v>3.2</v>
       </c>
       <c r="R18" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U18" t="n">
         <v>1.25</v>
       </c>
-      <c r="S18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.65</v>
-      </c>
       <c r="V18" t="n">
-        <v>4.6</v>
+        <v>9.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>5</v>
+        <v>2.56</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.48</v>
+        <v>2.37</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.5</v>
+        <v>1.52</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.15</v>
+        <v>4.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.62</v>
+        <v>1.14</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46078.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2678,77 +2678,77 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.39</v>
+        <v>2.73</v>
       </c>
       <c r="M19" t="n">
-        <v>2.73</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>3.17</v>
+        <v>2.65</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.93</v>
+        <v>3.44</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.5</v>
+        <v>1.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.28</v>
+        <v>1.96</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46078.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.03</v>
+        <v>1.23</v>
       </c>
       <c r="M21" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="N21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V21" t="n">
+        <v>6</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH21" t="n">
         <v>3.35</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O21" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V21" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.16</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46078.65625</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O22" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V22" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG22" t="n">
         <v>1.23</v>
       </c>
-      <c r="M22" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="N22" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>9.65</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V22" t="n">
-        <v>6</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AH22" t="n">
-        <v>3.35</v>
+        <v>1.16</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46078.65625</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S25" t="n">
         <v>2.25</v>
       </c>
-      <c r="M25" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O25" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.4</v>
-      </c>
       <c r="T25" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="U25" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V25" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="W25" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.59</v>
+        <v>2.25</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.27</v>
+        <v>2.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.28</v>
+        <v>5.25</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46078.6875</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="M26" t="n">
-        <v>2.74</v>
+        <v>2.98</v>
       </c>
       <c r="N26" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="O26" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="P26" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="R26" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="S26" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="T26" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="U26" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V26" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X26" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.25</v>
+        <v>2.59</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.8</v>
+        <v>2.27</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AC26" t="n">
-        <v>5.25</v>
+        <v>4.28</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46078.6875</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.55</v>
+        <v>1.17</v>
       </c>
       <c r="M28" t="n">
-        <v>3.2</v>
+        <v>6.75</v>
       </c>
       <c r="N28" t="n">
-        <v>2.89</v>
+        <v>16</v>
       </c>
       <c r="O28" t="n">
-        <v>3.1</v>
+        <v>1.48</v>
       </c>
       <c r="P28" t="n">
-        <v>2.1</v>
+        <v>3.06</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.25</v>
+        <v>10</v>
       </c>
       <c r="R28" t="n">
-        <v>1.43</v>
+        <v>1.21</v>
       </c>
       <c r="S28" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB28" t="n">
         <v>2.62</v>
       </c>
-      <c r="T28" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V28" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AC28" t="n">
-        <v>3.57</v>
+        <v>2.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.75</v>
+        <v>2.22</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.53</v>
+        <v>4.4</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46078.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.17</v>
+        <v>2.55</v>
       </c>
       <c r="M29" t="n">
-        <v>6.75</v>
+        <v>3.2</v>
       </c>
       <c r="N29" t="n">
-        <v>16</v>
+        <v>2.89</v>
       </c>
       <c r="O29" t="n">
-        <v>1.48</v>
+        <v>3.1</v>
       </c>
       <c r="P29" t="n">
-        <v>3.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>10</v>
+        <v>3.25</v>
       </c>
       <c r="R29" t="n">
-        <v>1.21</v>
+        <v>1.43</v>
       </c>
       <c r="S29" t="n">
-        <v>3.58</v>
+        <v>2.62</v>
       </c>
       <c r="T29" t="n">
-        <v>2.21</v>
+        <v>2.94</v>
       </c>
       <c r="U29" t="n">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="V29" t="n">
-        <v>4.6</v>
+        <v>6.95</v>
       </c>
       <c r="W29" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X29" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.5</v>
+        <v>2.03</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.62</v>
+        <v>1.73</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.2</v>
+        <v>3.57</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.22</v>
+        <v>1.75</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>4.4</v>
+        <v>1.53</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46078.69791666666</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="M31" t="n">
-        <v>4.58</v>
+        <v>6.14</v>
       </c>
       <c r="N31" t="n">
-        <v>5.49</v>
+        <v>9.85</v>
       </c>
       <c r="O31" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="P31" t="n">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="Q31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R31" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="S31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V31" t="n">
         <v>3.6</v>
       </c>
-      <c r="T31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V31" t="n">
-        <v>4.6</v>
-      </c>
       <c r="W31" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.3</v>
+        <v>7.25</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.63</v>
+        <v>1.29</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.45</v>
+        <v>3.7</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,22 +4229,22 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="M32" t="n">
-        <v>4.68</v>
+        <v>4.58</v>
       </c>
       <c r="N32" t="n">
-        <v>6.86</v>
+        <v>5.49</v>
       </c>
       <c r="O32" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="P32" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="R32" t="n">
         <v>1.23</v>
@@ -4256,10 +4256,10 @@
         <v>2.1</v>
       </c>
       <c r="U32" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="V32" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="W32" t="n">
         <v>1.17</v>
@@ -4268,13 +4268,13 @@
         <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AB32" t="n">
         <v>2.15</v>
@@ -4286,16 +4286,16 @@
         <v>1.63</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AG32" t="n">
         <v>1.18</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.81</v>
+        <v>2.45</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="M33" t="n">
-        <v>3.54</v>
+        <v>4.68</v>
       </c>
       <c r="N33" t="n">
-        <v>4.08</v>
+        <v>6.86</v>
       </c>
       <c r="O33" t="n">
-        <v>2.38</v>
+        <v>1.93</v>
       </c>
       <c r="P33" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T33" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q33" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T33" t="n">
-        <v>3.22</v>
-      </c>
       <c r="U33" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="V33" t="n">
-        <v>8.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="W33" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="X33" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.8</v>
+        <v>5.25</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.92</v>
+        <v>2.2</v>
       </c>
       <c r="AD33" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG33" t="n">
         <v>1.18</v>
       </c>
-      <c r="AE33" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH33" t="n">
-        <v>1.95</v>
+        <v>2.81</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.33</v>
+        <v>1.85</v>
       </c>
       <c r="M34" t="n">
-        <v>6.14</v>
+        <v>3.54</v>
       </c>
       <c r="N34" t="n">
-        <v>9.85</v>
+        <v>4.08</v>
       </c>
       <c r="O34" t="n">
-        <v>1.58</v>
+        <v>2.38</v>
       </c>
       <c r="P34" t="n">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q34" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="R34" t="n">
-        <v>1.17</v>
+        <v>1.47</v>
       </c>
       <c r="S34" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="T34" t="n">
-        <v>1.85</v>
+        <v>3.22</v>
       </c>
       <c r="U34" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="V34" t="n">
-        <v>3.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W34" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="X34" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.07</v>
+        <v>1.4</v>
       </c>
       <c r="Z34" t="n">
-        <v>7.25</v>
+        <v>2.8</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="AB34" t="n">
-        <v>3.4</v>
+        <v>1.75</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.87</v>
+        <v>3.92</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.83</v>
+        <v>1.18</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.66</v>
+        <v>2.03</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>3.7</v>
+        <v>1.95</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46078.70833333334</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,28 +5181,28 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="M40" t="n">
-        <v>3.79</v>
+        <v>3.44</v>
       </c>
       <c r="N40" t="n">
-        <v>5.14</v>
+        <v>3.37</v>
       </c>
       <c r="O40" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="P40" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="R40" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S40" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="T40" t="n">
         <v>2.8</v>
@@ -5217,37 +5217,37 @@
         <v>1.08</v>
       </c>
       <c r="X40" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD40" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z40" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB40" t="n">
+      <c r="AE40" t="n">
         <v>1.73</v>
       </c>
-      <c r="AC40" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF40" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46078.89583333334</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,28 +5300,28 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="M41" t="n">
-        <v>3.44</v>
+        <v>3.79</v>
       </c>
       <c r="N41" t="n">
-        <v>3.37</v>
+        <v>5.14</v>
       </c>
       <c r="O41" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="P41" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="R41" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S41" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="T41" t="n">
         <v>2.8</v>
@@ -5336,37 +5336,37 @@
         <v>1.08</v>
       </c>
       <c r="X41" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD41" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z41" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD41" t="n">
+      <c r="AE41" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG41" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE41" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH41" t="n">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46078.89583333334</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46078.375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1260,67 +1260,67 @@
         <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="O7" t="n">
-        <v>2.31</v>
+        <v>2.6</v>
       </c>
       <c r="P7" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.31</v>
+        <v>4.1</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S7" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="T7" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="U7" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V7" t="n">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="W7" t="n">
         <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.1</v>
+        <v>3.58</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.93</v>
+        <v>1.74</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46078.4375</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.65</v>
+        <v>3.5</v>
       </c>
       <c r="M13" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>4.05</v>
+        <v>1.84</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.5</v>
+        <v>1.65</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N14" t="n">
-        <v>1.84</v>
+        <v>4.05</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2321,77 +2321,77 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.39</v>
+        <v>2.73</v>
       </c>
       <c r="M16" t="n">
-        <v>2.73</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>3.17</v>
+        <v>2.65</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.93</v>
+        <v>3.44</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.5</v>
+        <v>1.85</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.28</v>
+        <v>1.96</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46078.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2440,77 +2440,77 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5.92</v>
+        <v>2.96</v>
       </c>
       <c r="M17" t="n">
-        <v>6</v>
+        <v>3.05</v>
       </c>
       <c r="N17" t="n">
-        <v>1.39</v>
+        <v>2.35</v>
       </c>
       <c r="O17" t="n">
-        <v>5.92</v>
+        <v>3.98</v>
       </c>
       <c r="P17" t="n">
-        <v>2.6</v>
+        <v>1.83</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.94</v>
+        <v>3.2</v>
       </c>
       <c r="R17" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U17" t="n">
         <v>1.25</v>
       </c>
-      <c r="S17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.65</v>
-      </c>
       <c r="V17" t="n">
-        <v>4.6</v>
+        <v>9.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>5</v>
+        <v>2.56</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.48</v>
+        <v>2.37</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.5</v>
+        <v>1.52</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.15</v>
+        <v>4.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.62</v>
+        <v>1.14</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46078.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2559,77 +2559,77 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.96</v>
+        <v>5.92</v>
       </c>
       <c r="M18" t="n">
-        <v>3.05</v>
+        <v>6</v>
       </c>
       <c r="N18" t="n">
-        <v>2.35</v>
+        <v>1.39</v>
       </c>
       <c r="O18" t="n">
-        <v>3.98</v>
+        <v>5.92</v>
       </c>
       <c r="P18" t="n">
-        <v>1.83</v>
+        <v>2.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.2</v>
+        <v>1.94</v>
       </c>
       <c r="R18" t="n">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>2.29</v>
+        <v>3.6</v>
       </c>
       <c r="T18" t="n">
-        <v>3.34</v>
+        <v>2.1</v>
       </c>
       <c r="U18" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="V18" t="n">
-        <v>9.5</v>
+        <v>4.6</v>
       </c>
       <c r="W18" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="X18" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.56</v>
+        <v>5</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.37</v>
+        <v>1.48</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.52</v>
+        <v>2.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.4</v>
+        <v>2.15</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.14</v>
+        <v>1.62</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.93</v>
+        <v>1.62</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46078.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2678,77 +2678,77 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L19" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="M19" t="n">
         <v>2.73</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.2</v>
-      </c>
       <c r="N19" t="n">
-        <v>2.65</v>
+        <v>3.17</v>
       </c>
       <c r="O19" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.44</v>
+        <v>1.93</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.85</v>
+        <v>3.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.96</v>
+        <v>1.28</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46078.625</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>15.5</v>
+        <v>2.78</v>
       </c>
       <c r="M23" t="n">
-        <v>8.4</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>1.11</v>
+        <v>2.45</v>
       </c>
       <c r="O23" t="n">
-        <v>9</v>
+        <v>3.3</v>
       </c>
       <c r="P23" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="R23" t="n">
-        <v>1.09</v>
+        <v>1.41</v>
       </c>
       <c r="S23" t="n">
-        <v>5.25</v>
+        <v>2.59</v>
       </c>
       <c r="T23" t="n">
-        <v>1.73</v>
+        <v>2.96</v>
       </c>
       <c r="U23" t="n">
-        <v>1.99</v>
+        <v>1.32</v>
       </c>
       <c r="V23" t="n">
-        <v>3.2</v>
+        <v>8</v>
       </c>
       <c r="W23" t="n">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.04</v>
+        <v>1.28</v>
       </c>
       <c r="Z23" t="n">
-        <v>8.5</v>
+        <v>3.1</v>
       </c>
       <c r="AA23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.22</v>
       </c>
-      <c r="AB23" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AE23" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AF23" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.06</v>
+        <v>1.45</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46078.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.78</v>
+        <v>15.5</v>
       </c>
       <c r="M24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="O24" t="n">
+        <v>9</v>
+      </c>
+      <c r="P24" t="n">
         <v>3.2</v>
       </c>
-      <c r="N24" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="O24" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.41</v>
+        <v>1.09</v>
       </c>
       <c r="S24" t="n">
-        <v>2.59</v>
+        <v>5.25</v>
       </c>
       <c r="T24" t="n">
-        <v>2.96</v>
+        <v>1.73</v>
       </c>
       <c r="U24" t="n">
-        <v>1.32</v>
+        <v>1.99</v>
       </c>
       <c r="V24" t="n">
-        <v>8</v>
+        <v>3.2</v>
       </c>
       <c r="W24" t="n">
-        <v>1.02</v>
+        <v>1.27</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.28</v>
+        <v>1.04</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.1</v>
+        <v>8.5</v>
       </c>
       <c r="AA24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD24" t="n">
         <v>2.1</v>
       </c>
-      <c r="AB24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AE24" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.45</v>
+        <v>1.06</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.44</v>
+        <v>1.03</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46078.66666666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.17</v>
+        <v>2.55</v>
       </c>
       <c r="M28" t="n">
-        <v>6.75</v>
+        <v>3.2</v>
       </c>
       <c r="N28" t="n">
-        <v>16</v>
+        <v>2.89</v>
       </c>
       <c r="O28" t="n">
-        <v>1.48</v>
+        <v>3.1</v>
       </c>
       <c r="P28" t="n">
-        <v>3.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>10</v>
+        <v>3.25</v>
       </c>
       <c r="R28" t="n">
-        <v>1.21</v>
+        <v>1.43</v>
       </c>
       <c r="S28" t="n">
-        <v>3.58</v>
+        <v>2.62</v>
       </c>
       <c r="T28" t="n">
-        <v>2.21</v>
+        <v>2.94</v>
       </c>
       <c r="U28" t="n">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="V28" t="n">
-        <v>4.6</v>
+        <v>6.95</v>
       </c>
       <c r="W28" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X28" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="Z28" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.5</v>
+        <v>2.03</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.62</v>
+        <v>1.73</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.2</v>
+        <v>3.57</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.22</v>
+        <v>1.75</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>4.4</v>
+        <v>1.53</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46078.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.55</v>
+        <v>1.17</v>
       </c>
       <c r="M29" t="n">
-        <v>3.2</v>
+        <v>6.75</v>
       </c>
       <c r="N29" t="n">
-        <v>2.89</v>
+        <v>16</v>
       </c>
       <c r="O29" t="n">
-        <v>3.1</v>
+        <v>1.48</v>
       </c>
       <c r="P29" t="n">
-        <v>2.1</v>
+        <v>3.06</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.25</v>
+        <v>10</v>
       </c>
       <c r="R29" t="n">
-        <v>1.43</v>
+        <v>1.21</v>
       </c>
       <c r="S29" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB29" t="n">
         <v>2.62</v>
       </c>
-      <c r="T29" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V29" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AC29" t="n">
-        <v>3.57</v>
+        <v>2.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.75</v>
+        <v>2.22</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.53</v>
+        <v>4.4</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46078.69791666666</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,22 +4229,22 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="M32" t="n">
-        <v>4.58</v>
+        <v>4.68</v>
       </c>
       <c r="N32" t="n">
-        <v>5.49</v>
+        <v>6.86</v>
       </c>
       <c r="O32" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="P32" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="Q32" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="R32" t="n">
         <v>1.23</v>
@@ -4256,10 +4256,10 @@
         <v>2.1</v>
       </c>
       <c r="U32" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="V32" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="W32" t="n">
         <v>1.17</v>
@@ -4268,13 +4268,13 @@
         <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AB32" t="n">
         <v>2.15</v>
@@ -4286,16 +4286,16 @@
         <v>1.63</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AG32" t="n">
         <v>1.18</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.45</v>
+        <v>2.81</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="M33" t="n">
-        <v>4.68</v>
+        <v>3.54</v>
       </c>
       <c r="N33" t="n">
-        <v>6.86</v>
+        <v>4.08</v>
       </c>
       <c r="O33" t="n">
-        <v>1.93</v>
+        <v>2.38</v>
       </c>
       <c r="P33" t="n">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="R33" t="n">
-        <v>1.23</v>
+        <v>1.47</v>
       </c>
       <c r="S33" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="T33" t="n">
-        <v>2.1</v>
+        <v>3.22</v>
       </c>
       <c r="U33" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="V33" t="n">
-        <v>4.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W33" t="n">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.25</v>
+        <v>2.8</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.2</v>
+        <v>3.92</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.63</v>
+        <v>1.18</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.65</v>
+        <v>2.03</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.81</v>
+        <v>1.95</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="M34" t="n">
-        <v>3.54</v>
+        <v>4.58</v>
       </c>
       <c r="N34" t="n">
-        <v>4.08</v>
+        <v>5.49</v>
       </c>
       <c r="O34" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="P34" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>5</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T34" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q34" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T34" t="n">
-        <v>3.22</v>
-      </c>
       <c r="U34" t="n">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="V34" t="n">
-        <v>8.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="W34" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="X34" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.4</v>
+        <v>1.09</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.92</v>
+        <v>2.2</v>
       </c>
       <c r="AD34" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG34" t="n">
         <v>1.18</v>
       </c>
-      <c r="AE34" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH34" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46078.70833333334</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="M3" t="n">
         <v>3.25</v>
       </c>
       <c r="N3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="P3" t="n">
         <v>2.05</v>
       </c>
-      <c r="O3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Q3" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="R3" t="n">
         <v>1.39</v>
@@ -802,10 +802,10 @@
         <v>2.63</v>
       </c>
       <c r="T3" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="U3" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V3" t="n">
         <v>6.65</v>
@@ -817,34 +817,34 @@
         <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46078.35416666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46078.4375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46078.4375</v>
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46078.5</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.5</v>
+        <v>1.55</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="N13" t="n">
-        <v>1.84</v>
+        <v>4.58</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46078.60416666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.65</v>
+        <v>3.5</v>
       </c>
       <c r="M14" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>4.05</v>
+        <v>2.05</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46078.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2321,77 +2321,77 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.73</v>
+        <v>3.05</v>
       </c>
       <c r="M16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
         <v>3.2</v>
       </c>
-      <c r="N16" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.32</v>
-      </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="S16" t="n">
-        <v>2.9</v>
+        <v>2.29</v>
       </c>
       <c r="T16" t="n">
-        <v>2.63</v>
+        <v>3.34</v>
       </c>
       <c r="U16" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="V16" t="n">
-        <v>6.1</v>
+        <v>9.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.44</v>
+        <v>2.55</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.96</v>
+        <v>1.53</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.37</v>
+        <v>1.14</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.49</v>
+        <v>1.28</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46078.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2440,77 +2440,77 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O17" t="n">
         <v>2.96</v>
       </c>
-      <c r="M17" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="O17" t="n">
-        <v>3.98</v>
-      </c>
       <c r="P17" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R17" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>2.29</v>
+        <v>2.9</v>
       </c>
       <c r="T17" t="n">
-        <v>3.34</v>
+        <v>2.7</v>
       </c>
       <c r="U17" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="V17" t="n">
-        <v>9.5</v>
+        <v>6.75</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.56</v>
+        <v>3.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.37</v>
+        <v>1.95</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.52</v>
+        <v>1.9</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.93</v>
+        <v>1.65</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46078.625</v>
@@ -2563,16 +2563,16 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>5.92</v>
+        <v>6.33</v>
       </c>
       <c r="M18" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="N18" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="O18" t="n">
-        <v>5.92</v>
+        <v>4.8</v>
       </c>
       <c r="P18" t="n">
         <v>2.6</v>
@@ -2587,7 +2587,7 @@
         <v>3.6</v>
       </c>
       <c r="T18" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="U18" t="n">
         <v>1.65</v>
@@ -2602,7 +2602,7 @@
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z18" t="n">
         <v>5</v>
@@ -2611,7 +2611,7 @@
         <v>1.48</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AC18" t="n">
         <v>2.15</v>
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="M19" t="n">
-        <v>2.73</v>
+        <v>2.87</v>
       </c>
       <c r="N19" t="n">
-        <v>3.17</v>
+        <v>3.25</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>1.93</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.5</v>
+        <v>2.62</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="M20" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="N20" t="n">
-        <v>3.19</v>
+        <v>2.97</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="M21" t="n">
-        <v>5.15</v>
+        <v>5.4</v>
       </c>
       <c r="N21" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="O21" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="P21" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="Q21" t="n">
-        <v>9.65</v>
+        <v>9</v>
       </c>
       <c r="R21" t="n">
         <v>1.34</v>
@@ -2947,16 +2947,16 @@
         <v>2.53</v>
       </c>
       <c r="U21" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="V21" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="W21" t="n">
         <v>1.09</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
         <v>1.22</v>
@@ -2965,28 +2965,28 @@
         <v>3.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AG21" t="n">
         <v>1.1</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46078.65625</v>
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.03</v>
+        <v>4.4</v>
       </c>
       <c r="M22" t="n">
         <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="O22" t="n">
-        <v>4.82</v>
+        <v>5.3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="R22" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="S22" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="T22" t="n">
-        <v>2.79</v>
+        <v>2.6</v>
       </c>
       <c r="U22" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="V22" t="n">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
       <c r="W22" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
         <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.28</v>
+        <v>3.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.23</v>
+        <v>1.9</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46078.65625</v>
@@ -3158,10 +3158,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="M23" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N23" t="n">
         <v>2.45</v>
@@ -3170,13 +3170,13 @@
         <v>3.3</v>
       </c>
       <c r="P23" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="Q23" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R23" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
         <v>2.59</v>
@@ -3185,46 +3185,46 @@
         <v>2.96</v>
       </c>
       <c r="U23" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V23" t="n">
         <v>8</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z23" t="n">
         <v>3.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AD23" t="n">
         <v>1.22</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AF23" t="n">
         <v>2.05</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46078.66666666666</v>
@@ -3277,37 +3277,37 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="M24" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="N24" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="O24" t="n">
         <v>9</v>
       </c>
       <c r="P24" t="n">
-        <v>3.2</v>
+        <v>3.46</v>
       </c>
       <c r="Q24" t="n">
         <v>1.4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="S24" t="n">
-        <v>5.25</v>
+        <v>5.05</v>
       </c>
       <c r="T24" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="U24" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="V24" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="W24" t="n">
         <v>1.27</v>
@@ -3319,31 +3319,31 @@
         <v>1.04</v>
       </c>
       <c r="Z24" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AB24" t="n">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AD24" t="n">
         <v>2.1</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AF24" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.06</v>
+        <v>5</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46078.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="M25" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="N25" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="O25" t="n">
-        <v>3.4</v>
+        <v>2.94</v>
       </c>
       <c r="P25" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.75</v>
+        <v>4.45</v>
       </c>
       <c r="R25" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="S25" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="T25" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="U25" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V25" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X25" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.25</v>
+        <v>2.59</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.8</v>
+        <v>2.37</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AC25" t="n">
-        <v>5.25</v>
+        <v>4.31</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AF25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.62</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46078.6875</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M26" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S26" t="n">
         <v>2.25</v>
       </c>
-      <c r="M26" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O26" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.4</v>
-      </c>
       <c r="T26" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="U26" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V26" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="W26" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X26" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.59</v>
+        <v>2.25</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.27</v>
+        <v>2.8</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.28</v>
+        <v>5.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46078.6875</v>
@@ -3634,22 +3634,22 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>5.5</v>
+        <v>6.45</v>
       </c>
       <c r="O27" t="n">
         <v>2.25</v>
       </c>
       <c r="P27" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Q27" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="R27" t="n">
         <v>1.55</v>
@@ -3658,7 +3658,7 @@
         <v>2.3</v>
       </c>
       <c r="T27" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="U27" t="n">
         <v>1.29</v>
@@ -3673,7 +3673,7 @@
         <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="Z27" t="n">
         <v>2.46</v>
@@ -3682,7 +3682,7 @@
         <v>2.44</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AC27" t="n">
         <v>4.5</v>
@@ -3697,10 +3697,10 @@
         <v>1.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46078.6875</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,70 +3753,70 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="M28" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="O28" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="P28" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="S28" t="n">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="T28" t="n">
-        <v>2.94</v>
+        <v>2.47</v>
       </c>
       <c r="U28" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="V28" t="n">
-        <v>6.95</v>
+        <v>5.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG28" t="n">
         <v>1.3</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
         <v>1.53</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.17</v>
+        <v>2.55</v>
       </c>
       <c r="M29" t="n">
-        <v>6.75</v>
+        <v>3.2</v>
       </c>
       <c r="N29" t="n">
-        <v>16</v>
+        <v>2.89</v>
       </c>
       <c r="O29" t="n">
-        <v>1.48</v>
+        <v>3.1</v>
       </c>
       <c r="P29" t="n">
-        <v>3.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>10</v>
+        <v>3.25</v>
       </c>
       <c r="R29" t="n">
-        <v>1.21</v>
+        <v>1.43</v>
       </c>
       <c r="S29" t="n">
-        <v>3.58</v>
+        <v>2.62</v>
       </c>
       <c r="T29" t="n">
-        <v>2.21</v>
+        <v>2.94</v>
       </c>
       <c r="U29" t="n">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="V29" t="n">
-        <v>4.6</v>
+        <v>6.95</v>
       </c>
       <c r="W29" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X29" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.5</v>
+        <v>2.03</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.62</v>
+        <v>1.73</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.2</v>
+        <v>3.57</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.22</v>
+        <v>1.75</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>4.4</v>
+        <v>1.53</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46078.69791666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.4</v>
+        <v>1.17</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
+        <v>6.75</v>
       </c>
       <c r="N30" t="n">
-        <v>2.8</v>
+        <v>16</v>
       </c>
       <c r="O30" t="n">
-        <v>2.75</v>
+        <v>1.48</v>
       </c>
       <c r="P30" t="n">
-        <v>2.4</v>
+        <v>3.06</v>
       </c>
       <c r="Q30" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="S30" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="T30" t="n">
-        <v>2.47</v>
+        <v>2.21</v>
       </c>
       <c r="U30" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="V30" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="W30" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y30" t="n">
         <v>1.12</v>
       </c>
-      <c r="X30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.18</v>
-      </c>
       <c r="Z30" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.05</v>
+        <v>2.62</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.53</v>
+        <v>2.22</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.35</v>
+        <v>1.67</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.53</v>
+        <v>4.4</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46078.69791666666</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,22 +4229,22 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="M32" t="n">
-        <v>4.68</v>
+        <v>4.58</v>
       </c>
       <c r="N32" t="n">
-        <v>6.86</v>
+        <v>5.49</v>
       </c>
       <c r="O32" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="P32" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="R32" t="n">
         <v>1.23</v>
@@ -4256,10 +4256,10 @@
         <v>2.1</v>
       </c>
       <c r="U32" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="V32" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="W32" t="n">
         <v>1.17</v>
@@ -4268,13 +4268,13 @@
         <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AB32" t="n">
         <v>2.15</v>
@@ -4286,16 +4286,16 @@
         <v>1.63</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AG32" t="n">
         <v>1.18</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.81</v>
+        <v>2.45</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,22 +4467,22 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="M34" t="n">
-        <v>4.58</v>
+        <v>4.68</v>
       </c>
       <c r="N34" t="n">
-        <v>5.49</v>
+        <v>6.86</v>
       </c>
       <c r="O34" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="P34" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="Q34" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="R34" t="n">
         <v>1.23</v>
@@ -4494,10 +4494,10 @@
         <v>2.1</v>
       </c>
       <c r="U34" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="V34" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="W34" t="n">
         <v>1.17</v>
@@ -4506,13 +4506,13 @@
         <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z34" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AB34" t="n">
         <v>2.15</v>
@@ -4524,16 +4524,16 @@
         <v>1.63</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AG34" t="n">
         <v>1.18</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.45</v>
+        <v>2.81</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4550,22 +4550,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4788,22 +4788,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46078.79166666666</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="M4" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="N4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R4" t="n">
         <v>1.44</v>
       </c>
-      <c r="O4" t="n">
-        <v>9.050000000000001</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.48</v>
-      </c>
       <c r="S4" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="T4" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U4" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="V4" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="W4" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.94</v>
+        <v>4.6</v>
       </c>
       <c r="AD4" t="n">
         <v>1.17</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.44</v>
+        <v>2.75</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46078.375</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46078.4375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46078.4375</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46078.5</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46078.5</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.55</v>
+        <v>3.5</v>
       </c>
       <c r="M13" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>4.58</v>
+        <v>2.05</v>
       </c>
       <c r="O13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF13" t="n">
         <v>2.05</v>
       </c>
-      <c r="P13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V13" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.15</v>
+        <v>1.3</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46078.60416666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.5</v>
+        <v>1.55</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="N14" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="O14" t="n">
         <v>2.05</v>
       </c>
-      <c r="O14" t="n">
-        <v>3.75</v>
-      </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="R14" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="S14" t="n">
-        <v>2.74</v>
+        <v>3.12</v>
       </c>
       <c r="T14" t="n">
-        <v>2.76</v>
+        <v>2.48</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="V14" t="n">
-        <v>6.9</v>
+        <v>6.05</v>
       </c>
       <c r="W14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X14" t="n">
         <v>1.04</v>
       </c>
-      <c r="X14" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH14" t="n">
-        <v>1.3</v>
+        <v>2.15</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46078.60416666666</v>
@@ -2206,40 +2206,40 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="M15" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="N15" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="O15" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="P15" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
         <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="T15" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="U15" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="V15" t="n">
-        <v>5.85</v>
+        <v>5.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
@@ -2248,22 +2248,22 @@
         <v>1.19</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AF15" t="n">
         <v>2.2</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2321,77 +2321,77 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="M16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S16" t="n">
         <v>2.9</v>
       </c>
-      <c r="N16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="O16" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="T16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V16" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC16" t="n">
         <v>3.2</v>
       </c>
-      <c r="R16" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V16" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AD16" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.28</v>
+        <v>1.49</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46078.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2440,77 +2440,77 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="M17" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="O17" t="n">
-        <v>2.96</v>
+        <v>3.98</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="S17" t="n">
-        <v>2.9</v>
+        <v>2.29</v>
       </c>
       <c r="T17" t="n">
-        <v>2.7</v>
+        <v>3.34</v>
       </c>
       <c r="U17" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="V17" t="n">
-        <v>6.75</v>
+        <v>9.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="AA17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AF17" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.49</v>
+        <v>1.28</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46078.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="O21" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.25</v>
       </c>
-      <c r="M21" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="N21" t="n">
-        <v>11</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>9</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V21" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AH21" t="n">
-        <v>3.42</v>
+        <v>1.13</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46078.65625</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.4</v>
+        <v>1.25</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>5.4</v>
       </c>
       <c r="N22" t="n">
-        <v>1.75</v>
+        <v>11</v>
       </c>
       <c r="O22" t="n">
-        <v>5.3</v>
+        <v>1.71</v>
       </c>
       <c r="P22" t="n">
-        <v>1.96</v>
+        <v>2.34</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.55</v>
+        <v>9</v>
       </c>
       <c r="R22" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="S22" t="n">
-        <v>2.5</v>
+        <v>2.83</v>
       </c>
       <c r="T22" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="U22" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="V22" t="n">
-        <v>7.6</v>
+        <v>6.1</v>
       </c>
       <c r="W22" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.9</v>
+        <v>2.74</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.95</v>
+        <v>2.28</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.74</v>
+        <v>1.47</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.15</v>
+        <v>3.42</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46078.65625</v>
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="M23" t="n">
         <v>3.1</v>
@@ -3212,7 +3212,7 @@
         <v>3.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE23" t="n">
         <v>1.77</v>
@@ -3221,10 +3221,10 @@
         <v>2.05</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46078.66666666666</v>
@@ -3280,67 +3280,67 @@
         <v>12</v>
       </c>
       <c r="M24" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="N24" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="O24" t="n">
         <v>9</v>
       </c>
       <c r="P24" t="n">
-        <v>3.46</v>
+        <v>3.37</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="R24" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="S24" t="n">
-        <v>5.05</v>
+        <v>4.8</v>
       </c>
       <c r="T24" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="U24" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="V24" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Z24" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AA24" t="n">
         <v>1.28</v>
       </c>
       <c r="AB24" t="n">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AG24" t="n">
-        <v>5</v>
+        <v>1.06</v>
       </c>
       <c r="AH24" t="n">
         <v>1.04</v>
@@ -3396,22 +3396,22 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="M25" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="N25" t="n">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="O25" t="n">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="P25" t="n">
         <v>2.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.45</v>
+        <v>4.65</v>
       </c>
       <c r="R25" t="n">
         <v>1.5</v>
@@ -3438,16 +3438,16 @@
         <v>1.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.31</v>
+        <v>3.86</v>
       </c>
       <c r="AD25" t="n">
         <v>1.18</v>
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="M26" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="N26" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="O26" t="n">
         <v>3.4</v>
@@ -3634,19 +3634,19 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="M27" t="n">
         <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>6.45</v>
+        <v>6.35</v>
       </c>
       <c r="O27" t="n">
         <v>2.25</v>
       </c>
       <c r="P27" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q27" t="n">
         <v>7.1</v>
@@ -3676,13 +3676,13 @@
         <v>1.48</v>
       </c>
       <c r="Z27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA27" t="n">
         <v>2.46</v>
       </c>
-      <c r="AA27" t="n">
-        <v>2.44</v>
-      </c>
       <c r="AB27" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AC27" t="n">
         <v>4.5</v>
@@ -3753,40 +3753,40 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="M28" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="N28" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="O28" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="P28" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="Q28" t="n">
         <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S28" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="T28" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="U28" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V28" t="n">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="W28" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X28" t="n">
         <v>1.01</v>
@@ -3795,31 +3795,31 @@
         <v>1.18</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.2</v>
+        <v>3.94</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AE28" t="n">
         <v>1.53</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46078.69791666666</v>
@@ -3872,43 +3872,43 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="M29" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="N29" t="n">
-        <v>2.89</v>
+        <v>2.6</v>
       </c>
       <c r="O29" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P29" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q29" t="n">
         <v>3.25</v>
       </c>
       <c r="R29" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="S29" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="T29" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="U29" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="V29" t="n">
-        <v>6.95</v>
+        <v>6.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y29" t="n">
         <v>1.3</v>
@@ -3917,16 +3917,16 @@
         <v>3.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.57</v>
+        <v>3.67</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE29" t="n">
         <v>1.75</v>
@@ -3991,40 +3991,40 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="M30" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="N30" t="n">
-        <v>16</v>
+        <v>16.64</v>
       </c>
       <c r="O30" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="P30" t="n">
-        <v>3.06</v>
+        <v>2.62</v>
       </c>
       <c r="Q30" t="n">
         <v>10</v>
       </c>
       <c r="R30" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S30" t="n">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="T30" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="U30" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="V30" t="n">
-        <v>4.6</v>
+        <v>4.95</v>
       </c>
       <c r="W30" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X30" t="n">
         <v>1.03</v>
@@ -4033,28 +4033,28 @@
         <v>1.12</v>
       </c>
       <c r="Z30" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.62</v>
+        <v>2.34</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AH30" t="n">
         <v>4.4</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.33</v>
+        <v>1.85</v>
       </c>
       <c r="M31" t="n">
-        <v>6.14</v>
+        <v>3.54</v>
       </c>
       <c r="N31" t="n">
-        <v>9.85</v>
+        <v>4.08</v>
       </c>
       <c r="O31" t="n">
-        <v>1.58</v>
+        <v>2.38</v>
       </c>
       <c r="P31" t="n">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="R31" t="n">
-        <v>1.17</v>
+        <v>1.47</v>
       </c>
       <c r="S31" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="T31" t="n">
-        <v>1.85</v>
+        <v>3.22</v>
       </c>
       <c r="U31" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="V31" t="n">
-        <v>3.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W31" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="X31" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.07</v>
+        <v>1.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>7.25</v>
+        <v>2.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="AB31" t="n">
-        <v>3.4</v>
+        <v>1.75</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.87</v>
+        <v>3.92</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.83</v>
+        <v>1.18</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.66</v>
+        <v>2.03</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>3.7</v>
+        <v>1.95</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,22 +4229,22 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="M32" t="n">
-        <v>4.58</v>
+        <v>4.68</v>
       </c>
       <c r="N32" t="n">
-        <v>5.49</v>
+        <v>6.86</v>
       </c>
       <c r="O32" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="P32" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="Q32" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="R32" t="n">
         <v>1.23</v>
@@ -4256,10 +4256,10 @@
         <v>2.1</v>
       </c>
       <c r="U32" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="V32" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="W32" t="n">
         <v>1.17</v>
@@ -4268,13 +4268,13 @@
         <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AB32" t="n">
         <v>2.15</v>
@@ -4286,16 +4286,16 @@
         <v>1.63</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AG32" t="n">
         <v>1.18</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.45</v>
+        <v>2.81</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="M33" t="n">
-        <v>3.54</v>
+        <v>4.58</v>
       </c>
       <c r="N33" t="n">
-        <v>4.08</v>
+        <v>5.49</v>
       </c>
       <c r="O33" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="P33" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>5</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T33" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q33" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T33" t="n">
-        <v>3.22</v>
-      </c>
       <c r="U33" t="n">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="V33" t="n">
-        <v>8.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="W33" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="X33" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.4</v>
+        <v>1.09</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.92</v>
+        <v>2.2</v>
       </c>
       <c r="AD33" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG33" t="n">
         <v>1.18</v>
       </c>
-      <c r="AE33" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH33" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="M34" t="n">
-        <v>4.68</v>
+        <v>6.14</v>
       </c>
       <c r="N34" t="n">
-        <v>6.86</v>
+        <v>9.85</v>
       </c>
       <c r="O34" t="n">
-        <v>1.93</v>
+        <v>1.58</v>
       </c>
       <c r="P34" t="n">
-        <v>2.62</v>
+        <v>3.25</v>
       </c>
       <c r="Q34" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="R34" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="S34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V34" t="n">
         <v>3.6</v>
       </c>
-      <c r="T34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V34" t="n">
-        <v>4.5</v>
-      </c>
       <c r="W34" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Z34" t="n">
-        <v>5.25</v>
+        <v>7.25</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.61</v>
+        <v>1.29</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.81</v>
+        <v>3.7</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.97</v>
+        <v>2.17</v>
       </c>
       <c r="M35" t="n">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
       <c r="N35" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="O35" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="P35" t="n">
         <v>2.05</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="R35" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S35" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T35" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U35" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V35" t="n">
-        <v>7.75</v>
+        <v>8.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X35" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.17</v>
+        <v>2.97</v>
       </c>
       <c r="M36" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="N36" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="O36" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="P36" t="n">
         <v>2.05</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="R36" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S36" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T36" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V36" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG36" t="n">
         <v>1.33</v>
       </c>
-      <c r="V36" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH36" t="n">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46078.79166666666</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,28 +5181,28 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="M40" t="n">
-        <v>3.44</v>
+        <v>3.79</v>
       </c>
       <c r="N40" t="n">
-        <v>3.37</v>
+        <v>5.14</v>
       </c>
       <c r="O40" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="P40" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="R40" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S40" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="T40" t="n">
         <v>2.8</v>
@@ -5217,37 +5217,37 @@
         <v>1.08</v>
       </c>
       <c r="X40" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD40" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z40" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD40" t="n">
+      <c r="AE40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG40" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE40" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH40" t="n">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46078.89583333334</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,28 +5300,28 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="M41" t="n">
-        <v>3.79</v>
+        <v>3.44</v>
       </c>
       <c r="N41" t="n">
-        <v>5.14</v>
+        <v>3.37</v>
       </c>
       <c r="O41" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="P41" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="R41" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S41" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="T41" t="n">
         <v>2.8</v>
@@ -5336,37 +5336,37 @@
         <v>1.08</v>
       </c>
       <c r="X41" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y41" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD41" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z41" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB41" t="n">
+      <c r="AE41" t="n">
         <v>1.73</v>
       </c>
-      <c r="AC41" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF41" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46078.89583333334</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI41"/>
+  <dimension ref="A1:AI43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -897,25 +897,25 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>7.2</v>
+        <v>5.25</v>
       </c>
       <c r="M4" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="O4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R4" t="n">
         <v>1.48</v>
-      </c>
-      <c r="O4" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.44</v>
       </c>
       <c r="S4" t="n">
         <v>2.5</v>
@@ -927,10 +927,10 @@
         <v>1.26</v>
       </c>
       <c r="V4" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
         <v>1.08</v>
@@ -954,16 +954,16 @@
         <v>1.17</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46078.375</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46078.4375</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46078.4375</v>
@@ -1575,22 +1575,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1607,77 +1607,77 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.49</v>
+        <v>1.44</v>
       </c>
       <c r="M10" t="n">
-        <v>2.85</v>
+        <v>4.4</v>
       </c>
       <c r="N10" t="n">
-        <v>3.01</v>
+        <v>7.5</v>
       </c>
       <c r="O10" t="n">
-        <v>3.07</v>
+        <v>1.91</v>
       </c>
       <c r="P10" t="n">
-        <v>1.92</v>
+        <v>2.38</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.8</v>
+        <v>6.5</v>
       </c>
       <c r="R10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U10" t="n">
         <v>1.44</v>
       </c>
-      <c r="S10" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.26</v>
-      </c>
       <c r="V10" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="W10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X10" t="n">
         <v>1.04</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y10" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.69</v>
+        <v>3.55</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.56</v>
+        <v>1.91</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.25</v>
+        <v>3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.47</v>
+        <v>2.8</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46078.5</v>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1726,77 +1726,77 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46078.5</v>
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
         <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>46078.5625</v>
+        <v>46078.5</v>
       </c>
     </row>
     <row r="13">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,76 +1968,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.5</v>
+        <v>2.49</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="N13" t="n">
-        <v>2.05</v>
+        <v>3.01</v>
       </c>
       <c r="O13" t="n">
-        <v>3.75</v>
+        <v>3.07</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="S13" t="n">
-        <v>2.74</v>
+        <v>2.46</v>
       </c>
       <c r="T13" t="n">
-        <v>2.76</v>
+        <v>3.28</v>
       </c>
       <c r="U13" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="V13" t="n">
-        <v>6.9</v>
+        <v>8.5</v>
       </c>
       <c r="W13" t="n">
         <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.4</v>
+        <v>2.69</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.81</v>
+        <v>1.56</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.14</v>
+        <v>4.25</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46078.60416666666</v>
+        <v>46078.5</v>
       </c>
     </row>
     <row r="14">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,76 +2087,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.55</v>
+        <v>3.8</v>
       </c>
       <c r="M14" t="n">
         <v>3.9</v>
       </c>
       <c r="N14" t="n">
-        <v>4.58</v>
+        <v>1.7</v>
       </c>
       <c r="O14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
         <v>1.44</v>
       </c>
-      <c r="V14" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AB14" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46078.60416666666</v>
+        <v>46078.5625</v>
       </c>
     </row>
     <row r="15">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,76 +2206,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.12</v>
+        <v>1.55</v>
       </c>
       <c r="M15" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="N15" t="n">
-        <v>3.3</v>
+        <v>4.58</v>
       </c>
       <c r="O15" t="n">
-        <v>2.62</v>
+        <v>2.05</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S15" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="T15" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="U15" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="V15" t="n">
-        <v>5.5</v>
+        <v>6.05</v>
       </c>
       <c r="W15" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AA15" t="n">
         <v>1.67</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.68</v>
+        <v>2.15</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46078.61458333334</v>
+        <v>46078.60416666666</v>
       </c>
     </row>
     <row r="16">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2321,80 +2321,80 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="M16" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q16" t="n">
         <v>2.5</v>
       </c>
-      <c r="O16" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.28</v>
-      </c>
       <c r="R16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="U16" t="n">
         <v>1.36</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.42</v>
-      </c>
       <c r="V16" t="n">
-        <v>6.65</v>
+        <v>6.9</v>
       </c>
       <c r="W16" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AE16" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46078.625</v>
+        <v>46078.60416666666</v>
       </c>
     </row>
     <row r="17">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,76 +2444,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.05</v>
+        <v>2.12</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="N17" t="n">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="O17" t="n">
-        <v>3.98</v>
+        <v>2.62</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S17" t="n">
         <v>3.2</v>
       </c>
-      <c r="R17" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.29</v>
-      </c>
       <c r="T17" t="n">
-        <v>3.34</v>
+        <v>2.45</v>
       </c>
       <c r="U17" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="V17" t="n">
-        <v>9.5</v>
+        <v>5.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.55</v>
+        <v>4.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.16</v>
+        <v>1.67</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.5</v>
+        <v>2.63</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.14</v>
+        <v>1.44</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>46078.625</v>
+        <v>46078.61458333334</v>
       </c>
     </row>
     <row r="18">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>6.33</v>
+        <v>2.6</v>
       </c>
       <c r="M18" t="n">
-        <v>5.8</v>
+        <v>2.88</v>
       </c>
       <c r="N18" t="n">
-        <v>1.38</v>
+        <v>2.5</v>
       </c>
       <c r="O18" t="n">
-        <v>4.8</v>
+        <v>2.96</v>
       </c>
       <c r="P18" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.94</v>
+        <v>3.28</v>
       </c>
       <c r="R18" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="T18" t="n">
-        <v>2.11</v>
+        <v>2.62</v>
       </c>
       <c r="U18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V18" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1.65</v>
       </c>
-      <c r="V18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AF18" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.15</v>
+        <v>1.49</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46078.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N19" t="n">
         <v>2.25</v>
       </c>
-      <c r="M19" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="N19" t="n">
-        <v>3.25</v>
-      </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.93</v>
+        <v>2.55</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.62</v>
+        <v>2.16</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46078.625</v>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="M20" t="n">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="N20" t="n">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2840,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA20" t="n">
         <v>2.62</v>
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
-        <v>46078.64583333334</v>
+        <v>46078.625</v>
       </c>
     </row>
     <row r="21">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,80 +2916,80 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.25</v>
+        <v>6.33</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>5.8</v>
       </c>
       <c r="N21" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="O21" t="n">
-        <v>5.42</v>
+        <v>4.8</v>
       </c>
       <c r="P21" t="n">
-        <v>1.97</v>
+        <v>2.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.55</v>
+        <v>1.94</v>
       </c>
       <c r="R21" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>2.53</v>
+        <v>3.6</v>
       </c>
       <c r="T21" t="n">
-        <v>2.6</v>
+        <v>2.11</v>
       </c>
       <c r="U21" t="n">
-        <v>1.31</v>
+        <v>1.65</v>
       </c>
       <c r="V21" t="n">
-        <v>7.8</v>
+        <v>4.6</v>
       </c>
       <c r="W21" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.31</v>
+        <v>1.11</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.92</v>
+        <v>5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.88</v>
+        <v>1.48</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.72</v>
+        <v>2.54</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.15</v>
+        <v>2.15</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.26</v>
+        <v>1.62</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>46078.65625</v>
+        <v>46078.625</v>
       </c>
     </row>
     <row r="22">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,76 +3039,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="M22" t="n">
-        <v>5.4</v>
+        <v>2.7</v>
       </c>
       <c r="N22" t="n">
-        <v>11</v>
+        <v>2.97</v>
       </c>
       <c r="O22" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.68</v>
+        <v>2.62</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.94</v>
+        <v>1.44</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>46078.65625</v>
+        <v>46078.64583333334</v>
       </c>
     </row>
     <row r="23">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,76 +3158,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.75</v>
+        <v>1.25</v>
       </c>
       <c r="M23" t="n">
-        <v>3.1</v>
+        <v>5.4</v>
       </c>
       <c r="N23" t="n">
-        <v>2.45</v>
+        <v>11</v>
       </c>
       <c r="O23" t="n">
-        <v>3.3</v>
+        <v>1.71</v>
       </c>
       <c r="P23" t="n">
-        <v>1.98</v>
+        <v>2.34</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.1</v>
+        <v>9</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="S23" t="n">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="T23" t="n">
-        <v>2.96</v>
+        <v>2.53</v>
       </c>
       <c r="U23" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="V23" t="n">
-        <v>8</v>
+        <v>6.1</v>
       </c>
       <c r="W23" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.02</v>
+        <v>1.68</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.5</v>
+        <v>2.74</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.77</v>
+        <v>2.28</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.05</v>
+        <v>1.47</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.4</v>
+        <v>3.42</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>46078.66666666666</v>
+        <v>46078.65625</v>
       </c>
     </row>
     <row r="24">
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,76 +3277,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>12</v>
+        <v>4.25</v>
       </c>
       <c r="M24" t="n">
-        <v>8.5</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>1.17</v>
+        <v>1.75</v>
       </c>
       <c r="O24" t="n">
-        <v>9</v>
+        <v>5.42</v>
       </c>
       <c r="P24" t="n">
-        <v>3.37</v>
+        <v>1.97</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.44</v>
+        <v>2.55</v>
       </c>
       <c r="R24" t="n">
-        <v>1.12</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>4.8</v>
+        <v>2.53</v>
       </c>
       <c r="T24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF24" t="n">
         <v>1.83</v>
       </c>
-      <c r="U24" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="V24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AG24" t="n">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>46078.66666666666</v>
+        <v>46078.65625</v>
       </c>
     </row>
     <row r="25">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,76 +3396,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.12</v>
+        <v>12</v>
       </c>
       <c r="M25" t="n">
-        <v>2.78</v>
+        <v>8.5</v>
       </c>
       <c r="N25" t="n">
-        <v>3.2</v>
+        <v>1.17</v>
       </c>
       <c r="O25" t="n">
-        <v>2.86</v>
+        <v>9</v>
       </c>
       <c r="P25" t="n">
-        <v>2.05</v>
+        <v>3.37</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.65</v>
+        <v>1.44</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5</v>
+        <v>1.12</v>
       </c>
       <c r="S25" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="T25" t="n">
-        <v>3.2</v>
+        <v>1.83</v>
       </c>
       <c r="U25" t="n">
-        <v>1.3</v>
+        <v>1.87</v>
       </c>
       <c r="V25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z25" t="n">
         <v>8.5</v>
       </c>
-      <c r="W25" t="n">
+      <c r="AA25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.04</v>
       </c>
-      <c r="X25" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AI25" s="3" t="n">
-        <v>46078.6875</v>
+        <v>46078.66666666666</v>
       </c>
     </row>
     <row r="26">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,76 +3515,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.24</v>
+        <v>2.75</v>
       </c>
       <c r="M26" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="N26" t="n">
-        <v>3.75</v>
+        <v>2.45</v>
       </c>
       <c r="O26" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P26" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="R26" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>2.25</v>
+        <v>2.59</v>
       </c>
       <c r="T26" t="n">
-        <v>3.6</v>
+        <v>2.96</v>
       </c>
       <c r="U26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V26" t="n">
+        <v>8</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD26" t="n">
         <v>1.25</v>
       </c>
-      <c r="V26" t="n">
-        <v>10</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB26" t="n">
+      <c r="AE26" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH26" t="n">
         <v>1.4</v>
       </c>
-      <c r="AC26" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AI26" s="3" t="n">
-        <v>46078.6875</v>
+        <v>46078.66666666666</v>
       </c>
     </row>
     <row r="27">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R27" t="n">
         <v>1.57</v>
       </c>
-      <c r="M27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N27" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="O27" t="n">
+      <c r="S27" t="n">
         <v>2.25</v>
       </c>
-      <c r="P27" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="R27" t="n">
+      <c r="T27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V27" t="n">
+        <v>10</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF27" t="n">
         <v>1.55</v>
       </c>
-      <c r="S27" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V27" t="n">
-        <v>9</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46078.6875</v>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,76 +3753,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="M28" t="n">
-        <v>3.44</v>
+        <v>2.78</v>
       </c>
       <c r="N28" t="n">
-        <v>2.72</v>
+        <v>3.2</v>
       </c>
       <c r="O28" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="P28" t="n">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="Q28" t="n">
-        <v>3</v>
+        <v>4.65</v>
       </c>
       <c r="R28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V28" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG28" t="n">
         <v>1.33</v>
       </c>
-      <c r="S28" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V28" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH28" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AI28" s="3" t="n">
-        <v>46078.69791666666</v>
+        <v>46078.6875</v>
       </c>
     </row>
     <row r="29">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,76 +3872,76 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N29" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V29" t="n">
+        <v>9</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z29" t="n">
         <v>2.5</v>
       </c>
-      <c r="M29" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N29" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O29" t="n">
-        <v>3</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y29" t="n">
+      <c r="AA29" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG29" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH29" t="n">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="AI29" s="3" t="n">
-        <v>46078.69791666666</v>
+        <v>46078.6875</v>
       </c>
     </row>
     <row r="30">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,49 +4110,49 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="M31" t="n">
-        <v>3.54</v>
+        <v>3.35</v>
       </c>
       <c r="N31" t="n">
-        <v>4.08</v>
+        <v>2.6</v>
       </c>
       <c r="O31" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="P31" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
       <c r="R31" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="S31" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="T31" t="n">
-        <v>3.22</v>
+        <v>2.8</v>
       </c>
       <c r="U31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V31" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y31" t="n">
         <v>1.3</v>
       </c>
-      <c r="V31" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.4</v>
-      </c>
       <c r="Z31" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="AA31" t="n">
         <v>1.95</v>
@@ -4161,25 +4161,25 @@
         <v>1.75</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.92</v>
+        <v>3.67</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.03</v>
+        <v>1.75</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AI31" s="3" t="n">
-        <v>46078.70833333334</v>
+        <v>46078.69791666666</v>
       </c>
     </row>
     <row r="32">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,76 +4229,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="M32" t="n">
-        <v>4.68</v>
+        <v>3.44</v>
       </c>
       <c r="N32" t="n">
-        <v>6.86</v>
+        <v>2.72</v>
       </c>
       <c r="O32" t="n">
-        <v>1.93</v>
+        <v>2.85</v>
       </c>
       <c r="P32" t="n">
-        <v>2.62</v>
+        <v>2.17</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.25</v>
+        <v>3</v>
       </c>
       <c r="R32" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="S32" t="n">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="T32" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="U32" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="V32" t="n">
-        <v>4.5</v>
+        <v>5.45</v>
       </c>
       <c r="W32" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="X32" t="n">
         <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.25</v>
+        <v>3.94</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.81</v>
+        <v>1.5</v>
       </c>
       <c r="AI32" s="3" t="n">
-        <v>46078.70833333334</v>
+        <v>46078.69791666666</v>
       </c>
     </row>
     <row r="33">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="M33" t="n">
-        <v>4.58</v>
+        <v>3.54</v>
       </c>
       <c r="N33" t="n">
-        <v>5.49</v>
+        <v>4.08</v>
       </c>
       <c r="O33" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V33" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA33" t="n">
         <v>1.95</v>
       </c>
-      <c r="P33" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>5</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V33" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AB33" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.2</v>
+        <v>3.92</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.63</v>
+        <v>1.18</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.6</v>
+        <v>2.03</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.3</v>
+        <v>1.72</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="M34" t="n">
-        <v>6.14</v>
+        <v>4.68</v>
       </c>
       <c r="N34" t="n">
-        <v>9.85</v>
+        <v>6.86</v>
       </c>
       <c r="O34" t="n">
-        <v>1.58</v>
+        <v>1.93</v>
       </c>
       <c r="P34" t="n">
-        <v>3.25</v>
+        <v>2.62</v>
       </c>
       <c r="Q34" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="R34" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W34" t="n">
         <v>1.17</v>
       </c>
-      <c r="S34" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T34" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V34" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.25</v>
-      </c>
       <c r="X34" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z34" t="n">
-        <v>7.25</v>
+        <v>5.25</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.29</v>
+        <v>1.61</v>
       </c>
       <c r="AB34" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AH34" t="n">
-        <v>3.7</v>
+        <v>2.81</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4545,27 +4545,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,76 +4586,76 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.17</v>
+        <v>1.33</v>
       </c>
       <c r="M35" t="n">
-        <v>3.34</v>
+        <v>6.14</v>
       </c>
       <c r="N35" t="n">
-        <v>3.55</v>
+        <v>9.85</v>
       </c>
       <c r="O35" t="n">
-        <v>2.4</v>
+        <v>1.58</v>
       </c>
       <c r="P35" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>6</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S35" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V35" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF35" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q35" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T35" t="n">
-        <v>3</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V35" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AG35" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.95</v>
+        <v>3.7</v>
       </c>
       <c r="AI35" s="3" t="n">
-        <v>46078.79166666666</v>
+        <v>46078.70833333334</v>
       </c>
     </row>
     <row r="36">
@@ -4664,27 +4664,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,76 +4705,76 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.97</v>
+        <v>1.63</v>
       </c>
       <c r="M36" t="n">
-        <v>3.27</v>
+        <v>4.58</v>
       </c>
       <c r="N36" t="n">
-        <v>2.5</v>
+        <v>5.49</v>
       </c>
       <c r="O36" t="n">
-        <v>3.5</v>
+        <v>1.95</v>
       </c>
       <c r="P36" t="n">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="R36" t="n">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="S36" t="n">
-        <v>2.62</v>
+        <v>3.6</v>
       </c>
       <c r="T36" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="U36" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="V36" t="n">
-        <v>7.75</v>
+        <v>4.6</v>
       </c>
       <c r="W36" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="X36" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.32</v>
+        <v>1.09</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.1</v>
+        <v>5.3</v>
       </c>
       <c r="AA36" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC36" t="n">
         <v>2.2</v>
       </c>
-      <c r="AB36" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AD36" t="n">
-        <v>1.26</v>
+        <v>1.63</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.36</v>
+        <v>2.45</v>
       </c>
       <c r="AI36" s="3" t="n">
-        <v>46078.79166666666</v>
+        <v>46078.70833333334</v>
       </c>
     </row>
     <row r="37">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,76 +4943,76 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.68</v>
+        <v>2.97</v>
       </c>
       <c r="M38" t="n">
-        <v>3.15</v>
+        <v>3.27</v>
       </c>
       <c r="N38" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="O38" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P38" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V38" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z38" t="n">
         <v>3.1</v>
       </c>
-      <c r="R38" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V38" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AA38" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AC38" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AI38" s="3" t="n">
-        <v>46078.8125</v>
+        <v>46078.79166666666</v>
       </c>
     </row>
     <row r="39">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,76 +5062,76 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.92</v>
+        <v>2.17</v>
       </c>
       <c r="M39" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="N39" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="O39" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="P39" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q39" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="R39" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S39" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="T39" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="U39" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V39" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="W39" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X39" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AA39" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE39" t="n">
         <v>2</v>
       </c>
-      <c r="AB39" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AF39" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG39" t="n">
         <v>1.3</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AI39" s="3" t="n">
-        <v>46078.83333333334</v>
+        <v>46078.79166666666</v>
       </c>
     </row>
     <row r="40">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,76 +5181,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.71</v>
+        <v>2.68</v>
       </c>
       <c r="M40" t="n">
-        <v>3.79</v>
+        <v>3.15</v>
       </c>
       <c r="N40" t="n">
-        <v>5.14</v>
+        <v>2.85</v>
       </c>
       <c r="O40" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S40" t="n">
         <v>2.4</v>
       </c>
-      <c r="P40" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q40" t="n">
+      <c r="T40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V40" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC40" t="n">
         <v>4.2</v>
       </c>
-      <c r="R40" t="n">
+      <c r="AD40" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH40" t="n">
         <v>1.4</v>
       </c>
-      <c r="S40" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V40" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AI40" s="3" t="n">
-        <v>46078.89583333334</v>
+        <v>46078.8125</v>
       </c>
     </row>
     <row r="41">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,75 +5300,313 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="M41" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="N41" t="n">
-        <v>3.37</v>
+        <v>4.1</v>
       </c>
       <c r="O41" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="P41" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R41" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S41" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="T41" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="U41" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V41" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W41" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X41" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z41" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AB41" t="n">
         <v>1.71</v>
       </c>
       <c r="AC41" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AI41" s="3" t="n">
+        <v>46078.83333333334</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="M42" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="N42" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="O42" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V42" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z42" t="n">
         <v>3.2</v>
       </c>
-      <c r="AD41" t="n">
+      <c r="AA42" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG42" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE41" t="n">
+      <c r="AH42" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AI42" s="3" t="n">
+        <v>46078.89583333334</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M43" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="N43" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="O43" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V43" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE43" t="n">
         <v>1.73</v>
       </c>
-      <c r="AF41" t="n">
+      <c r="AF43" t="n">
         <v>2</v>
       </c>
-      <c r="AG41" t="n">
+      <c r="AG43" t="n">
         <v>1.33</v>
       </c>
-      <c r="AH41" t="n">
+      <c r="AH43" t="n">
         <v>1.62</v>
       </c>
-      <c r="AI41" s="3" t="n">
+      <c r="AI43" s="3" t="n">
         <v>46078.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI43"/>
+  <dimension ref="A1:AI42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -618,12 +618,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Macarthur</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Central Coast Mariners</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,76 +659,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.75</v>
+        <v>3.1</v>
       </c>
       <c r="M2" t="n">
-        <v>4.29</v>
+        <v>3.25</v>
       </c>
       <c r="N2" t="n">
-        <v>4.34</v>
+        <v>2.1</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI2" s="3" t="n">
-        <v>46078.20833333334</v>
+        <v>46078.35416666666</v>
       </c>
     </row>
     <row r="3">
@@ -737,12 +737,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,76 +778,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.1</v>
+        <v>5.25</v>
       </c>
       <c r="M3" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N3" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="O3" t="n">
-        <v>4.09</v>
+        <v>5.5</v>
       </c>
       <c r="P3" t="n">
         <v>2.05</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.64</v>
+        <v>2.08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="S3" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.75</v>
+        <v>3.28</v>
       </c>
       <c r="U3" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="V3" t="n">
-        <v>6.65</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.14</v>
+        <v>2.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.14</v>
+        <v>4.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AG3" t="n">
         <v>1.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>46078.35416666666</v>
+        <v>46078.375</v>
       </c>
     </row>
     <row r="4">
@@ -856,12 +856,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,76 +897,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>46078.375</v>
+        <v>46078.41666666666</v>
       </c>
     </row>
     <row r="5">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,76 +1135,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.75</v>
+        <v>1.82</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>46078.41666666666</v>
+        <v>46078.4375</v>
       </c>
     </row>
     <row r="7">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,76 +1373,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>46078.4375</v>
+        <v>46078.45833333334</v>
       </c>
     </row>
     <row r="9">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,76 +1492,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>46078.45833333334</v>
+        <v>46078.5</v>
       </c>
     </row>
     <row r="10">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,34 +1611,34 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="M10" t="n">
-        <v>4.4</v>
+        <v>4.17</v>
       </c>
       <c r="N10" t="n">
-        <v>7.5</v>
+        <v>5.25</v>
       </c>
       <c r="O10" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="P10" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="T10" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U10" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V10" t="n">
         <v>6</v>
@@ -1647,37 +1647,37 @@
         <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH10" t="n">
-        <v>2.8</v>
+        <v>2.37</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46078.5</v>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1726,77 +1726,77 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46078.5</v>
@@ -1813,22 +1813,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1845,77 +1845,77 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46078.5</v>
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,76 +1968,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.49</v>
+        <v>3.8</v>
       </c>
       <c r="M13" t="n">
-        <v>2.85</v>
+        <v>3.9</v>
       </c>
       <c r="N13" t="n">
-        <v>3.01</v>
+        <v>1.7</v>
       </c>
       <c r="O13" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
         <v>1.44</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V13" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AB13" t="n">
-        <v>1.56</v>
+        <v>2.62</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46078.5</v>
+        <v>46078.5625</v>
       </c>
     </row>
     <row r="14">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,76 +2087,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="M14" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.44</v>
+        <v>1.93</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.62</v>
+        <v>1.78</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46078.5625</v>
+        <v>46078.60416666666</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M15" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="N15" t="n">
-        <v>4.58</v>
+        <v>4.4</v>
       </c>
       <c r="O15" t="n">
         <v>2.05</v>
@@ -2245,7 +2245,7 @@
         <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z15" t="n">
         <v>4</v>
@@ -2254,25 +2254,25 @@
         <v>1.67</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46078.60416666666</v>
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,76 +2325,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.5</v>
+        <v>2.12</v>
       </c>
       <c r="M16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S16" t="n">
         <v>3.2</v>
       </c>
-      <c r="N16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="O16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="T16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB16" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V16" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AC16" t="n">
-        <v>3.14</v>
+        <v>2.63</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.3</v>
+        <v>1.68</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46078.60416666666</v>
+        <v>46078.61458333334</v>
       </c>
     </row>
     <row r="17">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,76 +2444,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.12</v>
+        <v>3.05</v>
       </c>
       <c r="M17" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="O17" t="n">
-        <v>2.62</v>
+        <v>3.98</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="S17" t="n">
-        <v>3.2</v>
+        <v>2.29</v>
       </c>
       <c r="T17" t="n">
-        <v>2.45</v>
+        <v>3.34</v>
       </c>
       <c r="U17" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="V17" t="n">
-        <v>5.5</v>
+        <v>9.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.2</v>
+        <v>2.55</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.67</v>
+        <v>2.16</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.63</v>
+        <v>4.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.44</v>
+        <v>1.14</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AG17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.28</v>
       </c>
-      <c r="AH17" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AI17" s="3" t="n">
-        <v>46078.61458333334</v>
+        <v>46078.625</v>
       </c>
     </row>
     <row r="18">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2559,77 +2559,77 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="M18" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="N18" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="O18" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA18" t="n">
         <v>2.62</v>
       </c>
-      <c r="U18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V18" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AB18" t="n">
-        <v>1.92</v>
+        <v>1.44</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46078.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.05</v>
+        <v>7</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="N19" t="n">
-        <v>2.25</v>
+        <v>1.37</v>
       </c>
       <c r="O19" t="n">
-        <v>3.98</v>
+        <v>4.8</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.2</v>
+        <v>1.94</v>
       </c>
       <c r="R19" t="n">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>2.29</v>
+        <v>3.6</v>
       </c>
       <c r="T19" t="n">
-        <v>3.34</v>
+        <v>2.11</v>
       </c>
       <c r="U19" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="V19" t="n">
-        <v>9.5</v>
+        <v>4.6</v>
       </c>
       <c r="W19" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="X19" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.4</v>
+        <v>1.11</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.55</v>
+        <v>5</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.16</v>
+        <v>1.48</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.5</v>
+        <v>2.15</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.14</v>
+        <v>1.62</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46078.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.25</v>
+        <v>2.71</v>
       </c>
       <c r="M20" t="n">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.93</v>
+        <v>3.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.62</v>
+        <v>1.95</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.44</v>
+        <v>1.92</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46078.625</v>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,80 +2916,80 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>6.33</v>
+        <v>2.5</v>
       </c>
       <c r="M21" t="n">
-        <v>5.8</v>
+        <v>2.7</v>
       </c>
       <c r="N21" t="n">
-        <v>1.38</v>
+        <v>2.97</v>
       </c>
       <c r="O21" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.48</v>
+        <v>2.62</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.54</v>
+        <v>1.44</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>46078.625</v>
+        <v>46078.64583333334</v>
       </c>
     </row>
     <row r="22">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,76 +3039,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="M22" t="n">
-        <v>2.7</v>
+        <v>5.4</v>
       </c>
       <c r="N22" t="n">
-        <v>2.97</v>
+        <v>11</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.62</v>
+        <v>1.68</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.44</v>
+        <v>1.94</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>46078.64583333334</v>
+        <v>46078.65625</v>
       </c>
     </row>
     <row r="23">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="O23" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.25</v>
       </c>
-      <c r="M23" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="N23" t="n">
-        <v>11</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>9</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V23" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AH23" t="n">
-        <v>3.42</v>
+        <v>1.13</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46078.65625</v>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,76 +3277,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.25</v>
+        <v>12</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>8.5</v>
       </c>
       <c r="N24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="O24" t="n">
+        <v>9</v>
+      </c>
+      <c r="P24" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AC24" t="n">
         <v>1.75</v>
       </c>
-      <c r="O24" t="n">
-        <v>5.42</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.15</v>
-      </c>
       <c r="AD24" t="n">
-        <v>1.26</v>
+        <v>2</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>46078.65625</v>
+        <v>46078.66666666666</v>
       </c>
     </row>
     <row r="25">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>12</v>
+        <v>2.75</v>
       </c>
       <c r="M25" t="n">
-        <v>8.5</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>1.17</v>
+        <v>2.45</v>
       </c>
       <c r="O25" t="n">
-        <v>9</v>
+        <v>3.3</v>
       </c>
       <c r="P25" t="n">
-        <v>3.37</v>
+        <v>1.98</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.44</v>
+        <v>3.1</v>
       </c>
       <c r="R25" t="n">
-        <v>1.12</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>4.8</v>
+        <v>2.59</v>
       </c>
       <c r="T25" t="n">
-        <v>1.83</v>
+        <v>2.96</v>
       </c>
       <c r="U25" t="n">
-        <v>1.87</v>
+        <v>1.36</v>
       </c>
       <c r="V25" t="n">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="W25" t="n">
-        <v>1.24</v>
+        <v>1.05</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>8.5</v>
+        <v>3.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.28</v>
+        <v>2.02</v>
       </c>
       <c r="AB25" t="n">
-        <v>3.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.75</v>
+        <v>3.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.06</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46078.66666666666</v>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,76 +3515,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.75</v>
+        <v>2.12</v>
       </c>
       <c r="M26" t="n">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="N26" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="O26" t="n">
-        <v>3.3</v>
+        <v>2.86</v>
       </c>
       <c r="P26" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.1</v>
+        <v>4.65</v>
       </c>
       <c r="R26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V26" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y26" t="n">
         <v>1.4</v>
       </c>
-      <c r="S26" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V26" t="n">
-        <v>8</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.3</v>
-      </c>
       <c r="Z26" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.5</v>
+        <v>3.86</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AG26" t="n">
         <v>1.33</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AI26" s="3" t="n">
-        <v>46078.66666666666</v>
+        <v>46078.6875</v>
       </c>
     </row>
     <row r="27">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.12</v>
+        <v>1.57</v>
       </c>
       <c r="M28" t="n">
-        <v>2.78</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>3.2</v>
+        <v>6.35</v>
       </c>
       <c r="O28" t="n">
-        <v>2.86</v>
+        <v>2.25</v>
       </c>
       <c r="P28" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.65</v>
+        <v>7.1</v>
       </c>
       <c r="R28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V28" t="n">
+        <v>9</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AB28" t="n">
         <v>1.5</v>
       </c>
-      <c r="S28" t="n">
+      <c r="AC28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE28" t="n">
         <v>2.4</v>
       </c>
-      <c r="T28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U28" t="n">
+      <c r="AF28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG28" t="n">
         <v>1.3</v>
       </c>
-      <c r="V28" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH28" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46078.6875</v>
@@ -3831,12 +3831,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,76 +3872,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
       <c r="N29" t="n">
-        <v>6.35</v>
+        <v>16.64</v>
       </c>
       <c r="O29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>10</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T29" t="n">
         <v>2.25</v>
       </c>
-      <c r="P29" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="R29" t="n">
+      <c r="U29" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="V29" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA29" t="n">
         <v>1.55</v>
       </c>
-      <c r="S29" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V29" t="n">
-        <v>9</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.46</v>
-      </c>
       <c r="AB29" t="n">
-        <v>1.5</v>
+        <v>2.34</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.5</v>
+        <v>2.36</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.17</v>
+        <v>1.64</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="AI29" s="3" t="n">
-        <v>46078.6875</v>
+        <v>46078.69791666666</v>
       </c>
     </row>
     <row r="30">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.18</v>
+        <v>2.5</v>
       </c>
       <c r="M30" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O30" t="n">
+        <v>3</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V30" t="n">
         <v>6.5</v>
       </c>
-      <c r="N30" t="n">
-        <v>16.64</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>10</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V30" t="n">
-        <v>4.95</v>
-      </c>
       <c r="W30" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X30" t="n">
         <v>1.03</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.75</v>
+        <v>3.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.34</v>
+        <v>1.75</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.36</v>
+        <v>3.67</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.64</v>
+        <v>1.29</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.59</v>
+        <v>1.95</v>
       </c>
       <c r="AG30" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>4.4</v>
+        <v>1.53</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46078.69791666666</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4113,70 +4113,70 @@
         <v>2.5</v>
       </c>
       <c r="M31" t="n">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="N31" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="O31" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q31" t="n">
         <v>3</v>
       </c>
-      <c r="P31" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3.25</v>
-      </c>
       <c r="R31" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S31" t="n">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="T31" t="n">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="U31" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="V31" t="n">
-        <v>6.5</v>
+        <v>5.45</v>
       </c>
       <c r="W31" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.2</v>
+        <v>3.94</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.75</v>
+        <v>2.23</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.67</v>
+        <v>2.63</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.95</v>
+        <v>2.32</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46078.69791666666</v>
@@ -4188,12 +4188,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,76 +4229,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.5</v>
+        <v>1.53</v>
       </c>
       <c r="M32" t="n">
-        <v>3.44</v>
+        <v>4.68</v>
       </c>
       <c r="N32" t="n">
-        <v>2.72</v>
+        <v>6.86</v>
       </c>
       <c r="O32" t="n">
-        <v>2.85</v>
+        <v>1.93</v>
       </c>
       <c r="P32" t="n">
-        <v>2.17</v>
+        <v>2.62</v>
       </c>
       <c r="Q32" t="n">
-        <v>3</v>
+        <v>5.25</v>
       </c>
       <c r="R32" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="S32" t="n">
-        <v>3.04</v>
+        <v>3.6</v>
       </c>
       <c r="T32" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="U32" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="V32" t="n">
-        <v>5.45</v>
+        <v>4.5</v>
       </c>
       <c r="W32" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="X32" t="n">
         <v>1.01</v>
       </c>
       <c r="Y32" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG32" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z32" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH32" t="n">
-        <v>1.5</v>
+        <v>2.81</v>
       </c>
       <c r="AI32" s="3" t="n">
-        <v>46078.69791666666</v>
+        <v>46078.70833333334</v>
       </c>
     </row>
     <row r="33">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="M34" t="n">
-        <v>4.68</v>
+        <v>6.14</v>
       </c>
       <c r="N34" t="n">
-        <v>6.86</v>
+        <v>9.85</v>
       </c>
       <c r="O34" t="n">
-        <v>1.93</v>
+        <v>1.58</v>
       </c>
       <c r="P34" t="n">
-        <v>2.62</v>
+        <v>3.25</v>
       </c>
       <c r="Q34" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="R34" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="S34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V34" t="n">
         <v>3.6</v>
       </c>
-      <c r="T34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V34" t="n">
-        <v>4.5</v>
-      </c>
       <c r="W34" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Z34" t="n">
-        <v>5.25</v>
+        <v>7.25</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.61</v>
+        <v>1.29</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.81</v>
+        <v>3.7</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="M35" t="n">
-        <v>6.14</v>
+        <v>4.58</v>
       </c>
       <c r="N35" t="n">
-        <v>9.85</v>
+        <v>5.49</v>
       </c>
       <c r="O35" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="P35" t="n">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="Q35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R35" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V35" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W35" t="n">
         <v>1.17</v>
       </c>
-      <c r="S35" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T35" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V35" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.25</v>
-      </c>
       <c r="X35" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Z35" t="n">
-        <v>7.25</v>
+        <v>5.3</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.29</v>
+        <v>1.63</v>
       </c>
       <c r="AB35" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AH35" t="n">
-        <v>3.7</v>
+        <v>2.45</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4664,12 +4664,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,76 +4705,76 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>5.49</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AI36" s="3" t="n">
-        <v>46078.70833333334</v>
+        <v>46078.79166666666</v>
       </c>
     </row>
     <row r="37">
@@ -4788,22 +4788,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.97</v>
+        <v>2.17</v>
       </c>
       <c r="M38" t="n">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
       <c r="N38" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="O38" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="P38" t="n">
         <v>2.05</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="R38" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S38" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T38" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U38" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V38" t="n">
-        <v>7.75</v>
+        <v>8.5</v>
       </c>
       <c r="W38" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X38" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46078.79166666666</v>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,49 +5062,49 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.17</v>
+        <v>2.68</v>
       </c>
       <c r="M39" t="n">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="N39" t="n">
-        <v>3.55</v>
+        <v>2.85</v>
       </c>
       <c r="O39" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S39" t="n">
         <v>2.4</v>
       </c>
-      <c r="P39" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.6</v>
-      </c>
       <c r="T39" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U39" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V39" t="n">
-        <v>8.5</v>
+        <v>9.75</v>
       </c>
       <c r="W39" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X39" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AA39" t="n">
         <v>2.3</v>
@@ -5113,25 +5113,25 @@
         <v>1.53</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE39" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="AI39" s="3" t="n">
-        <v>46078.79166666666</v>
+        <v>46078.8125</v>
       </c>
     </row>
     <row r="40">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,76 +5181,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.68</v>
+        <v>1.92</v>
       </c>
       <c r="M40" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="N40" t="n">
-        <v>2.85</v>
+        <v>4.1</v>
       </c>
       <c r="O40" t="n">
-        <v>3.6</v>
+        <v>2.45</v>
       </c>
       <c r="P40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>4</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V40" t="n">
+        <v>7</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA40" t="n">
         <v>2</v>
       </c>
-      <c r="Q40" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S40" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T40" t="n">
+      <c r="AB40" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC40" t="n">
         <v>3.3</v>
       </c>
-      <c r="U40" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V40" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AD40" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.4</v>
+        <v>1.88</v>
       </c>
       <c r="AI40" s="3" t="n">
-        <v>46078.8125</v>
+        <v>46078.83333333334</v>
       </c>
     </row>
     <row r="41">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,76 +5300,76 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="M41" t="n">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="N41" t="n">
-        <v>4.1</v>
+        <v>3.37</v>
       </c>
       <c r="O41" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="P41" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="R41" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S41" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="T41" t="n">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="U41" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V41" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W41" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X41" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z41" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AA41" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB41" t="n">
         <v>1.71</v>
       </c>
       <c r="AC41" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AI41" s="3" t="n">
-        <v>46078.83333333334</v>
+        <v>46078.89583333334</v>
       </c>
     </row>
     <row r="42">
@@ -5488,125 +5488,6 @@
         <v>1.88</v>
       </c>
       <c r="AI42" s="3" t="n">
-        <v>46078.89583333334</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="n">
-        <v>46078</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Grêmio</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Atlético Mineiro</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L43" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="M43" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="N43" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="O43" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P43" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S43" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V43" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X43" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AI43" s="3" t="n">
         <v>46078.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -793,7 +793,7 @@
         <v>2.05</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="R3" t="n">
         <v>1.48</v>
@@ -805,19 +805,19 @@
         <v>3.28</v>
       </c>
       <c r="U3" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="V3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X3" t="n">
         <v>1.04</v>
       </c>
-      <c r="X3" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y3" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z3" t="n">
         <v>2.6</v>
@@ -844,7 +844,7 @@
         <v>1.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46078.375</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="M5" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="N5" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1135,22 +1135,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N6" t="n">
         <v>3.3</v>
       </c>
       <c r="O6" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="P6" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
         <v>1.41</v>
@@ -1159,49 +1159,49 @@
         <v>2.56</v>
       </c>
       <c r="T6" t="n">
-        <v>2.97</v>
+        <v>3.19</v>
       </c>
       <c r="U6" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="V6" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="W6" t="n">
         <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AC6" t="n">
         <v>3.58</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE6" t="n">
         <v>1.96</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46078.4375</v>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.49</v>
+        <v>1.4</v>
       </c>
       <c r="M9" t="n">
-        <v>2.85</v>
+        <v>4.33</v>
       </c>
       <c r="N9" t="n">
-        <v>3.01</v>
+        <v>8</v>
       </c>
       <c r="O9" t="n">
-        <v>3.07</v>
+        <v>1.91</v>
       </c>
       <c r="P9" t="n">
-        <v>1.92</v>
+        <v>2.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.8</v>
+        <v>6.5</v>
       </c>
       <c r="R9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U9" t="n">
         <v>1.44</v>
       </c>
-      <c r="S9" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.26</v>
-      </c>
       <c r="V9" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="W9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X9" t="n">
         <v>1.04</v>
       </c>
-      <c r="X9" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y9" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.69</v>
+        <v>3.55</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.56</v>
+        <v>1.91</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.47</v>
+        <v>2.8</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46078.5</v>
@@ -1575,22 +1575,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1607,77 +1607,77 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46078.5</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46078.5</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,34 +1849,34 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="M12" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="N12" t="n">
-        <v>7.5</v>
+        <v>5.25</v>
       </c>
       <c r="O12" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="P12" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="T12" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U12" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V12" t="n">
         <v>6</v>
@@ -1885,37 +1885,37 @@
         <v>1.09</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z12" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH12" t="n">
-        <v>2.8</v>
+        <v>2.37</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46078.5</v>
@@ -2090,10 +2090,10 @@
         <v>3.5</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N14" t="n">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="O14" t="n">
         <v>3.75</v>
@@ -2105,10 +2105,10 @@
         <v>2.6</v>
       </c>
       <c r="R14" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S14" t="n">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="T14" t="n">
         <v>2.82</v>
@@ -2123,31 +2123,31 @@
         <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE14" t="n">
         <v>1.75</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="AG14" t="n">
         <v>1.3</v>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="M15" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="N15" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="O15" t="n">
         <v>2.05</v>
@@ -2230,16 +2230,16 @@
         <v>3.12</v>
       </c>
       <c r="T15" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="U15" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="V15" t="n">
-        <v>6.05</v>
+        <v>5.95</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
         <v>1.04</v>
@@ -2254,25 +2254,25 @@
         <v>1.67</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46078.60416666666</v>
@@ -2444,46 +2444,46 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.05</v>
+        <v>2.62</v>
       </c>
       <c r="M17" t="n">
         <v>2.9</v>
       </c>
       <c r="N17" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="O17" t="n">
-        <v>3.98</v>
+        <v>3.72</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.2</v>
+        <v>3.52</v>
       </c>
       <c r="R17" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="S17" t="n">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="T17" t="n">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="U17" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="V17" t="n">
-        <v>9.5</v>
+        <v>8.4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="Z17" t="n">
         <v>2.55</v>
@@ -2492,25 +2492,25 @@
         <v>2.16</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46078.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.25</v>
+        <v>2.71</v>
       </c>
       <c r="M18" t="n">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.93</v>
+        <v>3.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.62</v>
+        <v>1.95</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.44</v>
+        <v>1.92</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46078.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>7</v>
+        <v>2.32</v>
       </c>
       <c r="M19" t="n">
-        <v>5.5</v>
+        <v>2.86</v>
       </c>
       <c r="N19" t="n">
-        <v>1.37</v>
+        <v>3.14</v>
       </c>
       <c r="O19" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="Z19" t="n">
-        <v>5</v>
+        <v>1.93</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.48</v>
+        <v>2.62</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.5</v>
+        <v>1.44</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46078.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.71</v>
+        <v>7.25</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="N20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P20" t="n">
         <v>2.6</v>
       </c>
-      <c r="O20" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC20" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V20" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AD20" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.49</v>
+        <v>1.15</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46078.625</v>
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="M21" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="N21" t="n">
-        <v>2.97</v>
+        <v>2.66</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="O22" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG22" t="n">
         <v>1.25</v>
       </c>
-      <c r="M22" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="N22" t="n">
-        <v>11</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>9</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V22" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AH22" t="n">
-        <v>3.42</v>
+        <v>1.13</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46078.65625</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.25</v>
+        <v>1.25</v>
       </c>
       <c r="M23" t="n">
-        <v>3.35</v>
+        <v>5.4</v>
       </c>
       <c r="N23" t="n">
-        <v>1.75</v>
+        <v>11</v>
       </c>
       <c r="O23" t="n">
-        <v>5.42</v>
+        <v>1.71</v>
       </c>
       <c r="P23" t="n">
-        <v>1.97</v>
+        <v>2.34</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.55</v>
+        <v>9</v>
       </c>
       <c r="R23" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="S23" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="T23" t="n">
         <v>2.53</v>
       </c>
-      <c r="T23" t="n">
-        <v>2.6</v>
-      </c>
       <c r="U23" t="n">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="V23" t="n">
-        <v>7.8</v>
+        <v>6.1</v>
       </c>
       <c r="W23" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.72</v>
+        <v>1.94</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.15</v>
+        <v>2.74</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.91</v>
+        <v>2.28</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.83</v>
+        <v>1.47</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.13</v>
+        <v>3.42</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46078.65625</v>
@@ -3277,19 +3277,19 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>12</v>
+        <v>10.7</v>
       </c>
       <c r="M24" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="N24" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="O24" t="n">
         <v>9</v>
       </c>
       <c r="P24" t="n">
-        <v>3.37</v>
+        <v>3.41</v>
       </c>
       <c r="Q24" t="n">
         <v>1.44</v>
@@ -3304,7 +3304,7 @@
         <v>1.83</v>
       </c>
       <c r="U24" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V24" t="n">
         <v>3.5</v>
@@ -3319,19 +3319,19 @@
         <v>1.05</v>
       </c>
       <c r="Z24" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AB24" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="AC24" t="n">
         <v>1.75</v>
       </c>
       <c r="AD24" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AE24" t="n">
         <v>1.74</v>
@@ -3396,25 +3396,25 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="M25" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N25" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O25" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P25" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="Q25" t="n">
         <v>3.1</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S25" t="n">
         <v>2.59</v>
@@ -3423,37 +3423,37 @@
         <v>2.96</v>
       </c>
       <c r="U25" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="V25" t="n">
         <v>8</v>
       </c>
       <c r="W25" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA25" t="n">
         <v>2.02</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC25" t="n">
         <v>3.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AF25" t="n">
         <v>2.05</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="M26" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="N26" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="O26" t="n">
-        <v>2.86</v>
+        <v>3.4</v>
       </c>
       <c r="P26" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.65</v>
+        <v>3.75</v>
       </c>
       <c r="R26" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S26" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="T26" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="U26" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V26" t="n">
-        <v>8.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W26" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X26" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Y26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB26" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z26" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AC26" t="n">
-        <v>3.86</v>
+        <v>5.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46078.6875</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.24</v>
+        <v>2.05</v>
       </c>
       <c r="M27" t="n">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="N27" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="O27" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="P27" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="S27" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="T27" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="U27" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V27" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X27" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.25</v>
+        <v>2.59</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AC27" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46078.6875</v>
@@ -3759,7 +3759,7 @@
         <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>6.35</v>
+        <v>5.5</v>
       </c>
       <c r="O28" t="n">
         <v>2.25</v>
@@ -3768,7 +3768,7 @@
         <v>1.89</v>
       </c>
       <c r="Q28" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="R28" t="n">
         <v>1.55</v>
@@ -3777,7 +3777,7 @@
         <v>2.3</v>
       </c>
       <c r="T28" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U28" t="n">
         <v>1.29</v>
@@ -3798,7 +3798,7 @@
         <v>2.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="AB28" t="n">
         <v>1.5</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="M34" t="n">
-        <v>6.14</v>
+        <v>4.58</v>
       </c>
       <c r="N34" t="n">
-        <v>9.85</v>
+        <v>5.49</v>
       </c>
       <c r="O34" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="P34" t="n">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="Q34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R34" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V34" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W34" t="n">
         <v>1.17</v>
       </c>
-      <c r="S34" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T34" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V34" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.25</v>
-      </c>
       <c r="X34" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Z34" t="n">
-        <v>7.25</v>
+        <v>5.3</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.29</v>
+        <v>1.63</v>
       </c>
       <c r="AB34" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AH34" t="n">
-        <v>3.7</v>
+        <v>2.45</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="M35" t="n">
-        <v>4.58</v>
+        <v>6.14</v>
       </c>
       <c r="N35" t="n">
-        <v>5.49</v>
+        <v>9.85</v>
       </c>
       <c r="O35" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="P35" t="n">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="Q35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R35" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="S35" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V35" t="n">
         <v>3.6</v>
       </c>
-      <c r="T35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V35" t="n">
-        <v>4.6</v>
-      </c>
       <c r="W35" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X35" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Z35" t="n">
-        <v>5.3</v>
+        <v>7.25</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.63</v>
+        <v>1.29</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.45</v>
+        <v>3.7</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.97</v>
+        <v>2.17</v>
       </c>
       <c r="M37" t="n">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
       <c r="N37" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="O37" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="P37" t="n">
         <v>2.05</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="R37" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S37" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T37" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U37" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V37" t="n">
-        <v>7.75</v>
+        <v>8.5</v>
       </c>
       <c r="W37" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X37" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.17</v>
+        <v>2.97</v>
       </c>
       <c r="M38" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="N38" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="O38" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="P38" t="n">
         <v>2.05</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="R38" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S38" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T38" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V38" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG38" t="n">
         <v>1.33</v>
       </c>
-      <c r="V38" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH38" t="n">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46078.79166666666</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,28 +5300,28 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="M41" t="n">
-        <v>3.44</v>
+        <v>3.79</v>
       </c>
       <c r="N41" t="n">
-        <v>3.37</v>
+        <v>5.14</v>
       </c>
       <c r="O41" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="P41" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="R41" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S41" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="T41" t="n">
         <v>2.8</v>
@@ -5336,37 +5336,37 @@
         <v>1.08</v>
       </c>
       <c r="X41" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD41" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z41" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD41" t="n">
+      <c r="AE41" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG41" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE41" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH41" t="n">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46078.89583333334</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,28 +5419,28 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="M42" t="n">
-        <v>3.79</v>
+        <v>3.44</v>
       </c>
       <c r="N42" t="n">
-        <v>5.14</v>
+        <v>3.37</v>
       </c>
       <c r="O42" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="P42" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="R42" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S42" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="T42" t="n">
         <v>2.8</v>
@@ -5455,37 +5455,37 @@
         <v>1.08</v>
       </c>
       <c r="X42" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y42" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD42" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z42" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB42" t="n">
+      <c r="AE42" t="n">
         <v>1.73</v>
       </c>
-      <c r="AC42" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF42" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46078.89583333334</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -662,19 +662,19 @@
         <v>3.1</v>
       </c>
       <c r="M2" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P2" t="n">
         <v>2.1</v>
       </c>
-      <c r="O2" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.05</v>
-      </c>
       <c r="Q2" t="n">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="R2" t="n">
         <v>1.39</v>
@@ -683,49 +683,49 @@
         <v>2.63</v>
       </c>
       <c r="T2" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="U2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V2" t="n">
-        <v>6.65</v>
+        <v>6.75</v>
       </c>
       <c r="W2" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
         <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AG2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH2" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.27</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46078.35416666666</v>
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="M3" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="N3" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="O3" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="P3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q3" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q3" t="n">
-        <v>2.17</v>
-      </c>
       <c r="R3" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="T3" t="n">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AF3" t="n">
         <v>1.53</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46078.375</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46078.41666666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="M6" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
         <v>3.3</v>
       </c>
       <c r="O6" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="P6" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>4.46</v>
       </c>
       <c r="R6" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="S6" t="n">
-        <v>2.56</v>
+        <v>2.31</v>
       </c>
       <c r="T6" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="V6" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="Z6" t="n">
-        <v>3</v>
+        <v>2.59</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46078.4375</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46078.4375</v>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46078.45833333334</v>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="M9" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>8</v>
+        <v>2.87</v>
       </c>
       <c r="O9" t="n">
-        <v>1.91</v>
+        <v>2.9</v>
       </c>
       <c r="P9" t="n">
-        <v>2.38</v>
+        <v>1.82</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.5</v>
+        <v>3.9</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>2.31</v>
       </c>
       <c r="T9" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="U9" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="V9" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.55</v>
+        <v>2.81</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.89</v>
+        <v>2.23</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.1</v>
+        <v>4.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.8</v>
+        <v>1.46</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46078.5</v>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46078.5</v>
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.49</v>
+        <v>4.15</v>
       </c>
       <c r="M11" t="n">
-        <v>2.85</v>
+        <v>4.05</v>
       </c>
       <c r="N11" t="n">
-        <v>3.01</v>
+        <v>1.67</v>
       </c>
       <c r="O11" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
         <v>1.44</v>
       </c>
-      <c r="S11" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V11" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AB11" t="n">
-        <v>1.56</v>
+        <v>2.62</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>46078.5</v>
+        <v>46078.5625</v>
       </c>
     </row>
     <row r="12">
@@ -1808,27 +1808,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1845,44 +1845,44 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.56</v>
+        <v>3.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>5.25</v>
+        <v>1.84</v>
       </c>
       <c r="O12" t="n">
-        <v>2.1</v>
+        <v>3.75</v>
       </c>
       <c r="P12" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.5</v>
+        <v>2.6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="T12" t="n">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="U12" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="V12" t="n">
-        <v>6</v>
+        <v>7.1</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
         <v>1.05</v>
@@ -1894,31 +1894,31 @@
         <v>3.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.73</v>
+        <v>1.97</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.37</v>
+        <v>1.3</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>46078.5</v>
+        <v>46078.60416666666</v>
       </c>
     </row>
     <row r="13">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,76 +1968,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="M13" t="n">
         <v>3.9</v>
       </c>
       <c r="N13" t="n">
+        <v>5</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V13" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.7</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46078.5625</v>
+        <v>46078.60416666666</v>
       </c>
     </row>
     <row r="14">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,76 +2087,76 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q14" t="n">
         <v>3.5</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="O14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P14" t="n">
+      <c r="R14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB14" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V14" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AC14" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.3</v>
+        <v>1.68</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46078.60416666666</v>
+        <v>46078.61458333334</v>
       </c>
     </row>
     <row r="15">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,76 +2206,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.6</v>
+        <v>2.62</v>
       </c>
       <c r="M15" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="N15" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="O15" t="n">
-        <v>2.05</v>
+        <v>3.72</v>
       </c>
       <c r="P15" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.8</v>
+        <v>3.52</v>
       </c>
       <c r="R15" t="n">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="S15" t="n">
-        <v>3.12</v>
+        <v>2.18</v>
       </c>
       <c r="T15" t="n">
-        <v>2.49</v>
+        <v>3.58</v>
       </c>
       <c r="U15" t="n">
-        <v>1.45</v>
+        <v>1.21</v>
       </c>
       <c r="V15" t="n">
-        <v>5.95</v>
+        <v>8.4</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.17</v>
+        <v>1.46</v>
       </c>
       <c r="Z15" t="n">
-        <v>4</v>
+        <v>2.55</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.67</v>
+        <v>2.16</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.69</v>
+        <v>3.75</v>
       </c>
       <c r="AD15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1.4</v>
       </c>
-      <c r="AE15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AI15" s="3" t="n">
-        <v>46078.60416666666</v>
+        <v>46078.625</v>
       </c>
     </row>
     <row r="16">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,76 +2325,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.12</v>
+        <v>2.84</v>
       </c>
       <c r="M16" t="n">
-        <v>3.8</v>
+        <v>2.85</v>
       </c>
       <c r="N16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q16" t="n">
         <v>3.3</v>
       </c>
-      <c r="O16" t="n">
+      <c r="R16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T16" t="n">
         <v>2.62</v>
       </c>
-      <c r="P16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R16" t="n">
+      <c r="U16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V16" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y16" t="n">
         <v>1.3</v>
       </c>
-      <c r="S16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.19</v>
-      </c>
       <c r="Z16" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46078.61458333334</v>
+        <v>46078.625</v>
       </c>
     </row>
     <row r="17">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.62</v>
+        <v>7.25</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="N17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="O17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB17" t="n">
         <v>2.5</v>
       </c>
-      <c r="O17" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="V17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AC17" t="n">
-        <v>3.75</v>
+        <v>2.15</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.11</v>
+        <v>1.62</v>
       </c>
       <c r="AE17" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.66</v>
+        <v>2.15</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46078.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.71</v>
+        <v>2.32</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="N18" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="O18" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA18" t="n">
         <v>2.62</v>
       </c>
-      <c r="U18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V18" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AB18" t="n">
-        <v>1.92</v>
+        <v>1.44</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46078.625</v>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="M19" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="N19" t="n">
-        <v>3.14</v>
+        <v>2.66</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2721,10 +2721,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
         <v>2.62</v>
@@ -2751,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>46078.625</v>
+        <v>46078.64583333334</v>
       </c>
     </row>
     <row r="20">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,76 +2801,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>7.25</v>
+        <v>3.3</v>
       </c>
       <c r="M20" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="N20" t="n">
-        <v>1.37</v>
+        <v>2.1</v>
       </c>
       <c r="O20" t="n">
-        <v>4.8</v>
+        <v>4.62</v>
       </c>
       <c r="P20" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.94</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="S20" t="n">
-        <v>3.6</v>
+        <v>2.39</v>
       </c>
       <c r="T20" t="n">
-        <v>2.11</v>
+        <v>2.8</v>
       </c>
       <c r="U20" t="n">
-        <v>1.65</v>
+        <v>1.28</v>
       </c>
       <c r="V20" t="n">
-        <v>4.6</v>
+        <v>9</v>
       </c>
       <c r="W20" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="Z20" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.48</v>
+        <v>2.27</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.5</v>
+        <v>1.58</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.15</v>
+        <v>4.05</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.62</v>
+        <v>1.16</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AI20" s="3" t="n">
-        <v>46078.625</v>
+        <v>46078.65625</v>
       </c>
     </row>
     <row r="21">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,76 +2920,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.6</v>
+        <v>1.18</v>
       </c>
       <c r="M21" t="n">
-        <v>2.8</v>
+        <v>5.5</v>
       </c>
       <c r="N21" t="n">
-        <v>2.66</v>
+        <v>12</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.62</v>
+        <v>1.62</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.44</v>
+        <v>2.15</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>46078.64583333334</v>
+        <v>46078.65625</v>
       </c>
     </row>
     <row r="22">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,76 +3039,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.25</v>
+        <v>2.63</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V22" t="n">
+        <v>8</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.75</v>
       </c>
-      <c r="O22" t="n">
-        <v>5.42</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V22" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AF22" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>46078.65625</v>
+        <v>46078.66666666666</v>
       </c>
     </row>
     <row r="23">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,76 +3158,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.25</v>
+        <v>10.7</v>
       </c>
       <c r="M23" t="n">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="N23" t="n">
-        <v>11</v>
+        <v>1.07</v>
       </c>
       <c r="O23" t="n">
-        <v>1.71</v>
+        <v>9</v>
       </c>
       <c r="P23" t="n">
-        <v>2.34</v>
+        <v>3.41</v>
       </c>
       <c r="Q23" t="n">
-        <v>9</v>
+        <v>1.44</v>
       </c>
       <c r="R23" t="n">
-        <v>1.34</v>
+        <v>1.12</v>
       </c>
       <c r="S23" t="n">
-        <v>2.83</v>
+        <v>4.8</v>
       </c>
       <c r="T23" t="n">
-        <v>2.53</v>
+        <v>1.83</v>
       </c>
       <c r="U23" t="n">
-        <v>1.45</v>
+        <v>1.86</v>
       </c>
       <c r="V23" t="n">
-        <v>6.1</v>
+        <v>3.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.68</v>
+        <v>1.24</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.94</v>
+        <v>3.4</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.74</v>
+        <v>1.75</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.35</v>
+        <v>1.95</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.28</v>
+        <v>1.74</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.42</v>
+        <v>1.04</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>46078.65625</v>
+        <v>46078.66666666666</v>
       </c>
     </row>
     <row r="24">
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,76 +3277,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>10.7</v>
+        <v>1.57</v>
       </c>
       <c r="M24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V24" t="n">
         <v>9</v>
       </c>
-      <c r="N24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="O24" t="n">
-        <v>9</v>
-      </c>
-      <c r="P24" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="V24" t="n">
-        <v>3.5</v>
-      </c>
       <c r="W24" t="n">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.05</v>
+        <v>1.48</v>
       </c>
       <c r="Z24" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.24</v>
+        <v>2.44</v>
       </c>
       <c r="AB24" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.75</v>
+        <v>4.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.95</v>
+        <v>1.17</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.74</v>
+        <v>2.4</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>46078.66666666666</v>
+        <v>46078.6875</v>
       </c>
     </row>
     <row r="25">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,76 +3396,76 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="M25" t="n">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="N25" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="O25" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="P25" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="S25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z25" t="n">
         <v>2.59</v>
       </c>
-      <c r="T25" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V25" t="n">
-        <v>8</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3</v>
-      </c>
       <c r="AA25" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AG25" t="n">
         <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AI25" s="3" t="n">
-        <v>46078.66666666666</v>
+        <v>46078.6875</v>
       </c>
     </row>
     <row r="26">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,76 +3634,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="M27" t="n">
-        <v>2.84</v>
+        <v>3.35</v>
       </c>
       <c r="N27" t="n">
-        <v>3.3</v>
+        <v>2.72</v>
       </c>
       <c r="O27" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="P27" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="R27" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>2.4</v>
+        <v>2.73</v>
       </c>
       <c r="T27" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="U27" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="V27" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X27" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.59</v>
+        <v>3.24</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AC27" t="n">
-        <v>4</v>
+        <v>3.41</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AE27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF27" t="n">
         <v>1.95</v>
       </c>
-      <c r="AF27" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>46078.6875</v>
+        <v>46078.69791666666</v>
       </c>
     </row>
     <row r="28">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,76 +3753,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.57</v>
+        <v>1.19</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>6.4</v>
       </c>
       <c r="N28" t="n">
-        <v>5.5</v>
+        <v>12</v>
       </c>
       <c r="O28" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V28" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AC28" t="n">
         <v>2.25</v>
       </c>
-      <c r="P28" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V28" t="n">
-        <v>9</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AD28" t="n">
-        <v>1.17</v>
+        <v>1.64</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.3</v>
+        <v>4.33</v>
       </c>
       <c r="AI28" s="3" t="n">
-        <v>46078.6875</v>
+        <v>46078.69791666666</v>
       </c>
     </row>
     <row r="29">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V29" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y29" t="n">
         <v>1.18</v>
       </c>
-      <c r="M29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N29" t="n">
-        <v>16.64</v>
-      </c>
-      <c r="O29" t="n">
+      <c r="Z29" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE29" t="n">
         <v>1.53</v>
       </c>
-      <c r="P29" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>10</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V29" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AF29" t="n">
-        <v>1.59</v>
+        <v>2.3</v>
       </c>
       <c r="AG29" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>4.4</v>
+        <v>1.53</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46078.69791666666</v>
@@ -3950,12 +3950,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,76 +3991,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.5</v>
+        <v>1.53</v>
       </c>
       <c r="M30" t="n">
-        <v>3.35</v>
+        <v>4.68</v>
       </c>
       <c r="N30" t="n">
-        <v>2.6</v>
+        <v>6.86</v>
       </c>
       <c r="O30" t="n">
-        <v>3</v>
+        <v>1.93</v>
       </c>
       <c r="P30" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB30" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q30" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V30" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AC30" t="n">
-        <v>3.67</v>
+        <v>2.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.29</v>
+        <v>1.63</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.53</v>
+        <v>2.81</v>
       </c>
       <c r="AI30" s="3" t="n">
-        <v>46078.69791666666</v>
+        <v>46078.70833333334</v>
       </c>
     </row>
     <row r="31">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,76 +4110,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.5</v>
+        <v>1.63</v>
       </c>
       <c r="M31" t="n">
-        <v>3.44</v>
+        <v>4.58</v>
       </c>
       <c r="N31" t="n">
-        <v>2.72</v>
+        <v>5.49</v>
       </c>
       <c r="O31" t="n">
-        <v>2.85</v>
+        <v>1.95</v>
       </c>
       <c r="P31" t="n">
-        <v>2.17</v>
+        <v>2.55</v>
       </c>
       <c r="Q31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="S31" t="n">
-        <v>3.04</v>
+        <v>3.6</v>
       </c>
       <c r="T31" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="U31" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="V31" t="n">
-        <v>5.45</v>
+        <v>4.6</v>
       </c>
       <c r="W31" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="X31" t="n">
         <v>1.01</v>
       </c>
       <c r="Y31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG31" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z31" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH31" t="n">
-        <v>1.5</v>
+        <v>2.45</v>
       </c>
       <c r="AI31" s="3" t="n">
-        <v>46078.69791666666</v>
+        <v>46078.70833333334</v>
       </c>
     </row>
     <row r="32">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="M32" t="n">
-        <v>4.68</v>
+        <v>3.54</v>
       </c>
       <c r="N32" t="n">
-        <v>6.86</v>
+        <v>4.08</v>
       </c>
       <c r="O32" t="n">
-        <v>1.93</v>
+        <v>2.38</v>
       </c>
       <c r="P32" t="n">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="R32" t="n">
-        <v>1.23</v>
+        <v>1.47</v>
       </c>
       <c r="S32" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="T32" t="n">
-        <v>2.1</v>
+        <v>3.22</v>
       </c>
       <c r="U32" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="V32" t="n">
-        <v>4.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W32" t="n">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="X32" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.25</v>
+        <v>2.8</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.2</v>
+        <v>3.92</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.63</v>
+        <v>1.18</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.65</v>
+        <v>2.03</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.81</v>
+        <v>1.95</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M33" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="N33" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="P33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>6</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T33" t="n">
         <v>1.85</v>
       </c>
-      <c r="M33" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="N33" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="O33" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T33" t="n">
-        <v>3.22</v>
-      </c>
       <c r="U33" t="n">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="V33" t="n">
-        <v>8.199999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="W33" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="X33" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.4</v>
+        <v>1.07</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.8</v>
+        <v>7.25</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.95</v>
+        <v>1.29</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.75</v>
+        <v>3.4</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.92</v>
+        <v>1.87</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.18</v>
+        <v>1.83</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.03</v>
+        <v>1.66</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.95</v>
+        <v>3.7</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4426,12 +4426,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4463,80 +4463,80 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.63</v>
+        <v>1.14</v>
       </c>
       <c r="M34" t="n">
-        <v>4.58</v>
+        <v>6.09</v>
       </c>
       <c r="N34" t="n">
-        <v>5.49</v>
+        <v>13.58</v>
       </c>
       <c r="O34" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="P34" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="Q34" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="R34" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S34" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T34" t="n">
         <v>2.1</v>
       </c>
       <c r="U34" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="V34" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="W34" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y34" t="n">
         <v>1.17</v>
       </c>
-      <c r="X34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.09</v>
-      </c>
       <c r="Z34" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.6</v>
+        <v>2.38</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.45</v>
+        <v>4.8</v>
       </c>
       <c r="AI34" s="3" t="n">
-        <v>46078.70833333334</v>
+        <v>46078.72916666666</v>
       </c>
     </row>
     <row r="35">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4582,80 +4582,80 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.33</v>
+        <v>5.5</v>
       </c>
       <c r="M35" t="n">
-        <v>6.14</v>
+        <v>3.8</v>
       </c>
       <c r="N35" t="n">
-        <v>9.85</v>
+        <v>1.5</v>
       </c>
       <c r="O35" t="n">
-        <v>1.58</v>
+        <v>6.34</v>
       </c>
       <c r="P35" t="n">
-        <v>3.25</v>
+        <v>2.11</v>
       </c>
       <c r="Q35" t="n">
-        <v>6</v>
+        <v>2.09</v>
       </c>
       <c r="R35" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="S35" t="n">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="T35" t="n">
-        <v>1.85</v>
+        <v>2.75</v>
       </c>
       <c r="U35" t="n">
-        <v>1.85</v>
+        <v>1.36</v>
       </c>
       <c r="V35" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="W35" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="X35" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="Z35" t="n">
-        <v>7.25</v>
+        <v>3.35</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.29</v>
+        <v>1.87</v>
       </c>
       <c r="AB35" t="n">
-        <v>3.4</v>
+        <v>1.81</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.87</v>
+        <v>3.2</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.83</v>
+        <v>1.27</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.66</v>
+        <v>1.92</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AH35" t="n">
-        <v>3.7</v>
+        <v>1.06</v>
       </c>
       <c r="AI35" s="3" t="n">
-        <v>46078.70833333334</v>
+        <v>46078.72916666666</v>
       </c>
     </row>
     <row r="36">
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="M36" t="n">
-        <v>2.81</v>
+        <v>3.34</v>
       </c>
       <c r="N36" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O36" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V36" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z36" t="n">
         <v>2.8</v>
       </c>
-      <c r="P36" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>4</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T36" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U36" t="n">
+      <c r="AA36" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD36" t="n">
         <v>1.22</v>
       </c>
-      <c r="V36" t="n">
-        <v>11</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AE36" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4788,22 +4788,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="M37" t="n">
-        <v>3.34</v>
+        <v>2.81</v>
       </c>
       <c r="N37" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="O37" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="P37" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="R37" t="n">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="S37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V37" t="n">
+        <v>11</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA37" t="n">
         <v>2.6</v>
       </c>
-      <c r="T37" t="n">
-        <v>3</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V37" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AB37" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH37" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.95</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46078.79166666666</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,28 +5300,28 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="M41" t="n">
-        <v>3.79</v>
+        <v>3.44</v>
       </c>
       <c r="N41" t="n">
-        <v>5.14</v>
+        <v>3.37</v>
       </c>
       <c r="O41" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="P41" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="R41" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S41" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="T41" t="n">
         <v>2.8</v>
@@ -5336,37 +5336,37 @@
         <v>1.08</v>
       </c>
       <c r="X41" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y41" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD41" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z41" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB41" t="n">
+      <c r="AE41" t="n">
         <v>1.73</v>
       </c>
-      <c r="AC41" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF41" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46078.89583333334</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,28 +5419,28 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="M42" t="n">
-        <v>3.44</v>
+        <v>3.79</v>
       </c>
       <c r="N42" t="n">
-        <v>3.37</v>
+        <v>5.14</v>
       </c>
       <c r="O42" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="P42" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="R42" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S42" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="T42" t="n">
         <v>2.8</v>
@@ -5455,37 +5455,37 @@
         <v>1.08</v>
       </c>
       <c r="X42" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD42" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z42" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD42" t="n">
+      <c r="AE42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG42" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE42" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH42" t="n">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46078.89583333334</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>2.84</v>
       </c>
       <c r="N24" t="n">
-        <v>5.5</v>
+        <v>3.3</v>
       </c>
       <c r="O24" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="P24" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>7.3</v>
+        <v>4.4</v>
       </c>
       <c r="R24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V24" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB24" t="n">
         <v>1.55</v>
       </c>
-      <c r="S24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V24" t="n">
-        <v>9</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AC24" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AD24" t="n">
         <v>1.17</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.3</v>
+        <v>1.56</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46078.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="M25" t="n">
-        <v>2.84</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="O25" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="P25" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.4</v>
+        <v>7.3</v>
       </c>
       <c r="R25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V25" t="n">
+        <v>9</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AB25" t="n">
         <v>1.5</v>
       </c>
-      <c r="S25" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V25" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AC25" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AD25" t="n">
         <v>1.17</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.56</v>
+        <v>2.3</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46078.6875</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.14</v>
+        <v>5.5</v>
       </c>
       <c r="M34" t="n">
-        <v>6.09</v>
+        <v>3.8</v>
       </c>
       <c r="N34" t="n">
-        <v>13.58</v>
+        <v>1.5</v>
       </c>
       <c r="O34" t="n">
-        <v>1.5</v>
+        <v>6.34</v>
       </c>
       <c r="P34" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S34" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q34" t="n">
-        <v>12</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.65</v>
-      </c>
       <c r="T34" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="U34" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="V34" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="W34" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="Z34" t="n">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.25</v>
+        <v>1.81</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.38</v>
+        <v>1.92</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AH34" t="n">
-        <v>4.8</v>
+        <v>1.06</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46078.72916666666</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4582,77 +4582,77 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>5.5</v>
+        <v>1.14</v>
       </c>
       <c r="M35" t="n">
-        <v>3.8</v>
+        <v>6.09</v>
       </c>
       <c r="N35" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="O35" t="n">
         <v>1.5</v>
       </c>
-      <c r="O35" t="n">
-        <v>6.34</v>
-      </c>
       <c r="P35" t="n">
-        <v>2.11</v>
+        <v>2.75</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.09</v>
+        <v>12</v>
       </c>
       <c r="R35" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S35" t="n">
-        <v>2.75</v>
+        <v>3.65</v>
       </c>
       <c r="T35" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="U35" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="V35" t="n">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="W35" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.87</v>
+        <v>1.53</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.81</v>
+        <v>2.25</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.92</v>
+        <v>2.38</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.06</v>
+        <v>4.8</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46078.72916666666</v>
@@ -4788,22 +4788,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.23</v>
+        <v>2.97</v>
       </c>
       <c r="M37" t="n">
-        <v>2.81</v>
+        <v>3.27</v>
       </c>
       <c r="N37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V37" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC37" t="n">
         <v>3.4</v>
       </c>
-      <c r="O37" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P37" t="n">
+      <c r="AD37" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF37" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q37" t="n">
-        <v>4</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T37" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V37" t="n">
-        <v>11</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AG37" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4907,22 +4907,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.97</v>
+        <v>2.23</v>
       </c>
       <c r="M38" t="n">
-        <v>3.27</v>
+        <v>2.81</v>
       </c>
       <c r="N38" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="O38" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>4</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T38" t="n">
         <v>3.5</v>
       </c>
-      <c r="P38" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.9</v>
-      </c>
       <c r="U38" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="V38" t="n">
-        <v>7.75</v>
+        <v>11</v>
       </c>
       <c r="W38" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X38" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.32</v>
+        <v>1.52</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.91</v>
+        <v>1.66</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46078.79166666666</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,28 +5300,28 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="M41" t="n">
-        <v>3.44</v>
+        <v>3.79</v>
       </c>
       <c r="N41" t="n">
-        <v>3.37</v>
+        <v>5.14</v>
       </c>
       <c r="O41" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="P41" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="R41" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S41" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="T41" t="n">
         <v>2.8</v>
@@ -5336,37 +5336,37 @@
         <v>1.08</v>
       </c>
       <c r="X41" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD41" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z41" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD41" t="n">
+      <c r="AE41" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG41" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE41" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH41" t="n">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46078.89583333334</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,28 +5419,28 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="M42" t="n">
-        <v>3.79</v>
+        <v>3.44</v>
       </c>
       <c r="N42" t="n">
-        <v>5.14</v>
+        <v>3.37</v>
       </c>
       <c r="O42" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="P42" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="R42" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S42" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="T42" t="n">
         <v>2.8</v>
@@ -5455,37 +5455,37 @@
         <v>1.08</v>
       </c>
       <c r="X42" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y42" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD42" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z42" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB42" t="n">
+      <c r="AE42" t="n">
         <v>1.73</v>
       </c>
-      <c r="AC42" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF42" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46078.89583333334</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI42"/>
+  <dimension ref="A1:AI43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -642,30 +642,30 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.1</v>
+        <v>3.21</v>
       </c>
       <c r="M2" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="N2" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="O2" t="n">
         <v>3.5</v>
@@ -674,34 +674,34 @@
         <v>2.1</v>
       </c>
       <c r="Q2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T2" t="n">
         <v>2.75</v>
       </c>
-      <c r="R2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.79</v>
-      </c>
       <c r="U2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V2" t="n">
-        <v>6.75</v>
+        <v>6.6</v>
       </c>
       <c r="W2" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z2" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="AA2" t="n">
         <v>2</v>
@@ -710,19 +710,19 @@
         <v>1.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AD2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG2" t="n">
         <v>1.26</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.33</v>
       </c>
       <c r="AH2" t="n">
         <v>1.3</v>
@@ -761,10 +761,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -774,77 +774,77 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M3" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N3" t="n">
         <v>1.58</v>
       </c>
       <c r="O3" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.05</v>
+        <v>2.26</v>
       </c>
       <c r="R3" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>2.49</v>
+        <v>2.29</v>
       </c>
       <c r="T3" t="n">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="U3" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="V3" t="n">
-        <v>8.1</v>
+        <v>10</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
         <v>1.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG3" t="n">
         <v>1.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46078.375</v>
@@ -1254,37 +1254,37 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="M7" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N7" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="P7" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S7" t="n">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="T7" t="n">
-        <v>3.19</v>
+        <v>2.9</v>
       </c>
       <c r="U7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V7" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="W7" t="n">
         <v>1.02</v>
@@ -1296,31 +1296,31 @@
         <v>1.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.58</v>
+        <v>3.48</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.96</v>
+        <v>1.76</v>
       </c>
       <c r="AF7" t="n">
         <v>1.85</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46078.4375</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="O9" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S9" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="T9" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U9" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="V9" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.05</v>
+        <v>4.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46078.5</v>
@@ -1575,22 +1575,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1607,77 +1607,77 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.55</v>
+        <v>1.55</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="N10" t="n">
-        <v>2.7</v>
+        <v>6</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>2.15</v>
       </c>
       <c r="P10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF10" t="n">
         <v>1.85</v>
       </c>
-      <c r="Q10" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AG10" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.41</v>
+        <v>2.3</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46078.5</v>
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.15</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
+        <v>3</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V11" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC11" t="n">
         <v>4.05</v>
       </c>
-      <c r="N11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>46078.5625</v>
+        <v>46078.5</v>
       </c>
     </row>
     <row r="12">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,76 +1849,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>4.05</v>
       </c>
       <c r="N12" t="n">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="O12" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.99</v>
+        <v>1.44</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.75</v>
+        <v>2.62</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>46078.60416666666</v>
+        <v>46078.5625</v>
       </c>
     </row>
     <row r="13">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="M13" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>1.84</v>
       </c>
       <c r="O13" t="n">
-        <v>2.05</v>
+        <v>3.75</v>
       </c>
       <c r="P13" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="R13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V13" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.29</v>
       </c>
-      <c r="S13" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V13" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AE13" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.25</v>
+        <v>1.3</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46078.60416666666</v>
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,76 +2087,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.15</v>
+        <v>1.6</v>
       </c>
       <c r="M14" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="N14" t="n">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="O14" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="R14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S14" t="n">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="T14" t="n">
-        <v>2.39</v>
+        <v>2.49</v>
       </c>
       <c r="U14" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="V14" t="n">
-        <v>5.5</v>
+        <v>5.95</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AA14" t="n">
         <v>1.67</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.68</v>
+        <v>2.25</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46078.61458333334</v>
+        <v>46078.60416666666</v>
       </c>
     </row>
     <row r="15">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,76 +2206,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9</v>
+        <v>3.55</v>
       </c>
       <c r="N15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O15" t="n">
         <v>2.5</v>
       </c>
-      <c r="O15" t="n">
-        <v>3.72</v>
-      </c>
       <c r="P15" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.59</v>
+        <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>2.18</v>
+        <v>3.4</v>
       </c>
       <c r="T15" t="n">
-        <v>3.58</v>
+        <v>2.39</v>
       </c>
       <c r="U15" t="n">
-        <v>1.21</v>
+        <v>1.53</v>
       </c>
       <c r="V15" t="n">
-        <v>8.4</v>
+        <v>5.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.46</v>
+        <v>1.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.55</v>
+        <v>4.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.16</v>
+        <v>1.67</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.75</v>
+        <v>2.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.11</v>
+        <v>1.44</v>
       </c>
       <c r="AE15" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46078.625</v>
+        <v>46078.61458333334</v>
       </c>
     </row>
     <row r="16">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.84</v>
+        <v>2.32</v>
       </c>
       <c r="M16" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="N16" t="n">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="O16" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA16" t="n">
         <v>2.62</v>
       </c>
-      <c r="U16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V16" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AB16" t="n">
-        <v>1.92</v>
+        <v>1.44</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46078.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>7.25</v>
+        <v>2.84</v>
       </c>
       <c r="M17" t="n">
-        <v>5.5</v>
+        <v>2.85</v>
       </c>
       <c r="N17" t="n">
-        <v>1.37</v>
+        <v>2.25</v>
       </c>
       <c r="O17" t="n">
-        <v>4.8</v>
+        <v>2.98</v>
       </c>
       <c r="P17" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.94</v>
+        <v>3.3</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="T17" t="n">
-        <v>2.11</v>
+        <v>2.62</v>
       </c>
       <c r="U17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V17" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.65</v>
       </c>
-      <c r="V17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AF17" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.15</v>
+        <v>1.49</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46078.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="M18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N18" t="n">
         <v>2.87</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T18" t="n">
         <v>3.3</v>
       </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.75</v>
+        <v>1.37</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.93</v>
+        <v>2.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46078.625</v>
@@ -2641,12 +2641,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,76 +2682,76 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="M19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P19" t="n">
         <v>2.6</v>
       </c>
-      <c r="M19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.62</v>
+        <v>1.48</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.44</v>
+        <v>2.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>46078.64583333334</v>
+        <v>46078.625</v>
       </c>
     </row>
     <row r="20">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,76 +2801,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="M20" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="N20" t="n">
-        <v>2.1</v>
+        <v>2.66</v>
       </c>
       <c r="O20" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.27</v>
+        <v>2.62</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
-        <v>46078.65625</v>
+        <v>46078.64583333334</v>
       </c>
     </row>
     <row r="21">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,76 +3039,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="N22" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="O22" t="n">
-        <v>3.4</v>
+        <v>4.62</v>
       </c>
       <c r="P22" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="S22" t="n">
-        <v>2.59</v>
+        <v>2.39</v>
       </c>
       <c r="T22" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="U22" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="V22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W22" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="Z22" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.02</v>
+        <v>2.27</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AE22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF22" t="n">
         <v>1.75</v>
       </c>
-      <c r="AF22" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>46078.66666666666</v>
+        <v>46078.65625</v>
       </c>
     </row>
     <row r="23">
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,76 +3277,76 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V24" t="n">
+        <v>8</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF24" t="n">
         <v>2.05</v>
-      </c>
-      <c r="M24" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V24" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.8</v>
       </c>
       <c r="AG24" t="n">
         <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>46078.6875</v>
+        <v>46078.66666666666</v>
       </c>
     </row>
     <row r="25">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R25" t="n">
         <v>1.57</v>
       </c>
-      <c r="M25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O25" t="n">
+      <c r="S25" t="n">
         <v>2.25</v>
       </c>
-      <c r="P25" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="R25" t="n">
+      <c r="T25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V25" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF25" t="n">
         <v>1.55</v>
       </c>
-      <c r="S25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V25" t="n">
-        <v>9</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46078.6875</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="M26" t="n">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="N26" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O26" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="P26" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="S26" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="T26" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="U26" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V26" t="n">
-        <v>9.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X26" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.25</v>
+        <v>2.59</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AC26" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46078.6875</v>
@@ -3593,12 +3593,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,76 +3634,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.38</v>
+        <v>1.57</v>
       </c>
       <c r="M27" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>2.72</v>
+        <v>5.5</v>
       </c>
       <c r="O27" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="P27" t="n">
-        <v>2.09</v>
+        <v>1.89</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.25</v>
+        <v>7.3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="S27" t="n">
-        <v>2.73</v>
+        <v>2.3</v>
       </c>
       <c r="T27" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="U27" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="V27" t="n">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="W27" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
         <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.26</v>
+        <v>1.48</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.24</v>
+        <v>2.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.41</v>
+        <v>4.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.49</v>
+        <v>2.3</v>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>46078.69791666666</v>
+        <v>46078.6875</v>
       </c>
     </row>
     <row r="28">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.19</v>
+        <v>2.38</v>
       </c>
       <c r="M28" t="n">
-        <v>6.4</v>
+        <v>3.35</v>
       </c>
       <c r="N28" t="n">
-        <v>12</v>
+        <v>2.72</v>
       </c>
       <c r="O28" t="n">
-        <v>1.59</v>
+        <v>3</v>
       </c>
       <c r="P28" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S28" t="n">
         <v>2.73</v>
       </c>
-      <c r="Q28" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.5</v>
-      </c>
       <c r="T28" t="n">
-        <v>2.23</v>
+        <v>2.9</v>
       </c>
       <c r="U28" t="n">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="V28" t="n">
-        <v>4.8</v>
+        <v>6.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="X28" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.9</v>
+        <v>3.24</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.39</v>
+        <v>1.85</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.25</v>
+        <v>3.41</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.64</v>
+        <v>1.28</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.11</v>
+        <v>1.31</v>
       </c>
       <c r="AH28" t="n">
-        <v>4.33</v>
+        <v>1.49</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46078.69791666666</v>
@@ -3950,12 +3950,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,76 +3991,76 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.53</v>
+        <v>1.19</v>
       </c>
       <c r="M30" t="n">
-        <v>4.68</v>
+        <v>6.4</v>
       </c>
       <c r="N30" t="n">
-        <v>6.86</v>
+        <v>12</v>
       </c>
       <c r="O30" t="n">
-        <v>1.93</v>
+        <v>1.59</v>
       </c>
       <c r="P30" t="n">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.25</v>
+        <v>9.5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S30" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="T30" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V30" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AE30" t="n">
         <v>2.1</v>
       </c>
-      <c r="U30" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AF30" t="n">
-        <v>2.2</v>
+        <v>1.64</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.81</v>
+        <v>4.33</v>
       </c>
       <c r="AI30" s="3" t="n">
-        <v>46078.70833333334</v>
+        <v>46078.69791666666</v>
       </c>
     </row>
     <row r="31">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="M31" t="n">
-        <v>4.58</v>
+        <v>6.14</v>
       </c>
       <c r="N31" t="n">
-        <v>5.49</v>
+        <v>9.85</v>
       </c>
       <c r="O31" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="P31" t="n">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="Q31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R31" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="S31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V31" t="n">
         <v>3.6</v>
       </c>
-      <c r="T31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V31" t="n">
-        <v>4.6</v>
-      </c>
       <c r="W31" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.3</v>
+        <v>7.25</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.63</v>
+        <v>1.29</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.45</v>
+        <v>3.7</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="M32" t="n">
-        <v>3.54</v>
+        <v>4.68</v>
       </c>
       <c r="N32" t="n">
-        <v>4.08</v>
+        <v>6.86</v>
       </c>
       <c r="O32" t="n">
-        <v>2.38</v>
+        <v>1.93</v>
       </c>
       <c r="P32" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T32" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3.22</v>
-      </c>
       <c r="U32" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="V32" t="n">
-        <v>8.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="W32" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="X32" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.8</v>
+        <v>5.25</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.92</v>
+        <v>2.2</v>
       </c>
       <c r="AD32" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG32" t="n">
         <v>1.18</v>
       </c>
-      <c r="AE32" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH32" t="n">
-        <v>1.95</v>
+        <v>2.81</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.33</v>
+        <v>1.85</v>
       </c>
       <c r="M33" t="n">
-        <v>6.14</v>
+        <v>3.54</v>
       </c>
       <c r="N33" t="n">
-        <v>9.85</v>
+        <v>4.08</v>
       </c>
       <c r="O33" t="n">
-        <v>1.58</v>
+        <v>2.38</v>
       </c>
       <c r="P33" t="n">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q33" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="R33" t="n">
-        <v>1.17</v>
+        <v>1.47</v>
       </c>
       <c r="S33" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="T33" t="n">
-        <v>1.85</v>
+        <v>3.22</v>
       </c>
       <c r="U33" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="V33" t="n">
-        <v>3.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W33" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="X33" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.07</v>
+        <v>1.4</v>
       </c>
       <c r="Z33" t="n">
-        <v>7.25</v>
+        <v>2.8</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="AB33" t="n">
-        <v>3.4</v>
+        <v>1.75</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.87</v>
+        <v>3.92</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.83</v>
+        <v>1.18</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.66</v>
+        <v>2.03</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AH33" t="n">
-        <v>3.7</v>
+        <v>1.95</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4426,12 +4426,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4463,80 +4463,80 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>5.5</v>
+        <v>1.63</v>
       </c>
       <c r="M34" t="n">
-        <v>3.8</v>
+        <v>4.58</v>
       </c>
       <c r="N34" t="n">
-        <v>1.5</v>
+        <v>5.49</v>
       </c>
       <c r="O34" t="n">
-        <v>6.34</v>
+        <v>1.95</v>
       </c>
       <c r="P34" t="n">
-        <v>2.11</v>
+        <v>2.55</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.09</v>
+        <v>5</v>
       </c>
       <c r="R34" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="S34" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="T34" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="U34" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="V34" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="W34" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X34" t="n">
         <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.27</v>
+        <v>1.09</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.35</v>
+        <v>5.3</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.87</v>
+        <v>1.63</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.81</v>
+        <v>2.15</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.27</v>
+        <v>1.63</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="AG34" t="n">
         <v>1.18</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.06</v>
+        <v>2.45</v>
       </c>
       <c r="AI34" s="3" t="n">
-        <v>46078.72916666666</v>
+        <v>46078.70833333334</v>
       </c>
     </row>
     <row r="35">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4582,77 +4582,77 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.14</v>
+        <v>5.5</v>
       </c>
       <c r="M35" t="n">
-        <v>6.09</v>
+        <v>3.8</v>
       </c>
       <c r="N35" t="n">
-        <v>13.58</v>
+        <v>1.5</v>
       </c>
       <c r="O35" t="n">
-        <v>1.5</v>
+        <v>6.34</v>
       </c>
       <c r="P35" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S35" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q35" t="n">
-        <v>12</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S35" t="n">
-        <v>3.65</v>
-      </c>
       <c r="T35" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="U35" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="V35" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="W35" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="Z35" t="n">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.25</v>
+        <v>1.81</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.38</v>
+        <v>1.92</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AH35" t="n">
-        <v>4.8</v>
+        <v>1.06</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46078.72916666666</v>
@@ -4664,27 +4664,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4701,80 +4701,80 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.17</v>
+        <v>1.14</v>
       </c>
       <c r="M36" t="n">
-        <v>3.34</v>
+        <v>6.09</v>
       </c>
       <c r="N36" t="n">
-        <v>3.55</v>
+        <v>13.58</v>
       </c>
       <c r="O36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>12</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V36" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC36" t="n">
         <v>2.4</v>
       </c>
-      <c r="P36" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R36" t="n">
+      <c r="AD36" t="n">
         <v>1.44</v>
       </c>
-      <c r="S36" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T36" t="n">
-        <v>3</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V36" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AE36" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.95</v>
+        <v>4.8</v>
       </c>
       <c r="AI36" s="3" t="n">
-        <v>46078.79166666666</v>
+        <v>46078.72916666666</v>
       </c>
     </row>
     <row r="37">
@@ -4788,22 +4788,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.97</v>
+        <v>2.23</v>
       </c>
       <c r="M37" t="n">
-        <v>3.27</v>
+        <v>2.81</v>
       </c>
       <c r="N37" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="O37" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>4</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T37" t="n">
         <v>3.5</v>
       </c>
-      <c r="P37" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.9</v>
-      </c>
       <c r="U37" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="V37" t="n">
-        <v>7.75</v>
+        <v>11</v>
       </c>
       <c r="W37" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X37" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.32</v>
+        <v>1.52</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.91</v>
+        <v>1.66</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46078.79166666666</v>
@@ -4907,22 +4907,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.23</v>
+        <v>2.97</v>
       </c>
       <c r="M38" t="n">
-        <v>2.81</v>
+        <v>3.27</v>
       </c>
       <c r="N38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V38" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC38" t="n">
         <v>3.4</v>
       </c>
-      <c r="O38" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P38" t="n">
+      <c r="AD38" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF38" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q38" t="n">
-        <v>4</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V38" t="n">
-        <v>11</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AG38" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46078.79166666666</v>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,49 +5062,49 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.68</v>
+        <v>2.17</v>
       </c>
       <c r="M39" t="n">
-        <v>3.15</v>
+        <v>3.34</v>
       </c>
       <c r="N39" t="n">
-        <v>2.85</v>
+        <v>3.55</v>
       </c>
       <c r="O39" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="P39" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="R39" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="S39" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="T39" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U39" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="V39" t="n">
-        <v>9.75</v>
+        <v>8.5</v>
       </c>
       <c r="W39" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X39" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AA39" t="n">
         <v>2.3</v>
@@ -5113,25 +5113,25 @@
         <v>1.53</v>
       </c>
       <c r="AC39" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="AI39" s="3" t="n">
-        <v>46078.8125</v>
+        <v>46078.79166666666</v>
       </c>
     </row>
     <row r="40">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,76 +5181,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.92</v>
+        <v>2.68</v>
       </c>
       <c r="M40" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O40" t="n">
         <v>3.6</v>
       </c>
-      <c r="N40" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O40" t="n">
-        <v>2.45</v>
-      </c>
       <c r="P40" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q40" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="R40" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V40" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH40" t="n">
         <v>1.4</v>
       </c>
-      <c r="S40" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V40" t="n">
-        <v>7</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AI40" s="3" t="n">
-        <v>46078.83333333334</v>
+        <v>46078.8125</v>
       </c>
     </row>
     <row r="41">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,40 +5300,40 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.71</v>
+        <v>1.92</v>
       </c>
       <c r="M41" t="n">
-        <v>3.79</v>
+        <v>3.6</v>
       </c>
       <c r="N41" t="n">
-        <v>5.14</v>
+        <v>4.1</v>
       </c>
       <c r="O41" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="P41" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="R41" t="n">
         <v>1.4</v>
       </c>
       <c r="S41" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="T41" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="U41" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V41" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W41" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X41" t="n">
         <v>1.06</v>
@@ -5342,25 +5342,25 @@
         <v>1.3</v>
       </c>
       <c r="Z41" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AC41" t="n">
         <v>3.3</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG41" t="n">
         <v>1.3</v>
@@ -5369,7 +5369,7 @@
         <v>1.88</v>
       </c>
       <c r="AI41" s="3" t="n">
-        <v>46078.89583333334</v>
+        <v>46078.83333333334</v>
       </c>
     </row>
     <row r="42">
@@ -5488,6 +5488,125 @@
         <v>1.62</v>
       </c>
       <c r="AI42" s="3" t="n">
+        <v>46078.89583333334</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="M43" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="N43" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="O43" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V43" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AI43" s="3" t="n">
         <v>46078.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -893,32 +893,32 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.6</v>
+        <v>4.17</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N4" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="O4" t="n">
-        <v>5.15</v>
+        <v>5.25</v>
       </c>
       <c r="P4" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="R4" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S4" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="T4" t="n">
         <v>3.2</v>
@@ -933,37 +933,37 @@
         <v>1.04</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46078.41666666666</v>
@@ -999,90 +999,90 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="M5" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V5" t="n">
+        <v>10</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AA5" t="n">
         <v>2.65</v>
       </c>
-      <c r="N5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46078.41666666666</v>
@@ -1118,69 +1118,69 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N6" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="P6" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.46</v>
+        <v>4.51</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="T6" t="n">
         <v>3.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="V6" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
         <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.59</v>
+        <v>2.49</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AB6" t="n">
         <v>1.61</v>
@@ -1192,16 +1192,16 @@
         <v>1.16</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46078.4375</v>
@@ -1237,20 +1237,20 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1369,26 +1369,26 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
         <v>1.97</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="N8" t="n">
-        <v>3.48</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="P8" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.27</v>
+        <v>5.82</v>
       </c>
       <c r="R8" t="n">
         <v>1.47</v>
@@ -1397,10 +1397,10 @@
         <v>2.39</v>
       </c>
       <c r="T8" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="V8" t="n">
         <v>8.5</v>
@@ -1412,13 +1412,13 @@
         <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AB8" t="n">
         <v>1.57</v>
@@ -1430,16 +1430,16 @@
         <v>1.16</v>
       </c>
       <c r="AE8" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46078.45833333334</v>
@@ -1466,19 +1466,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="P9" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="R9" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="T9" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="V9" t="n">
-        <v>9.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
         <v>1.07</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.25</v>
+        <v>4.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46078.5</v>
@@ -1575,22 +1575,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1607,77 +1607,77 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.55</v>
+        <v>2.4</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>6</v>
+        <v>2.95</v>
       </c>
       <c r="O10" t="n">
-        <v>2.15</v>
+        <v>3.18</v>
       </c>
       <c r="P10" t="n">
-        <v>2.25</v>
+        <v>1.82</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.95</v>
+        <v>4.06</v>
       </c>
       <c r="R10" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>3.13</v>
+        <v>2.48</v>
       </c>
       <c r="T10" t="n">
-        <v>2.73</v>
+        <v>3.34</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="V10" t="n">
-        <v>6.5</v>
+        <v>8.9</v>
       </c>
       <c r="W10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X10" t="n">
         <v>1.08</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y10" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.24</v>
+        <v>2.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.96</v>
+        <v>2.35</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.88</v>
+        <v>1.57</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.12</v>
+        <v>4.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46078.5</v>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1726,77 +1726,77 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N11" t="n">
+        <v>6</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH11" t="n">
         <v>2.3</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V11" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.46</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46078.5</v>
@@ -1852,10 +1852,10 @@
         <v>4.15</v>
       </c>
       <c r="M12" t="n">
-        <v>4.05</v>
+        <v>3.74</v>
       </c>
       <c r="N12" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="N13" t="n">
-        <v>1.84</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>3.75</v>
+        <v>2.05</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="S13" t="n">
-        <v>2.84</v>
+        <v>3.12</v>
       </c>
       <c r="T13" t="n">
-        <v>2.82</v>
+        <v>2.49</v>
       </c>
       <c r="U13" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="V13" t="n">
-        <v>7.1</v>
+        <v>5.95</v>
       </c>
       <c r="W13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X13" t="n">
         <v>1.04</v>
       </c>
-      <c r="X13" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y13" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.99</v>
+        <v>1.67</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.1</v>
+        <v>2.69</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.3</v>
+        <v>2.25</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46078.60416666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="M14" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="N14" t="n">
-        <v>5</v>
+        <v>1.84</v>
       </c>
       <c r="O14" t="n">
-        <v>2.05</v>
+        <v>3.75</v>
       </c>
       <c r="P14" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="R14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V14" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.29</v>
       </c>
-      <c r="S14" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V14" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AE14" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.25</v>
+        <v>1.3</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46078.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="M16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N16" t="n">
         <v>2.87</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T16" t="n">
         <v>3.3</v>
       </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.75</v>
+        <v>1.37</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.93</v>
+        <v>2.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46078.625</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="M18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB18" t="n">
         <v>2.5</v>
       </c>
-      <c r="M18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="O18" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="V18" t="n">
-        <v>10</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AC18" t="n">
-        <v>3.75</v>
+        <v>2.15</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.17</v>
+        <v>1.62</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46078.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>7.25</v>
+        <v>2.32</v>
       </c>
       <c r="M19" t="n">
-        <v>5.5</v>
+        <v>2.87</v>
       </c>
       <c r="N19" t="n">
-        <v>1.37</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="Z19" t="n">
-        <v>5</v>
+        <v>1.93</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.48</v>
+        <v>2.62</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.5</v>
+        <v>1.44</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46078.625</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>10.7</v>
+        <v>2.63</v>
       </c>
       <c r="M23" t="n">
-        <v>9</v>
+        <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>1.07</v>
+        <v>2.5</v>
       </c>
       <c r="O23" t="n">
-        <v>9</v>
+        <v>3.4</v>
       </c>
       <c r="P23" t="n">
-        <v>3.41</v>
+        <v>1.96</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.44</v>
+        <v>3.1</v>
       </c>
       <c r="R23" t="n">
-        <v>1.12</v>
+        <v>1.41</v>
       </c>
       <c r="S23" t="n">
-        <v>4.8</v>
+        <v>2.59</v>
       </c>
       <c r="T23" t="n">
-        <v>1.83</v>
+        <v>2.96</v>
       </c>
       <c r="U23" t="n">
-        <v>1.86</v>
+        <v>1.32</v>
       </c>
       <c r="V23" t="n">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="W23" t="n">
-        <v>1.24</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.05</v>
+        <v>1.28</v>
       </c>
       <c r="Z23" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.24</v>
+        <v>2.02</v>
       </c>
       <c r="AB23" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE23" t="n">
         <v>1.75</v>
       </c>
-      <c r="AD23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AF23" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.06</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46078.66666666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.63</v>
+        <v>10.7</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>9</v>
       </c>
       <c r="N24" t="n">
-        <v>2.5</v>
+        <v>1.07</v>
       </c>
       <c r="O24" t="n">
-        <v>3.4</v>
+        <v>9</v>
       </c>
       <c r="P24" t="n">
-        <v>1.96</v>
+        <v>3.41</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.1</v>
+        <v>1.44</v>
       </c>
       <c r="R24" t="n">
-        <v>1.41</v>
+        <v>1.12</v>
       </c>
       <c r="S24" t="n">
-        <v>2.59</v>
+        <v>4.8</v>
       </c>
       <c r="T24" t="n">
-        <v>2.96</v>
+        <v>1.83</v>
       </c>
       <c r="U24" t="n">
-        <v>1.32</v>
+        <v>1.86</v>
       </c>
       <c r="V24" t="n">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.02</v>
+        <v>1.24</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.28</v>
+        <v>1.05</v>
       </c>
       <c r="Z24" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.02</v>
+        <v>1.24</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.5</v>
+        <v>1.75</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.22</v>
+        <v>1.95</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.06</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.4</v>
+        <v>1.04</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46078.66666666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="M25" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="O25" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="P25" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.75</v>
+        <v>7.3</v>
       </c>
       <c r="R25" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="S25" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="T25" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U25" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V25" t="n">
-        <v>9.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="W25" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X25" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.8</v>
+        <v>2.44</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46078.6875</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R27" t="n">
         <v>1.57</v>
       </c>
-      <c r="M27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N27" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O27" t="n">
+      <c r="S27" t="n">
         <v>2.25</v>
       </c>
-      <c r="P27" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="R27" t="n">
+      <c r="T27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V27" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF27" t="n">
         <v>1.55</v>
       </c>
-      <c r="S27" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V27" t="n">
-        <v>9</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46078.6875</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T28" t="n">
         <v>2.38</v>
       </c>
-      <c r="M28" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N28" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="O28" t="n">
-        <v>3</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.9</v>
-      </c>
       <c r="U28" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="V28" t="n">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="W28" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X28" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.24</v>
+        <v>3.98</v>
       </c>
       <c r="AA28" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.41</v>
+        <v>2.75</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46078.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="M29" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N29" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O29" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="P29" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="Q29" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="R29" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="S29" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="T29" t="n">
-        <v>2.38</v>
+        <v>2.9</v>
       </c>
       <c r="U29" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="V29" t="n">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X29" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.98</v>
+        <v>3.24</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.23</v>
+        <v>1.85</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.75</v>
+        <v>3.41</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46078.69791666666</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="M33" t="n">
-        <v>3.54</v>
+        <v>4.58</v>
       </c>
       <c r="N33" t="n">
-        <v>4.08</v>
+        <v>5.49</v>
       </c>
       <c r="O33" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="P33" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>5</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T33" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q33" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T33" t="n">
-        <v>3.22</v>
-      </c>
       <c r="U33" t="n">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="V33" t="n">
-        <v>8.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="W33" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="X33" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.4</v>
+        <v>1.09</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.92</v>
+        <v>2.2</v>
       </c>
       <c r="AD33" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG33" t="n">
         <v>1.18</v>
       </c>
-      <c r="AE33" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH33" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="M34" t="n">
-        <v>4.58</v>
+        <v>3.54</v>
       </c>
       <c r="N34" t="n">
-        <v>5.49</v>
+        <v>4.08</v>
       </c>
       <c r="O34" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V34" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA34" t="n">
         <v>1.95</v>
       </c>
-      <c r="P34" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>5</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V34" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AB34" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.2</v>
+        <v>3.92</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.63</v>
+        <v>1.18</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.6</v>
+        <v>2.03</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.3</v>
+        <v>1.72</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46078.70833333334</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>5.5</v>
+        <v>1.14</v>
       </c>
       <c r="M35" t="n">
-        <v>3.8</v>
+        <v>6.09</v>
       </c>
       <c r="N35" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="O35" t="n">
         <v>1.5</v>
       </c>
-      <c r="O35" t="n">
-        <v>6.34</v>
-      </c>
       <c r="P35" t="n">
-        <v>2.11</v>
+        <v>2.75</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.09</v>
+        <v>12</v>
       </c>
       <c r="R35" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S35" t="n">
-        <v>2.75</v>
+        <v>3.65</v>
       </c>
       <c r="T35" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="U35" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="V35" t="n">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="W35" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.87</v>
+        <v>1.53</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.81</v>
+        <v>2.25</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.92</v>
+        <v>2.38</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.06</v>
+        <v>4.8</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46078.72916666666</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.14</v>
+        <v>5.5</v>
       </c>
       <c r="M36" t="n">
-        <v>6.09</v>
+        <v>3.8</v>
       </c>
       <c r="N36" t="n">
-        <v>13.58</v>
+        <v>1.5</v>
       </c>
       <c r="O36" t="n">
-        <v>1.5</v>
+        <v>6.34</v>
       </c>
       <c r="P36" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S36" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q36" t="n">
-        <v>12</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S36" t="n">
-        <v>3.65</v>
-      </c>
       <c r="T36" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="U36" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="V36" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="W36" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="Z36" t="n">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.25</v>
+        <v>1.81</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.38</v>
+        <v>1.92</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AH36" t="n">
-        <v>4.8</v>
+        <v>1.06</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46078.72916666666</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.97</v>
+        <v>2.17</v>
       </c>
       <c r="M38" t="n">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
       <c r="N38" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="O38" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="P38" t="n">
         <v>2.05</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="R38" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S38" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T38" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U38" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V38" t="n">
-        <v>7.75</v>
+        <v>8.5</v>
       </c>
       <c r="W38" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X38" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46078.79166666666</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.17</v>
+        <v>2.97</v>
       </c>
       <c r="M39" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="N39" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="O39" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="P39" t="n">
         <v>2.05</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="R39" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S39" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T39" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V39" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG39" t="n">
         <v>1.33</v>
       </c>
-      <c r="V39" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH39" t="n">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46078.79166666666</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,28 +5419,28 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="M42" t="n">
-        <v>3.44</v>
+        <v>3.79</v>
       </c>
       <c r="N42" t="n">
-        <v>3.37</v>
+        <v>5.14</v>
       </c>
       <c r="O42" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="P42" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="R42" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S42" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="T42" t="n">
         <v>2.8</v>
@@ -5455,37 +5455,37 @@
         <v>1.08</v>
       </c>
       <c r="X42" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD42" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z42" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD42" t="n">
+      <c r="AE42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG42" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE42" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH42" t="n">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46078.89583333334</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,28 +5538,28 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="M43" t="n">
-        <v>3.79</v>
+        <v>3.44</v>
       </c>
       <c r="N43" t="n">
-        <v>5.14</v>
+        <v>3.37</v>
       </c>
       <c r="O43" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="P43" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="R43" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S43" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="T43" t="n">
         <v>2.8</v>
@@ -5574,37 +5574,37 @@
         <v>1.08</v>
       </c>
       <c r="X43" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y43" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD43" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z43" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB43" t="n">
+      <c r="AE43" t="n">
         <v>1.73</v>
       </c>
-      <c r="AC43" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF43" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46078.89583333334</v>

--- a/jogos_2026-02-25.xlsx
+++ b/jogos_2026-02-25.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,23 +871,23 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>1</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.17</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>3.2</v>
+        <v>2.48</v>
       </c>
       <c r="N4" t="n">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="O4" t="n">
-        <v>5.25</v>
+        <v>4.42</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.36</v>
+        <v>3.7</v>
       </c>
       <c r="R4" t="n">
-        <v>1.47</v>
+        <v>1.76</v>
       </c>
       <c r="S4" t="n">
-        <v>2.39</v>
+        <v>1.93</v>
       </c>
       <c r="T4" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="U4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V4" t="n">
+        <v>10</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH4" t="n">
         <v>1.27</v>
-      </c>
-      <c r="V4" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.11</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46078.41666666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,22 +990,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>4.17</v>
       </c>
       <c r="M5" t="n">
-        <v>2.48</v>
+        <v>3.2</v>
       </c>
       <c r="N5" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="O5" t="n">
-        <v>4.42</v>
+        <v>5.25</v>
       </c>
       <c r="P5" t="n">
-        <v>1.63</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.7</v>
+        <v>2.36</v>
       </c>
       <c r="R5" t="n">
-        <v>1.76</v>
+        <v>1.47</v>
       </c>
       <c r="S5" t="n">
-        <v>1.93</v>
+        <v>2.39</v>
       </c>
       <c r="T5" t="n">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="V5" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH5" t="n">
         <v>1.11</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.27</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46078.41666666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,19 +1109,19 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="M6" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="O6" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="P6" t="n">
-        <v>1.86</v>
+        <v>1.99</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.51</v>
+        <v>3.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S6" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="T6" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V6" t="n">
-        <v>9.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.49</v>
+        <v>3.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.1</v>
+        <v>3.48</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.99</v>
+        <v>1.76</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46078.4375</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,19 +1228,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="M7" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N7" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="P7" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.99</v>
       </c>
-      <c r="Q7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V7" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AF7" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46078.4375</v>
@@ -1456,29 +1456,29 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.42</v>
+        <v>1.55</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>6</v>
       </c>
       <c r="O9" t="n">
-        <v>3.14</v>
+        <v>2.15</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.4</v>
+        <v>5.95</v>
       </c>
       <c r="R9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U9" t="n">
         <v>1.4</v>
       </c>
-      <c r="S9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.3</v>
-      </c>
       <c r="V9" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.7</v>
+        <v>3.24</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.23</v>
+        <v>1.96</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.05</v>
+        <v>3.12</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="AE9" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF9" t="n">
         <v>1.85</v>
       </c>
-      <c r="AF9" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AG9" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46078.5</v>
@@ -1694,29 +1694,29 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1726,77 +1726,77 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.55</v>
+        <v>2.42</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>6</v>
+        <v>3.05</v>
       </c>
       <c r="O11" t="n">
-        <v>2.15</v>
+        <v>3.14</v>
       </c>
       <c r="P11" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.95</v>
+        <v>3.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>3.13</v>
+        <v>2.6</v>
       </c>
       <c r="T11" t="n">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="V11" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.24</v>
+        <v>2.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.96</v>
+        <v>2.23</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.12</v>
+        <v>4.05</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46078.5</v>
@@ -1832,20 +1832,20 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1942,19 +1942,19 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1964,77 +1964,77 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="M13" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="O13" t="n">
+        <v>4</v>
+      </c>
+      <c r="P13" t="n">
         <v>2.05</v>
       </c>
-      <c r="P13" t="n">
-        <v>2.4</v>
-      </c>
       <c r="Q13" t="n">
-        <v>4.8</v>
+        <v>2.45</v>
       </c>
       <c r="R13" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="S13" t="n">
-        <v>3.12</v>
+        <v>2.92</v>
       </c>
       <c r="T13" t="n">
-        <v>2.49</v>
+        <v>2.74</v>
       </c>
       <c r="U13" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="V13" t="n">
-        <v>5.95</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.69</v>
+        <v>3.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AG13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH13" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>2.25</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46078.60416666666</v>
@@ -2061,16 +2061,16 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -2083,77 +2083,77 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.5</v>
+        <v>1.55</v>
       </c>
       <c r="M14" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="N14" t="n">
-        <v>1.84</v>
+        <v>4.65</v>
       </c>
       <c r="O14" t="n">
-        <v>3.75</v>
+        <v>2.15</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.6</v>
+        <v>4.59</v>
       </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>2.84</v>
+        <v>3.08</v>
       </c>
       <c r="T14" t="n">
-        <v>2.82</v>
+        <v>2.53</v>
       </c>
       <c r="U14" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="V14" t="n">
-        <v>7.1</v>
+        <v>5.8</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.99</v>
+        <v>1.71</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.3</v>
+        <v>2.05</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46078.60416666666</v>
@@ -2212,58 +2212,58 @@
         <v>3.55</v>
       </c>
       <c r="N15" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O15" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="P15" t="n">
         <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R15" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="T15" t="n">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="U15" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="V15" t="n">
         <v>5.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z15" t="n">
         <v>4.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AD15" t="n">
         <v>1.44</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AF15" t="n">
         <v>2.2</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="M16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S16" t="n">
         <v>2.9</v>
       </c>
-      <c r="N16" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="O16" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.31</v>
-      </c>
       <c r="T16" t="n">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="U16" t="n">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="V16" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.5</v>
+        <v>3.54</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.45</v>
+        <v>1.83</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.5</v>
+        <v>2.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.28</v>
+        <v>1.49</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46078.625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,19 +2418,19 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2440,77 +2440,77 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.84</v>
+        <v>6.68</v>
       </c>
       <c r="M17" t="n">
-        <v>2.85</v>
+        <v>5.05</v>
       </c>
       <c r="N17" t="n">
-        <v>2.25</v>
+        <v>1.39</v>
       </c>
       <c r="O17" t="n">
-        <v>2.98</v>
+        <v>4.8</v>
       </c>
       <c r="P17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC17" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.9</v>
-      </c>
-